--- a/political_youtube/transcript_analysis/first_run_vertexai/complete_classification.xlsx
+++ b/political_youtube/transcript_analysis/first_run_vertexai/complete_classification.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bened\PycharmProjects\youtube_data\political_youtube\transcript_analysis\first_run_vertexai\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\PyhcarmProjects\youtube_data\political_youtube\transcript_analysis\first_run_vertexai\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E741CA41-F6B0-4D40-B83E-0D71E95A498C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{118B088C-84EE-4567-B5B2-CEF3D9EC26DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="20715" windowHeight="13155" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="113">
   <si>
     <t>video_id</t>
   </si>
@@ -148,6 +148,222 @@
   </si>
   <si>
     <t>RPLNJCPzgWc</t>
+  </si>
+  <si>
+    <t>[Musik] erstaunlich dass dieser Mann noch lebt bei Verrätern kennt Putin sonst keine Gnade [Musik] aktuell geht dieses Video viral es soll brigoschi zeigen [Musik] kämpferisch die Authentizität des Materials schwer zu klären doch eins ist sicher die Verbreitung solcher vernichtenden Anklagen dürfte dem russischen Präsidenten nicht gefallen ein Mann mit vielen Gesichtern erlebte im Luxus schuf sich zahlreiche Identitäten man kennt ihn als Putin treuen Koch despotischen Oligarchen als brutalen und ambitionierten Söldner Chef der wagnertruppe immer wieder greift er Putin und die russische Militärführung öffentlich an wer ist der Mann der Putin herausfordert wir sprechen mit [Musik] insiders er wird verehrt und gefürchtet doch wie groß ist seine Macht tatsächlich Rätsel prigoshi der orchestraato wohin dirigiert er seine Truppen als nächstes frontal Spurensuche brigoshin [Musik] so wie in Russland lange gesehen wurde Putins martialischer Heerführer der im Auftrag des Kreml mit seiner Gruppe Wagner weltweit Angst und Schrecken verbreitet und seine Wagner Truppen sind allgegenwärtig spätestens seit der kurzmeuterei die 200 km vor Moskau abrupt endete ist selten sind Überwachung Joseph Jones hat früher für den britischen Geheimdienst gearbeitet seit Jahren analysiert er Daten und Posts auf Social Media Kanälen der Gruppe Wagner die Zukunft der Gruppe Wagner undurchsichtig und auch die ihres Chefs laut Geheimdienst Information trachtet Putin nach Rache i think Partner Chef mit Kritikern umgeht hat er schon mehrfach bewiesen [Musik] auch prigoschin ist berüchtigt für seine Skrupellosigkeit und das schon vor seiner Zeit als wagner-chef damals hat Maxim ihn kennen und fürchten gelernt Sankt Petersburg Maxim arbeitete hier für brigoschin als Security man psychotherror und Schikanen gehörten zum Alltag at nights and scary [Musik] you sleeping your cats you know that's sleep I see time not sleeping no I'm not sleeping I see that you sleep and I know that your slipin your fucking the head of like Touch Ideen ein Vorfall ist Maxim besonders in Erinnerung geblieben brigochen habe mitbekommen dass Maxims damaliger Vorgesetzter sich die Hälfte des Gehalts der Angestellten in die eigene Tasche gesteckt habe plötzlich sei sein Chef dann verschwunden oh mein Gott [Musik] zwei Tage sei er noch geblieben dann Flo er heute lebt Maxim in einem anderen Land hat immer noch Angst vor brigoshi as just like a prison man just all these of fancy root the world the style of speaking gefängnisjago nicht verwunderlich brigochen selbst saß neun Jahre im Gefängnis seine Nähe zu straff Gefangenen zeigt auch das Projekt Cara Name für die massenhafte Rekrutierung von Häftlingen für den Angriffskrieg in der Ukraine diese Bilder zeigen die prigos in Russlands Gefängnissen unserer wird laut Gruppe Wagner wurden 49.000 Häftlinge rekrutiert Gefangene mit zum Teil lebenslangen Haftstrafen lockte er mit dem Versprechen von Freiheit nach 6 Monaten Söldner Einsatz im Krieg jetzt muss man aber auch wissen dass natürlich gerade diese Strafgefangenen ein Großteil dieser völlig absorten Wellen von Angriffen im bachmut gestellt haben das heißt ein großer Anteil dieser Kämpfer hat gar keine Chance gehabt die sechs Monate zu überleben jetzt wurde das Projekt Kabel beendet die Söldner der Gruppe Wagner von ihren sich neu hunderte Fahrzeuge auf dem Weg nach Belarus vor Ort spricht rigorchin zu seinen Kämpfern kurz darauf ein bizarrer Auftritt Putin und der belarussische Machthaber Lukaschenko Scherzen über einen Ausflug der Söldner nach Polen dann hast natürlich die Vorstellung von Wagner Söldnern auf direktem Weg in den Westen das soll vor allem Ängste führen Wagner ist für Russland als Unsicherheitsfaktor über die Ukraine hinaus wichtig als Unsicherheitsfaktor der jetzt auch ganz klar nicht mehr als Russland definiert werden kann ist es natürlich ein Vorteil und wenn dann hier Dinge passieren die vielleicht auch gar nicht durch den Kreml angeordnet wurden erhöhtes den Druck auf NATO es ist Teil der hybriden Kriegsführung und der Sinn und Zweck ist einfach Unsicherheit zu produzieren was Wagnis Rolle bisher über welche Rolle brigosch ihn dabei spielen wird ist noch unklar fest steht weiterhin scheint er mächtig genug um den Kreml-Chef herauszufordern brigoschin bleibt unberechenbar so wie seine Söldner die Gruppe Wagner was denkst du was wird der nächste Schachzug schreibt uns in die Kommentare und wenn du mehr über das Geschäft der Wagner sollte man wissen willst klick auf unseren Film Links</t>
+  </si>
+  <si>
+    <t>cLiNYKAZg60</t>
+  </si>
+  <si>
+    <t>nJJHj66uruw</t>
+  </si>
+  <si>
+    <t>[Musik] ein Jahr ist es erst her dass die Menschen in Pakistan von Regenfluten vertrieben wurden und nun steht die Provinz Punjab im Osten des Landes unter Wasser hunderte Dörfer sind überschwemmt die Rettungsteams sind unablässig im Einsatz [Applaus] unterwegs deshalb Hochwasser das benachbarte indien hat wegen extremer Monsun Niederschläge überschüssiges Wasser in den Fluss geleitet der die beiden Nachbarländer durchquert Sultan mach Mut hat nur eins im Sinn die eingeschlossenen Menschen zu retten das war alles bewohnbares Land hier leben Menschen die Infrastruktur wurde durch die Überschwemmung zerstört viele dieser Gebiete sind ohne Boot nicht zu erreichen innerhalb weniger Wochen müssen hunderttausende Menschen aus diesem Teil des Punjab evakuiert werden setzt alle Opfer ins Boot und bringt sie an Land habt ihr genug Schwimmwesten kommen sie ja genau Rettungsweste für sie stecken Sie hier die Hand durch wir machen uns Sorgen um unsere Häuser sie wurden beschädigt unser Vieh sitzt hier fest die Maisernte ist vernichtet und das Futter für die Tiere ist durch das Wasser jetzt schlecht wir wissen nicht was wir für unser Vieh tun können es ist die einzige Lebensgrundlage die uns noch bleibt wir sind sechs Brüder und jeder hat ein Feld verloren bei mir wurden sechs Hektar durch Überschwemmungen zerstört ohne die Retter wären wir alle ertrunken die Rettungskräfte lassen niemanden zurück gut so bleib am Boot gut so [Musik] wir hatten den Monsunregen im August erwartet aber er kam schon im Juli die Jahreszeiten verschieben sich in Folge der globalen Erwärmung wenn dieser Trend anhält und es jedes Jahr mehr Regen und Überschwemmungen gibt dann brauchen wir mehr Ressourcen mehr Boote und mehr Helfer mal sehen ob in diesem Dorf noch jemand ist hier jemand hallo wir sind Rettungskräfte wir wollen sie evakuieren okay los geht's in dieser agrarprovinz wurden mehrere hektareis Weizen und Maisfelder zerstört die Retter versuchen auch jene vom gehen zu überzeugen die nicht wollen obwohl sie in Lebensgefahr schweben haben sie Transportmittel und wegzukommen nein überall ist Wasser haben Sie Medikamente und Lebensmittel erhalten nein nichts wie viele Familien leben hier um die 16 sie sollten gehen es ist gefährlich hier nein wir wollen hier nicht weg warum nicht wir nehmen sie mit wir können nirgendwohin kommen Sie mit und wohin in eine Notunterkunft nein ich will nicht dass meine Frau und meine Kinder im Notlager leben sie wollen bleiben von hier kommen Sie nicht auf trockenes Gelände wir brauchen Ihre Hilfe nicht sie sind vom Wasser eingeschlossen das ist sinnlos und gefährlich wir sollten eine Entschädigung und Land den überschwemmungssicherung Gebiet bekommen diese Region wird jedes Jahr überschwemmt wir haben diese Tortur satt es wäre besser für uns wenn wir trinken Sultan Mahmut gibt auf und fährt weg er konnte die Opfer nicht überzeugen und auch nicht ihren Zorn auf die Regierung besänftigen sie werfen ihr Trägheit vor okay wir kommen noch ein Dorf ist überschwemmt [Musik] vor einem Jahr stand ein Drittel von Pakistan nach Rekord Niederschlägen während des Monsuns unter Wasser alles eine Folge des Klimawandels die Provinz sind im Süden des Landes war am stärksten betroffen im distrik da du trafen wir erschart und seine Familie die sich auf einen aus dem Wasser herausragenden Abschnitt einer Autobahn gerettet hatten ihr Haus war überflutet worden [Musik] nach mehreren Monaten ging das Wasser endlich zurück die Zerstörung blieb er schaut konnte in sein Haus zurückkehren und muss sehen wie er alleine klarkommt das ist das Zimmer meiner Schwester es wurde durch die Überschwemmung beschädigt das Dach ist eingestürzt wir haben es erst einmal provisorisch mit Holzlatten ausgebessert es gibt keinen Strom mehr so leute wir hatten ein paar Solarpaneele aber die meisten wurden während der Überschwemmung gestohlen keines von den Geräten hier funktioniert mehr das war das Zimmer meines Bruders nur noch Ziegelsteine das Dachblech wurde gestohlen wir haben weder von der Regierung noch von den NGOs Hilfe erhalten mein Bruder hat im Hof ein Zelt aufgebaut mit unserem Einkommen können wir uns nur ernähren ein Wiederaufbau ist nicht drin sie überleben irgendwie erschatz Familie lebt schon mehrere Monate am Ufer eines Bachs ohne Schutz vor Mücken und anderen Insekten die Kinder sind die ersten Opfer [Musik] krank und es wird nicht besser sie hat epileptische Anfälle ihr ganze Körper wird steif wir müssen ihr Medikamente Spritzen aber zwei Tage lang haben sie nicht aus dem Bett für eine Behandlung haben wir kein Geld wir sind arm wie sollen wir die bezahlen der Arzt sagt sie müsste sechs bis sieben Monate ins Krankenhaus aber dazu fehlen uns einfach die Mittel [Musik] mandure ans Alltag hat sich drastisch verändert 12 Monate später gibt es hier immer noch keinen Strom nichts mehr ist wie vor der Katastrophe [Musik] wir haben kein frisches Wasser und müssen unsere Wäsche in diesem Bach waschen ständig werden wir krank wir haben Fieber leiden unter Übelkeit und außerdem ist es hier sehr heiß jedes Jahr steigen die Temperaturen aber wir müssen das hinnehmen an diesem Tag ist es laut Thermometer 41 Grad heiß gefühlt sind es eher 51 [Musik] der sind gehört zu den heißesten Regionen der Erde Rekordtemperaturen und Überschwemmungen haben die Ernten vernichtet und damit auch die Wirtschaft hier an dieser Straße zu den Feldern arbeitet ershardt mehr als acht Stunden am Tag sein Gehalt hat sich mangelskunden halbiert er bekommt umgerechnet nur 45 Euro pro Monat vor den Überschwemmungen haben wir täglich umgerechnet 40 Kilo Brot verkauft heute sind es in guten Tagen nicht mehr als fünf Lastwagen mit Getreide und Reis unterwegs die Fahrer und Reisende waren unsere Hauptkunden aber das ist vorbei mit meinen Kindern zu verbringen oder mit ihnen zu reden [Musik] früher war ich nicht so da habe ich Ihnen was zu Essen gemacht und ihn gegeben was sie wollten [Musik] das kann ich mir nicht mehr leisten sie wollen alles mögliche und ich weiß nicht was ich machen soll es ist deprimierend das Dorf ist verwüstet obwohl die Regierung finanzielle Entschädigung und Wiederaufbau versprochen hat haben die meisten Opfer bisher nicht mehr bekommen als warme Worte bis 2022 wurden hier täglich bis zu 1000 Tonnen Reis produziert 200 Dorfbewohner sind arbeitslos wir versuchen was zu machen aber wie Sie sehen wurde das Gebäude beschädigt sogar die Mauern sind eingestürzt dieser Betrieb war ein Segen für uns als weniger Gäste ins Restaurant kam habe ich hier zusätzlich gearbeitet unsere Häuser wurden beschädigt und jetzt fehlen uns die Mittel um das Problem zu beheben in dieser Mühle wurde die Spreu vom Reiskorn getrennt sie ist schwer beschädigt alles ist verrostet alle Maschinen wurden zerstört die Mühle stand monatelang unter Wasser das kann man alles wegwerfen soll in Pakistan gibt es kaum Versicherungen für solche Schäden 2010 wurde dieser Betrieb schon mal durch Überschwemmungen zerstört das gesamte Gebäude und die Maschinen wir haben sechs Jahre gebraucht um alles wieder aufzubauen 2022 gab es erneut Überschwemmungen jetzt fragen wir uns sollen wir wieder alles aufbauen wer garantiert uns das ist keine weiteren Überschwemmungen mehr gibt und dass ich diese Situation nicht wiederholt gegen den Klimawandel kann man nichts machen bestenfalls bauen wir ein Schutzwall um den Betrieb aber was nützt der Betrieb überhaupt wenn die Reisfelder zerstört sind er wird weiterhin geschlossen bleiben wieder aufbauen oder irgendwo anders ein besseres Leben finden einige Studien schätzen dass der Klimawandel in Pakistan bis 2050 gut 2 Millionen Menschen im Land vertreiben wird [Musik]</t>
+  </si>
+  <si>
+    <t>[Musik] NachDenkSeiten die kritische website Stimmen aus der Ukraine wie Kiew jeden Kritiker zum staatsverräter erklärt ein Artikel von Maxim Golda in letzter Zeit lesen bzw hören wie oft in den ukrainischen Nachrichten oder im Fernsehen von sogenannten staatsverrätern die vom ukrainischen Sicherheitsdienst oder den Staatsanwälten enttarnt wurden und staatsfeindliche Aktivitäten sowie des Verrates verdächtigt werden in der Regel handelt es sich bei den sogenannten Verrätern um bekannte Persönlichkeiten des öffentlichen Lebens oder Politiker welche die Politik der Regierung kritisieren sich für Frieden aussprechen oder korrupte Machenschaften des derzeitigen Regimes aufdecken viel weniger bekannt sind jedoch die zahlreichen Fälle in denen normale Bürger wegen absolut geringfügiger Vergehen ebenso als Verräter gebrandmarkt werden regierungskritische Beiträge in sozialen Netzwerken oder auch nur ein Like auf Facebook reichen aus ein Einblick in die Mechanismen des Kiefer Unterdrückungsapparates die Behörden verfolgen dabei mehrere Ziele erstens die Aufmerksamkeit der Ukrainer von ihren eigenen Fehlkalkulationen Fehlern Verbrechen und Versäumnissen abzulenken zweitens Aufbau des Bildes von sogenannten volksfeinden drittens die strafrechtliche Verfolgung von politischen Gegnern und Konkurrenten und viertens Schaffung und Pflege einer allumfassenden Atmosphäre der Angst des gegenseitigen Misstrauens und des Hasses in der ukrainischen Gesellschaft der Verwirklichung des Prinzips teile und herrsche die Punkte 1 2 und 4 zielen auf das Erzielen psychologischer Ergebnisse ab wie zum Beispiel die massenhafte Täuschung der Gesellschaft die diese in den Abgrund der Angst und Misstrauen stürzt und die Aufmerksamkeit von der Realität ablenkt Punkt 3 ermöglicht es mit Gegnern der Obrigkeit umzugehen sie von der politischen Ebene zu entfernen Sie im Gefängnisse zu werfen sie zu verstümmeln oder sogar zu töten sie zu verfolgen Ihnen Ihr Eigentum und ihre Geschäfte wegzunehmen die Uneingeweihten stellen sich zweifellos eine Frage warum werden Gegner der Behörden und andere Personen oft unter genau diesem Artikel des Strafgesetzbuches und der genau diesen Verbrechen Hochverrat angeklagt die Antwort lautet wie folgt der Wortlaut des Straftatbestandes Hochverrat in Artikel 111 des Strafgesetzbuches der Ukraine ist sehr vage und abstrakt was dem Strafsystem die Möglichkeit gibt jeden zu belangen der vom Präsidenten oder seinem Team angezeigt wird ich möchte die Leser und Hörer daran erinnern dass die derzeitige Fassung dieser Bestimmung von Abgeordneten der Partei von Präsident selinski verfasst und angenommen wurde so dass es nicht verwunderlich ist dass sie genauso ausgefallen ist multilateral vage und je nach Aufgabe oder Anweisung von oben unterschiedlich auslegbar schließlich müssen sie zugeben dass die Formulierung eine Handlung die zum Nachteil der Souveränität der territorialen Integrität und Unverletzlichkeit der Verteidigungsfähigkeit der staatlichen wirtschaftlichen und informationellen Sicherheit der Ukraine begangen wurde beliebig ausgelegt werden kann und letztlich jeder unter diese Begriffe fallen kann das wichtigste und entscheidende ist wer heute in der Ukraine das Recht hat diese Worte anzuwenden auszulegen und zu bewerten offensichtlich sind dies nicht die Gerichte sondern die Sonderdienste und Staatsanwälte beide sind absolut abhängig und werden vom Präsidenten oder seinen Strukturen ernannt und abgesetzt nachdem er an die Macht gekommen war hat silensky alles getan um die Ernennung aller Leiter der Strafverfolgungsbehörden zu beeinflussen und seine Leute dort unterzubringen jetzt während des Krieges ist es ihm gelungen die gesamte Macht über die Justiz in der Ukraine in seinen Händen zu konzentrieren obwohl dies absolut im Widerspruch zu den Bestimmungen der ukrainischen Verfassung steht denn die Leitung der Ermittlungsbehörden GBI SPU Staatsanwaltschaft Polizei und BEB und das Justizwesens wird nun vollständig vom Präsidentenamt kontrolliert und ist ihm gegenüber rechenschaftspflichtig das heißt sie wird von ihm ernannt und abgesetzt darüber hinaus ist staatsverrat ein besonders schweres Verbrechen und die Sanktion des Artikels 111 sieht eine Freiheitsstrafe von bis zu 15 Jahren vor während der Strafprozess Recht die Festnahme eines Verdächtigen nach diesem Artikel ohne Recht auf Kaution und Freiheit zulässt zweifellos würde jeder vernünftiger Jurist aus einem demokratischen Land das über einen unabhängiges und relativ faires und unparteiisches Justizsystem verfügt die Frage stellen aber um die Schuld einer Person an einem so schweren Verbrechen zu beweisen braucht man eindeutige und unwiderlegbare Beweise die auf ausschließlich legale Weise gesammelt wurden wie zum Beispiel Materialien von operativen Maßnahmen zum Beispiel ab Hörgeräte Lesen von Korrespondenz Überwachung Video und Audioaufnahmen von Gesprächen treffen Aktionen physische Beweise qualitative agentenberichte und nur auf der Grundlage der Summe all dieser Beweismittel und ihrer umfassenden Bewertung vor Gericht wäre eine faire und objektive gerichtliche Entscheidung über die Schuld oder Unschuld des Angeklagten möglich und der Jurist hätte mit seinem Einwand vollkommen recht allerdings mit einer Einschränkung wir sprechen hier von der Ukraine im Jahr 2023 werte Leser Werte höhere in ihrem Rechtssystem ist es notwendig gründlich die Schuld einer Person vor einem Richter zu beweisen um ihn vor Gericht zu bringen in der Ukraine seit dem Beginn des Krieges gibt es dafür keine Notwendigkeit mehr in keiner Form man muss den Gegner der Behörden also die Opfer einfach nur festnehmen und in Gewahrsam nehmen und das ist alles weiter werden in der Haftanstalt unerträgliche Bedingungen geschaffen es wird gefoltert und gequält erpresst und missbraucht und er ist auf unbestimmte Zeit dort das ist auch heute der Fall die ganze Welt kennt die schreckliche Situation mit linken Aktivisten und Antifaschisten den Brüdern Alex dem Publizisten und Blogger Dimitris quarzow der Rechtsanwältin und Menschenrechtsaktivistin Elena berechner ja die für ihre antifaschistische Haltung bekannt ist und vielen anderen Personen des öffentlichen Lebens die sich aus der Opposition heraus zu Wort gemeldet haben Leser und Hörer werden einwenden aber es ist unmöglich einen Menschen zu ergreifen und hinter Gitter zu werfen indem man ihn eines der schwersten Verbrechen gegen das Land beschuldigt wie es die Gestapo einst in Nazi Deutschland Tat ohne irgendwelche zumindestens die geringsten Gründe und Begründungen es ist möglich heute in der Ukraine ist es möglich aber um der andauernden Gesetzlosigkeit und Rechtlosigkeit wenigstens den Anschein einer gewissen Legitimität zu geben haben die Strafverfolgungsbehörden SPI und Staatsanwaltschaft gelernt und jetzt geben sie acht die Worte und Äußerungen einer Person ihre Kommentare und Beiträge in den sozialen Netzwerken von sogenannten Experten überprüfen zu lassen zu diesem Zweck nehmen die Beamten der Staatsanwaltschaft die Worte eines jeden Gegners der derzeitigen Regierung sei es ein Post in sozialen Netzwerken eine Rede im Fernsehen oder ein Artikel in der Zeitung und nennen und führen eine spezielle forensische linguistische Untersuchung durch bei der entsprachexperte die Fragen beantwortet die ihm im Rahmen der Untersuchung gestellt werden erstens steckt in diesen Worten etwas Schlechtes gegen die Ukraine zweitens gibt es irgendetwas was darauf hinweist dass die Person indirekt oder direkt den Feind unterstützt und drittens stehen diese Wörter in einem kausalen Zusammenhang mit irgendwelchen folgen und so weiter und so fort wie Sie wissen kann schlecht jedes Wort jede Position jede Aussage genannt werden denn es handelt sich um eine äußerst relative und bewährende Arbeit eine äußerst subjektive Wahrnehmung die von einem forensischen Sachverständigen vorgenommen wird und das Hauptproblem in einem solchen Fall ist es den richtigen Experten zu finden der die Worte des Opfers des Regimes richtig bewertet und das richtige Gutachten schreibt woher kommt dieses Fachwissen wie wird dieses Fachwissen formalisiert und hier ist das interessante für diejenigen die die Arbeit des derzeitigen Systems der Verfolgung an das Denken der in der Ukraine nicht kennen ein Teil des Gutachtens kann in staatlichen Institutionen für forensische Gutachten erstellt werden wo der Sachverständige vom Institutsleiter einen Auftrag erhält den er erfüllt und das notwendige schreibt da die Experten in der Ukraine derzeit keine Verantwortung tragen können Sie schreiben was sie wollen darüber hinaus gibt es einfach speziell geschaffene also ernannte Sachverständige denen das staatliche verfolgungssystem geholfen hat die erforderliche Lizenz des ukrainischen Justizministeriums zu erhalten welche es Ihnen erlaubt sprachliche Prüfungen durchzuführen sie werden vom staatlichen verfolgungssystem unterhalten und bekommen gute Honorare für die Sie einfach die vom System geforderten Gutachten abstempeln wenn sie ein schlechtes Gutachten brauchen schreiben sie ein schlechtes wenn Sie ein gutes brauchen schreiben Sie ein gutes die Schlussfolgerungen des Gutachtens dienen dann als Basis für die Strafverfolgung und werden zur Grundlage für die Verfolgung einer Person Verdächtigung Fahndung Festnahme Verhaftung Inhaftierung und so weiter in den letzten anderthalb Jahren wurden in der Ukraine mehr als 1.500 Strafverfahren unter dem Artikel Hochverrat eingeleitet das heißt im Durchschnitt werden jeden Tag zwei oder drei Strafverfahren unter diesem Artikel eingeleitet lassen Sie mich noch einmal wiederholen die Schlussfolgerungen der Ermittlungsbehörde im Einklang mit dem Gesetz haben für das Gericht keine Bedeutung und sind kein Beweis für die Schuld einer Person solange der Fall vor Gericht verhandelt wird spielen keine Beweise eine Rolle sondern nur alle Beweise die vor Gericht erhoben oder vom Richter während des Prozesses untersucht wurden damit aber der Verdacht besteht dass eine Straftat begangen wurde musste ermittlungs- bzw Strafverfolgungsbehörde zumindestens einige Daten sammeln die irgendwie darauf hindeuten dass die Meinung der ermittlungs- bzw Strafverfolgungsbehörde über die Schuld einer Person richtig ist genau aus diesem Grund sind solche bewusst falschen Gutachten über angeblich staatsfeindliche Äußerungen einer Person erforderlich das bedeutet keineswegs dass Menschen verurteilt oder verschuldigt befunden werden im Gegenteil ein normales Gericht würde sie für unschuldig und ihre Schuld unbewiesen halten aber das wird offensichtlich nicht so bald passieren sondern erst wenn das derzeitige Regime wechselt wer von den politischen Gefangenen dies erleben wird ist leider eine rhetorische Frage sind Informationen über den Frieden und für den Frieden anti-ukrainische Informationen für die derzeitige Regierung die in Anführungszeichen Kriegspartei diejenigen die wollen dass der Krieg weitergeht die damit Geld verdienen oder ihren politischen Lebenszyklus verlängern ja sie erklären Menschen zu Feinden und Verrätern am Vaterland das Regime tut dies mit Hilfe von Mitarbeitern der Sonderdienste Staatsanwälten Ermittlern und Richtern und gibt ihnen entsprechende Anweisungen aber fragen sie sich die oben genannten die diese illegalen kriminellen Anweisungen ausführen was werden sie dann tun wenn die Macht im Lande wechselt es ist unwahrscheinlich dass es vielen von ihnen gelingen wird aus der Ukraine zu fliehen und das ist unwahrscheinlich dass irgendein zivilisiertes Land den Tätern Hilfe und Unterschlupfen wird ich hoffe diejenigen denken darüber nach bevor Sie einen weiteren Strafbefehl ausführen Quellenangaben und weiterführende Verlinkungen finden Sie auf www nachdenkseiten.de oder im Beschreibungstext unter dem youtube-podcast [Musik] dieses Audio konnte nur entstehen weil zahlreiche Leser und Leserinnen die NachDenkSeiten fördern und durch Spenden unterstützen wenn sie auch etwas tun wollen klicken Sie einfach den entsprechenden Button auf unserer Website an übrigens sie können uns auch bei iTunes Soundcloud und Youtube hören und wenn Sie mögen gerne unseren Kanal abonnieren und eine positive Bewertung für uns abgeben wir freuen uns über Ihre Unterstützung und die Weiterverbreitung unserer Inhalte [Musik]</t>
+  </si>
+  <si>
+    <t>6eA4xSaYSos</t>
+  </si>
+  <si>
+    <t>jeder Schritt zählt jeder einzelne Schritt hin zum eigenen Selbst zur Selbstentdeckung selbst Entwicklung sich selber überhaupt erstmal zu spüren ist ein Schritt wenn man es mal bildlich sieht aus dem ganz tiefen dunkel in das eigene Licht und das ist großartig also ich hatte so viele Licht Erlebnisse in diesen 20 Jahren und ich habe das recht schnell geschafft weil ich diese Mission in mir gefühlt habe okay ich bin unter anderem auf der Erde um den Menschen diese unendliche Liebe und Kraft der Engel nahezubringen damit sie eine gute Stabilität im Leben haben damit sie wissen dass göttliche beschützt mich es fällt mir den Raum ich kann mich darin beschützen und geborgen fühlen das war der Start und dadurch dass ich das mit so viel Hingabe und Liebe auch mit Zweifeln gemacht habe aber eben trotzdem gesagt hat okay ich stelle mich zur Verfügung ich gebe mich diesen Prozess hin kamen die Menschen auf mich zu ich bin einerseits auf die Menschen zugegangen ich hatte so eine schöne kleine Geschichte ich habe in Leverkusen gewohnt und ja Rheinland Deutschland und da gab es einen ganz süßes kleines esoterikgeschäft es waren vor 20 Jahren ja da gab es halt nix also heute ist Überfluss da an spirituellen Infos damals nicht aber dieses bezaubernde Geschäft hat eben eine tolle Besitzerin gehabt und dann bin ich ganz vorsichtig in dieses Geschäft rein mit meiner kleinen Mappe ich habe wie wild Engel gemalt nach dieser Begegnung dich hatte und habe ganz ganz viele Botschaften bekommen habe die alle aufgeschrieben und dann bin ich zu ihr gegangen dazu darf ich Ihnen mal meine Dinge zeigen die ich hier gerade erlebe haben Sie eine Idee was ich machen kann und die war wirklich ja also ich nicht aus dem Ego sondern weil es so war sie war überwältigt sie kannte das so nicht dass da jemand zu ihr kommt und ihr diese Bilder zeigt und diese Freude daran hat dann hat sie ganz spontan gesagt wir machen eine Ausstellung hier ja wir müssen überlegen wie wir das hier sinnvoll tun können dann lade ich die Leute ein und das war der Start ich habe mich getraut das zu zeigen ich fand es total spooky zu dem Zeitpunkt also es war noch so oh Gott ja ich glaube das muss keinem erzählen das hätte wirklich Angst dass sie dann zum Beispiel die die Psychiatrie anruft und da kommen die Leute mit der weißen Jacke und bringen mich da rein aber ich habe mich trotzdem getraut und das war dieses tiefe wissen es ist wichtig ich will das machen ich muss nicht aber ich will das machen und ich habe Unterstützung von den Engeln von Gott und dann fing es an zu fließen und jeder Schritt dahin war ein Schritt aus meiner Krankheit heraus aus meiner Depression heraus ich habe gesehen oh da gibt es Menschen die lassen sich von mir ein persönliches Engelbild malen und bezahlen Geld dafür sind wenn sie es bekommen so berührt dass ihm die Tränen runterlaufen sie mich umarmen diese dankbar sind mein Leben bekam einen Sinn ja und das war das größte größte Geschenk das ich mir machen konnte also jeder Schritt in diesen 20 Jahren war wichtig wundervoll</t>
+  </si>
+  <si>
+    <t>für die wesentlichen Wesen hier das ist auch mit Lesen angesprochen und das gebe ich später noch drauf ein ist alles offensichtlich das heißt wir Menschen können uns verbergen füreinander aber alles darüber unsterblichen Welt sieht ja eh alles und wenn wir nachher aus diesem Leben rausgehen dann sind wir ja auch wieder nackt dann wisst euch ist alles sichtbar und dann sehen wir ja selber und eigenen Fehler also im Grunde ist die Idee dass wir uns verstecken können der eigentliche Lüge wir können uns ja gar nicht verstecken nur temporär vielleicht aber letzten Endes ist ja alles offensichtlich ja und mir fehlt noch ein bisschen länger machen für alle anderen die jetzt glauben nur die geistigen Wesen können das sehen es gibt ganz viele Menschen die auch unter uns sind die den Durchblick haben und nach unseren Kursen zum Beispiel hat jeder den Durchblick den der Begriffe hat was für Spirit meint macht der der wirklich Freude an der Konfrontation hat und am eintauchen und dann wirklich ein transformieren der wird wieder klare Sicht haben oder das ist klar dass ich nach außen ja was ich auf dem Weg nach innen entwickelt ist eben diese Wertschätzung und diese Liebe und dieses Verständnis dieses Mitgefühl welches dann wenn man nach außen auch klar schauen kann eben Gott sei Dank da ist ja man hat mit jedem Mitgefühl ob man will oder nicht ob ein Arsch ist oder nicht ist nebensächlich und es gibt also es gibt viele die dich jetzt schon durchschauen aber nicht sagen ja du kannst es aber spüren jene die dich durchschauen sind in der Regel nicht jene die dich beruhigen jene dich beruhigen möchten Dich einschläfern weil sie Angst haben was du bei ihnen finden könntest ja geh also lieber zu Leuten die ein bisschen Furore machen als bei den anderen auch wenn das andere still und Weise und gurehaft erscheinen mag er scheint trügt ja geh dorthin wo es dir unangenehm ist weil du Angst hast weil Gott hinter dieser Angst versteckt sich das was du wirklich bist und wenn da einer ist der dir davor Angst machen kann dann ist es auch der der dabei helfen kann diese Angst zu überwinden ja weil wer sie selbst überwunden hat fürchtet sich nicht vor den Ängsten anderer vor der Wut anderer wenn du einen wirklich echten spirituellen spirituellen Lehrer hast dann kommt der Moment an dem du auf ihn sauer werden wirst und dort klären sich die meisten wieder ab weil es wird sortiert je näher wir dem Feuer kommen desto heißer wird es und wenn wir nicht Hitze geprüft sind macht es keinen Sinn ins Feuer zu gehen das wäre Leichtsinn und wer zu leichtsinnig daherkommt wird einfach wieder ins Leben zurückgeschickt bis er nicht mehr so leichtsinnig ist dann kommt er wieder und er wird auch nicht abgelehnt ja aber es ist wichtig dass wir wissen es geht nicht darum dass wir gut sind sondern dass wir bereit sind ja ich kämpfe ein Leben lang schon drum gut genug zu sein für den lieben Gott und ich habe noch nie das Gefühl gehabt ich bin wirklich gut genug aber die Frage bin ich bereit kann ich mit einem klaren Ja beantworten ich bin bereit mich hinzugeben das ist in meinen Augen die leere Jesu gewesen die Hingabe die Liebe klar aber auch die Gerechtigkeit ja wenn man die Gerechtigkeit nicht fürchtet kann dann kann man sich der Liebe hingeben um das ganze Interview kostenfrei weiter zu schauen Besuche einfach diese Website an frieden.de oder klicke auf den Link in der Beschreibung</t>
+  </si>
+  <si>
+    <t>243Ua1VJ04k</t>
+  </si>
+  <si>
+    <t>6qKkSqe9bls</t>
+  </si>
+  <si>
+    <t>die Kinder werden immer cooler die wollen sich ja voreinander nicht die Blöße geben sie wollen ja gegenseitig sozusagen sich übertrumpfen und cool sein da kann man sich nicht verletzlich zeigen das heißt man fliegt vor seinen eigenen Gefühlen die man vielleicht auch hat dann sind die Kinder und das ist das große Problem der heutigen Pädagogen sie sind immer schwieriger zu unterrichten das heißt Erziehung und unterrichtbarkeit wird immer schwieriger für Kinder weil die die nicht mehr zuhören weil die zu den Kindern keine Bindung hat hast du zu deinem Kind umgekehrt eine super gute Bindung es ist es Erziehung ist es macht nebenbei das ist auch kein Problem und unterrichtsbarkeit genauso aber wenn das Kind unreif ist weil es aufgrund von diesen traumatischen Erlebnissen sozusagen fest in dieser unreife steckt ähm und dann eben nicht auf Erwachsene sich bindet sondern auf Gleichaltrige dann wird es sehr schwer für die erwachsen weil die Störfaktoren wenn der Lehrer sagt ja ihr müsst jetzt das Lernen dann sagte sich das Kind innerlich nee von dir höre ich mir nichts an du bist ja nicht der auf den ich mich jetzt hier sozusagen eingeschlossen habe das heißt wir haben es heute mit viel geleiteten bindungsinstinkten zu tun ein Unverständnis darüber dass Kinder diese Instinkte haben oder Bindung brauchen in unser heutigen Gesellschaft und dass diese Instinkte immer wirken nur sie haben sich sozusagen die falsche Richtung orientierte beziehungsweise auch die falschen Bezugsperson nämlich andere unreife von den kannst du nichts lernen das ist ja immer und daraus entstehen dann später auch die sogenannten Tyrannen Opfer Konstellation das ist Kinder gibt die sind körperlich vielleicht schon stärker und aggressiver und die setzen sich gegen Schwächere durch ja und behaupten sich auf diese Art und Weise wenn die anderen die schwächeren wieder traumatisiert das Kind das andere das ist dann auf verhaltensauffällig alle sagen oh Gott oh Gott ein verhaltensauffälliges Kind das ist so aggressiv das können sie tun und so weiter alle Schreiner wieder auf verstehen aber nicht dass der Kontext in dem dieses Kind sich so verhält entscheidend ist daraus entsteht aber auch ein weiteres Problem nämlich Drogenkonsum Alkoholismus Pornografie Gaming und gerade jetzt zu beobachten verfrühte Sexualität gerade auch bei Mädchen in Kombination mit entsprechenden sexueller Perversion und die digitalen Medien haben dazu enorm beigetragen dass nicht nur der Porno Konsum gestiegen ist sondern dass eben auch ja die Kinder sich gegenseitig mit mit Abartigkeit und Perversionen und wer am besten mit wem schon was rumgemacht hat oder wer ganz viel Alkohol konsumieren kann und kiffen kann und so weiter sich gegenseitig übertrumpfen oder schlimmer noch wenn wenn Kinder sich gegenseitig verprügeln das Filmen ja das sind alles so Auswüchse von dieser Subkultur von dieser unreifen Kinder und Jugendkultur die in Folge von dieser Gleichaltrigen Orientierung entstanden ist die wieder nur die Folge von Bindungslosigkeit entstanden ist die wiederum die Folge von frühkindlichen traumatischen Erlebnissen ist um das ganze Interview kostenfrei weiter zu schauen Besuche einfach diese Website an frieden.de oder klicke auf den Link in der Beschreibung</t>
+  </si>
+  <si>
+    <t>nUcRCaHqFho</t>
+  </si>
+  <si>
+    <t>hwtez66l_2I</t>
+  </si>
+  <si>
+    <t>BKDHflRipyc</t>
+  </si>
+  <si>
+    <t>wpJByIviXWU</t>
+  </si>
+  <si>
+    <t>ich bin 46 intensiv Krankenschwester und seit 20 Jahren im Beruf ich habe gefälscht weil ich meinen Beruf sonst nicht mehr ausüben hätte können nach dem ersten Todesfällen von nastassinica wurde es mir immer unheimlicher durch die Tröpfcheninfektion schützt mich keine Impfung vor der Weitergabe ich bin bis zu dem Zeitpunkt bin ich nie straffällig geworden und da hat man eine Grenze überschritten ist ja davor da wurden wir noch beklatscht und gefeiert weil wir in der Pflege doch so wichtig sind und das Jahr darauf wirst du nötig eine Straftat zu tun wir sind eine Ecke gedrängt und gezwungen zu einer Impfung die mir als als als Junge relativ junger Mensch mir wahrscheinlich nichts bringt ich arbeite in der Gastronomie als wird ich habe gefälscht weil ich keine neue artigen Impfstoff an mir ausprobiert haben wollte ich habe gefälscht weil ich Angst vor einem neuart Impfstoff hatte ich hätte sonst nicht mehr arbeiten dürfen ich habe mich gewundert dass mitten in einer Pandemie eine neue nicht erprobte Technologie ausprobiert wird und nicht auf bewährte Technologien zurückgegriffen wird das hat mich stutzig gemacht ich hatte im Vorfeld die Dokumentation auf Arte zu Schweinegrippe Vogelgrippe gesehen die Profiteure der Angst hieß und was mich stutzig gemacht hat war eben dass es dieselben Akteure waren ich wusste dass zum Beispiel der Impfstoffhersteller Feiser eine der größten Strafzahlungen in der Geschichte überhaupt des Gesundheitswesens zahlen musste für mich waren diese ganzen Institutionen einfach nicht vertrauenswürdig wenn die Polizei gekommen ist um zu kontrollieren ob ein Gast da ist der ungeimpft ist bin ich derjenige gewesen der die Strafe bekommt hätte ich habe eine Aufgabe bekommen vom Staat mit der ich eigentlich nichts zu tun habe ich war eine Kontrollinstanz das war entsetzlich ich wollte das nicht wissen ob die Leute geimpft sind oder nicht ich wollte das machen was ich immer gemacht habe jeden willkommen heißen der zu mir kommen möchte ich bin Gastgeber ich bin kein Kontrolleur fand ich furchtbar einfach auch ein Verrat an mir selber</t>
+  </si>
+  <si>
+    <t>DtQ59rRANcY</t>
+  </si>
+  <si>
+    <t>mein legendärer Schlagabtausch mit dem deutschen Jim Kraemer Marcel Fratscher bei Illner im ZDF hat schon jetzt über eine Million Aufrufe auf Youtube und heute möchte ich mir mal die Aussagen von damals kritisch anschauen auch selbstkritisch natürlich um zu schauen wer lag richtig wie habe ich performt wie sah ich aus saßen die Haare war ich gut rasiert und so weiter mit euch heute in einem neuen reaction Video und damit herzlich willkommen zu einer neuen Folge finanzielle Intelligenz mein Name ist Mark Friedrich und Partner Vermögenssicherung ich war damals geladen weil mein vorletztes Buch der größte Crash aller Zeiten wochenlang auf der Spiegel Bestsellerliste stand und es war leider wie so oft drei gegen ein ich war sozusagen derjenige der dann die ganze Tasche abbekommen hat und meine Thesen wurden natürlich kritisch begutachtet schauen wir uns mal die Argumente an von Elena und Co das was Kriminelle aus Sachsens Schatzkammer dem Grünen Gewölbe gestohlen haben ist in seinem Wert nicht nur unbezahlbar es ist krisenfest Sachwerte sein das einzige was einen Finanzcrash überstehen würde sagt unser Gast Mark Friedrich und der Crash der kommt Friedrich legt sich fest spätestens 2023 ist es soweit Börsencrash über Inflation der Zusammenbruch des Euro die Finanzkrise 2018 dagegen nicht mehr als eine leichte Brise gewesen wir sagen den sparen und sparen dass ihre Einlagen sicher sind auch dafür steht die Bundesregierung ein ein solches Versprechen zieht dann wohl nicht mehr wohin also mit dem Ersparten der Rad von Mark Friedrich Oldtimer steigen im großen Kunstwerke ebenfalls Land geht immer Feld Wald und Whisky das gute Zeug verstehen sich flüssig bleiben garantiert ja schauen wir uns mal die Aussagen an Whisky war definitiv eine sehr gute Entscheidung weil wir hatten im Schnitt 58% Wertsteigerung auch Immobilien sind damals noch gestiegen bis 2022 damals habe ich dann vor einem Jahr ein Video gemacht um zu sagen achtung die Immobilienblase die wird jetzt bald platzen das Video findet ihr wahrscheinlich hier oben sehenswert und immer noch aktuell Kunstwerke Oldtimer auch die liefen noch relativ gut dann jetzt auch nicht mehr da würde ich jetzt auch eher vorsichtig sein leider wurde im Video nicht erwähnt Gold Bitcoin oder auch Diamanten oder auch natürlich Rohstoff Aktien die ich ja auch immer empfohlen habe jetzt natürlich die große Frage der Finanzkrise bis 2023 ist ja schon da oftmals oder gesagt ach der ist doch gar nicht gekommen naja ich sehe das ein bisschen anders natürlich wir hatten eine Corona crascht das war aber nicht den ich gemeint habe und ich habe ja auch nicht gesagt dass es nur ein Börsencrash ist sondern es geht wirklich um einen großen Crash um ein System Crash um diese Zeiten meinte den Paradigmenwechsel über den ich ja immer wieder spreche und ja der Euro besteht bis heute immer noch aber natürlich muss man auch in respektive sagen wir haben natürlich jetzt eine hohe Inflation noch keine hyperin Aktion aber eine Inflation die höchste in den letzten 40 Jahren und seit Einführung des Euros hat der Euro definitiv offiziell schon laut Statistischen Bundesamt 35% an Kaufkraft verloren inoffiziell das wissen wir alle hat der Euro natürlich weit mehr verloren wenn wir da mal gegen Werte dagegenstellen gegenüber Gold über 90 Prozent gegenüber Immobilien ebenfalls oder natürlich gegenüber Bitcoin 99,99% Wertverlust das sind wir schon in der Hyperinflation also würde ich mal sagen die Antwort ist jein ich bin teilweise regelig richtig teilweise nein würde der Euro noch in die Länge gezogen werden die EZB und Notenbanken noch länger sozusagen gutes Geld schlechten Geld hinterherwerfen und Gesetze brechen um den Euro zu retten ja natürlich definitiv und der nächste scam ist ja schon vorbereitet mit dem cbdc dem digitalen Euro um dem ponsis geben dem Pferd betrug System noch ein bisschen Leben einzuhauchen um ihn auf die nächste Ebene zu hießen versucht man jetzt die lebenslängende Maßnahme dass man die digitalen Euro einführt und dann gibt's auch kein Banken ran mehr keine Möglichkeit mehr die auch die fluchttüre aus dem jetzigen Geldsystem zu finden dann sind die Türen verschlossen also dahingehend kritisch muss man sagen tatsächlich der der größte Crash aller Zeiten der Börse ist nicht gekommen aber natürlich der Systemcrash ist definitiv da und den habe ich ja auch mit unter anderem gemeint schaut raus was passiert in den letzten Jahren wir sehen Krieg in Europa wir sehen eine Inflation die höchste seit 40 Jahren wir sehen weiterhin ausufern der Schulden die Staatsschulden Deutschland sind auf einem Rekordniveau auch in den USA steigen die Schulden immer weiter und nach wie vor bleibe ich meine Aussage treu die Frage ist nicht ob sondern lediglich wann dann das ganze System kippt und ich persönlich denke wir sind mittendrin statt davor aber lass mich mal wissen wie eure Meinung dazu ist schauen wir weiter Herr Friedrich Aktien Wald Streuobstwiesen und sogar Whisky das ist ihr Ernst ja Gold mit ja also da wird schon mal eine Frage gestellt oder vielmehr Frau Illner sagt zu meinem Subtext praktisch dem Zuschauer nehmen sie nicht voll den Herrn Friedrich der hat ja keine Ahnung ne also Gold hat zum Beispiel seit 2001 gegenüber dem Euro sich vor fünffacht also war auf jeden Fall ein guter Wertspeicher und ist seit jeher inflationsgeschützen seit jeher ein wertvoller Wertspeicher in Krisenzeiten aus dem Grund haben ja die Notenbanken weltweit in den letzten Jahren rekordmengen an Gold aufgekauft um ihre Kaufkraft zu schützen gegenüber der Entwertung und der Entwertung dem Kaufkraftverlust vorzubeugen und auch die Deutsche Bundesbank übrigens und die EZB gehören zu den größten Goldbesitzern weltweit umso mehr braucht man Gegengewicht eine Art Lebensversicherung gegen diesen Wahnsinn wenn noch nie wurde eine Krise durch Geld drucken gelöst und noch nie wurde Wohlstand durch Gelddrucken gelöst das haben wir in 20er Jahren in Deutschland versucht irgendwie seit den 70er Jahren ja also man lässt mich gar nicht erst aus wenn ich jetzt ungefähr 22 Sekunden Redezeit dann kommt schon die erste Grätsche und man merkt ja auch schon ähm die Herrschaften außer Frau Wagenknecht waren er natürlich gegen mich gestellt ne gegen mich gebürstet hat mir auch gleich noch einen weiteren Verlauf sehen aber man hat natürlich wenig Chancen seine Argumente ausführlich zu erklären ja aber du musst dir eines der reichsten Länder der Welt sein aber die haben 100 Millionen Dollar schein also man kann nicht Wohlstand erzeugen durch Geld drucken die Notenbank wird als nächstes nicht nur die Zinsen negativbereich denken nein die wird auch noch Aktien kaufen mit den aufkaufen und die werden auch noch Helikopter Geld verteilen das heißt sie werden alle noch hier Geld bekommen 5 oder 10.000 €, also wir sind im Endspiel monetären Endspiel wir sehen einfach eine verzweifelte Straßenbahn wir werden auch nie wieder steigende Zinsen im Eurosystem erleben und ganz im da lege ich falsch tatsächlich das habe ich falsch prognostiziert nämlich bis zur corona-krise war das tatsächlich der Fall aber seit 2022 sehen wir ja steigende Zinsen aber die Mathematik ist nach wie vor eigentlich gegeben weil steigende Zinsen bedeuten natürlich dass die Länder vor allem im Süden Europas immer mehr die Bredouille geraten was ich da nicht mit berücksichtigt hatte war natürlich dass die EZB weiterhin Gesetze bricht und weiterhin Staatsanleihen aufkauft obwohl es gar nicht dürfte also ohne die EZB das müssen wir uns klar sein deswegen ist es auch wieder so fifty fifty ich lag eigentlich richtig aber wiederum nicht weil keiner hätte sich ähm ja vorstellen können dass die EZB geltendes Gesetz bricht kaufen Sie einfach Staatsanleihen von Italien ohne die EZB mehr südamer schon längst bankrott und werde Euro schon sehen übrigens ich war auch 2010 11 mal bei einer Sendung klappt bei Phoenix mit Hans Werner sind und auch mit Peer Steinbrück und damals haben auch alle waren der festen Überzeugung dass der Euro die Binzen geht also war wirklich eigentlich hinter der Kamera was klar und im Nachhinein habe ich dann mit hans Werner Sinn mal gesprochen vor zwei drei Jahren nächstes Jahr er hätte sich auch nicht vorstellen können dass die Politik geltendes Gesetz bricht dass die EZB im Mandat massivst ausweitet sogar über die mandatsgrenzen hinaus und deswegen waren lagen alle falsch damals mit dem mit dem Crash des Euros und des ganzen Systems also weil man nicht sich deshalb vorstellen können dass wirklich alles in die Waagschale geworfen wird dass sie verzweifung so groß ist das von oberster Stelle gesetzt sind gebrochen werden negativbereich abbrauschen und das was nicht funktioniert sehen wir ja anhand dessen dass sie nur grins hier schon ein bisschen hat schon ein paar Argumente auf der Zunge fakt ist tatsächlich die Zinsen waren bei 0 sind lange bei 0% geblieben auch das hatte ich im vorletzten Buch prognostiziert in den Minusbereich sind wir nicht gekommen wird es noch kommen ich gehe davon aus warum wir werden auf jeden Fall jetzt eine zweite Inflationswelle sehen das heißt dann werden die inflationswerte wieder steigen dann wird die Notenbank wieder die Zinsen weiter erhöhen müssen und dann wird das Problem aber so groß werden dass man rasant die Zinsen senken muss um die Wirtschaft anzukurbeln um dann wieder das System in Gang zu bringen weil dann schwenkt das Pendel einfach von der einen extrem in die andere extreme und die großen turbulenten volatilen Bewegungen die werden mir meine Ansicht nach den kommenden Jahren sehen inklusive tatsächlich Inflation und sogar Staatsmann konnte in der Eurozone jetzt schon wieder ein Aufkaufprogramm gestartet hat mit 20 Milliarden Euro im Monat wo weitere zombieunternehmen künstlich an dem Leben erhalten bleiben die Bank of international settlemen die Notenbank der Notenbank geht davon aus dass in der Eurozone 15% alle Unternehmen zombie-unternehmen sind das heißt die gibt es nur noch weil die Zinsen so niedrig sind und weil diese Aussage stimmt und da lag ich auch den absolut richtig warum weil wir sehen wir ja auf einmal die Insolvenzquoten nach oben schnellen also Unternehmen in ganz Europa in Deutschland gehen auf einmal Bankrott weil die Zinsen stark steigen weil die sind nicht mehr zum nullzins Verschulden können also diese Aussage ist absolut richtig das sind wir nicht nur in der Eurozone sondern auch in den USA wo wir jetzt die stärkste Insolvenzquote seit über 10 Jahren haben weil die steigenden Zinsen machen nicht nur den Schuldenländern zu schaffen sondern natürlich auch den Unternehmen die schlecht kapitalisiert sind und die sich jetzt nicht mehr verschulden können zu 0% und jetzt kommt praktisch die Problematik ans Tageslicht die Jahre lang mit historisch tiefen Zinsen überdeckt wurde künstlich am Leben erhalten auf diese 2.23 super spät spätestens und woher haben sie diese Gewissheit also warum spätestens in vier Jahren das sind so viele Indikatoren erstens die südlichen Länder Europas müssen sich in den nächsten Jahren mit hunderten Milliarden an Staatsanleihen refinanzieren da ist die Frage der kauft die noch außer der EZB ja parallel haben wir jetzt schon die Banken und die Versicherung die Werte gibt es ein großes bankenversicherung sterben bei der nullzins und der Negativzins die Bilanzen und die Gewinne konnte wir sehen die Aktien kostet Deutsche Bank die müssen verstaatlicht werden weil spätestens gut Commerzbank wurde ja verstanden fakt ist natürlich dass wir auch Versicherungen gesehen haben die liquidiert wurden sind die aufgefangen wurden sind die gerettet worden sind wir sahen dass die Banken in die geraten sind nicht nur die Kredits auch viele andere Banken natürlich also da liegt auch natürlich ein kann der Wahrheit wo ich jetzt nicht richtig lag war natürlich dass die Notenbanken die Staatsanleihen alle aufgekauft haben dass man wirklich mehr Staatsanleihen aufgekocht hat auch durch Tricks natürlich ja durch neue Programme und das verschleiert hat um die weitere Quote zu erhöhen weil es gibt ja eine Grenze bei den qu wie viel Staatsanleihen die EZB kaufen darf aber man hat einfach wieder eine Trickkiste gegriffen und hat so das schön und charmant umgangen so dass wir jetzt natürlich dass die EZB größter Gläubiger der ganzen Länder ist vor allem in Südeuropa und weiterhin kräftig Staatsanleihen aufkauft ansonsten wäre das ganze schon längst über den Jordan gegangen es war Jahren werden die umkippen müssen da musste stark wieder eingreifen wir dürfen wieder Garantien vergeben weil die einfach nicht mehr wettbewerbsfähig sind also ein großes bankenversicherung sterben wird kommen dann haben wir die ganzen Problem mit den Negativzinsen wir haben 2,6 Billionen Euro durch die aufkaufprogramme der EZB ins System gepumpt für die wir alle haften also die riesigen steigen vor allem für die deutschen weil wir haben den größten Anteil über die Bundesbank an der EZB also sind so viele Indikatoren parallel werden aus ihrer Sicht ja gib mal ganz kurz weiter an Herrn also Zusammenbruch vor allen Dingen ausgelöst eben Euro-Raum ist da für sie irgendetwas jetzt kommt an der Argumentation nein das ist eine Schwäche von Metall rein kretscht dass ich ihn ja ich wusste einfach gleich was er sagt ne und da war ich dann einfach so getriggert und ich hatte auch schon gemerkt wie natürlich die Stimmung gegen mich war schon im Gespräch davor oder da gibt es so ein Gästeraum ne das hatte ich dann abgesondert ja Sarah kann leider ganz ganz spät deswegen seid ihr wirklich alleine und ähm es war ja eine komische Stimmung einfach also man hat schon gemerkt dass da ein bisschen Feindseligkeiten sind fakt ist aber ähm seine Argumentation die jetzt kommt ist natürlich schwach und zeigt halt einfach dass er keine Gegenargumente liefern konnte und auch hier wiederum Frau in hat jetzt nicht meine ganze Argumentationskette zu hören bekommen aber klar ist der Talkshow geschuldet weil man hat halt bloß drei Minuten Zeit interessant ich bin ich bin Krisen angeschaut eigentlich es gibt eigentlich überhaupt keinen wissenschaftliche Basis für ihre Argumente das stimmt natürlich nicht also ich hier auch einen Student der Geschichte und der Zyklen und natürlich gibt es tausende Beweise also wir haben viele Währungsräume scheitern sehen vor allem Währungsunionen haben niemals funktioniert weil halt unterschiedlich starke Volkswirtschaften in einem währungskorsett schlecht funktionieren irgendwann scheitern auch Geldsysteme die ungedeckt sind sind immer gescheitert und wir hatten natürlich über Inflation in der Weimarer Republik wir haben über Inflation in den letzten 70 80 Jahren immer wieder gehabt vor allem seit 1971 seitdem der Goldstandard aufgehoben wurde haben wir viele Pleiten gesehen auch vor allem in Südamerika aus dem Grund hatte da einfach nicht recht also es gibt natürlich wissenschaftliche Belege dafür das Geldsysteme natürlich scheitern wenn sie sich das Bank das war es natürlich arrogant von mir zu sagen ah okay also da habe ich mich da habe ich mich jetzt nicht von der besten Seite gezeigt da war ich noch vielleicht ein bisschen und souverän grünen Ohren oder ähm ja zu vielleicht zu sehr auf Krawall gebürstet ich hatte mir damals vorgenommen bei den anderen Sendung ich sehr wenig Redeanteil hatte öfter zwischenzukriechen öfters sozusagen auch mal ins Wort zu fallen das hatte ich mir dann abgeguckt von ähm Politikern mit denen ich halt den Sendungen war die einfach dann losgeht haben und dann irgendwie 20 Minuten lang geredet haben und da hatte ich mir vorgenommen das mache ich jetzt auch das Thema und Finanzsystem anschauen dann haben viele Banken Eigenkapital aufgebaut die Konsolidierung das Banken sterben was Sie beschreiben ist etwas gesundes und notwendig ist dass die Konsolidierung von Finanzinstitution geht das macht die Finanzinstitution stärker die große Deutsche Bank nee also sie haben keine keine Grundlage dafür schauen Sie mal gute auch das natürlich absolut arrogant von mir ich muss mich entschuldigen mich wieder ja es ist halt einfach man müsste Zeit haben deswegen mache ich ja die Formate hier Interviews dass man einfach mal eine Stunde Zeit hatten dann dazu reden sich auszutauschen die Argumente auszutauschen und so weiter also es war jetzt nicht die beste Schokoladenseite von meiner Seite aus da sage ich wirklich würde ich jetzt anders machen ähm aber auch da muss ich wieder sagen es ist dem geschuldet dass man einfach weiß okay es sind drei gegen ein und man hat gerade mal vielleicht zwei Minuten Redezeit und man möchte ja sein Punkt irgendwie valide und überzeugend und verständlich rüberbringen und dahingehend ja gut sein auch da wiederum was ich halt wieder perfide fand das hat mich auch getriggert natürlich bei ihm dass er immer mit diesem Argument kam ja Wissenschaften keine Argumente wissenschaftlich unbelegt und so weiter also praktisch im Zuschauer suggeriert hat ach der Friedrich das ist doch hier ein Dampfplauderer und es ist überhaupt nicht von dir der überhaupt mit überhaupt nichts recht ich meine auch da ähm ich bin wenigstens mutig genug Prognosen zu geben und habe auch viele Prognosen in den Büchern oder auch ein Interviews gegeben viele viele sind eingetroffen einige natürlich auch nicht bzw die werden noch kommen das sind bin ich überzeugt ja dass sie Zeit noch nicht reif dafür aber ähm ich hätte auf meine Argumente einzugehen und Gegenargumente zu bringen geht's dann immer mit dieser mit diesem Totschlagargument ja ähm die Vermehrung Diskreditierung einfach um dann der Argumentationskette aus dem Weg zu gehen und das war ja in den letzten Jahren immer gang und gäbe und das habe ich erst in den letzten Jahren durch Gespräch mit Matthias das mit z.B über die Massenpsychose das findet hier oben das Video unbedingt sehenswert erlernt das praktisch wenn man keine Argumente hat auf meine Argumente dann gibt's immer gleich irgendwelche Totschlagargumente um den Diskurs zu stoppen um dem Zuschauer zu signalisieren beschäftigt euch gar nicht mit den Aussagen von Friedrich ist ein Spinner Verschwörungstheorie hat keine Ahnung will nur seine Bücher verkaufen und so weiter und dann halt selber keine Argumente hat dann wird's halt persönlich und das erleben wir halt hier leider in Reinform das Masse Fratz schon mich natürlich versucht zu diffamieren zu tun genau das was ich gerade prognostiziert habe würde es ja ausgesprochen einfach nur Schwarzmalerei Tatsache ist viele europäische Länder haben harte Reform gemacht schauen sich Spanien an schauen sich Portugal anschauen sich Irland an sie sind auf einen guten Weg des Finanzsystem ja Griechenland Italien hat natürlich nicht erwähnt Frankreich und so weiter allen Ländern Südeuropas in die Schulden jetzt noch höher als damals zur Zeit der Ausstrahlung dieser Sendung und natürlich auch die deutschen Schulden sind weiter gestiegen obwohl wir ja rekordhaare hatten mit Steuereinnahmen und so weiter also wir sehen dieses ungedeckte Papiergeldsystem zieht darauf ab die Schulden immer weiter wachsen zu lassen weil es ein Schuldgeldsystem ist Schulden oder viel mehr Geld kommt nur ins System durch neue Schulden Wissen auf Gedeih und Verderben dazu gezwungen immer mehr Schulden zu produzieren ins System zu pumpen damit das ganze Geld Karussell überhaupt noch am Laufen ist und nochmal das tatsächlich wahnsinnig viele unten interessant dass jetzt Frau innen auch erkennt Mensch der palabert ja nur der fratcher Argumente bringen sie mir Argumente das war dann gut das heißt ein gutes mit zur Seite gesprungen ist nur am Leben erhalten werden weil es so viel billiges Geld gibt und die wären längst im Konkurs wenn es das nicht gäbe auch das ist eigentlich falsch denn und da ist er absolut auf dem falschen Pfad natürlich ist es nicht falsch das haben die letzten Jahre ja bewiesen da entweder erflunkert oder er weiß es einfach nicht beides natürlich fraglich für ein Experten des DIW na dann ist er auf dem falschen posten würde ich sagen aber wir wissen ja alle marcel fratsche ist ein lackierter SPD und sehr regierungsnah und hofft ja auch auf einen Posten das habe ich ja vorhin gesagt dass er sich bewirbt für Bundesbank EZB oder auch vielleicht für politische Ämter dessen ist man sich bewusst da gibt es auch einen schönen Artikel in der FAZ können wir hier mal einblenden und dahingehend kann er gar nichts anderes sagen und wir wissen ja alle wie oft Marcel fragt schon der Vergangenheit falsch schlafen das habe ich immer immer wieder auch auf Twitter sozusagen unter die Nase gerieben bis es ihm halt dann zu viel war weil er keine Argumente mehr hatte mich dann einfach geblockt hat ne also Inflation z.B hat er gesagt ja Inflation wird nicht kommen dann war es nur temporär und dann was natürlich nur eine grüne Inflation also er ist wirklich der deutsche kennt Jim Gamer ist ein amerikanischer Moderator einer Börsensendung und ähm er hat wirklich eine hundertprozentige Trefferquote wenn er sagt Apple geht jetzt irgendwie ein Bach runter dann steigt Apple auf neue Rekordniveaus und genau weiß worser also er ist der große Kontraindikator genauso bedeuten erst einmal das digitale Unternehmen sich günstiger finanzieren können und natürlich gibt es immer Unternehmen die Pleite gehen die Konkurrenzunternehmen können hier müssen wir es auf jeden Fall dann den Chart einblenden mit den steigenden Insolvenzquoten in Europa in Deutschland aber auch natürlich weltweit weil wenn die Zinsen steigen dann wie gesagt kippen die zombe übernehmen um und die waren laut Bank of international settlement bei jetzt schon zuletzt 20% in USA ebenso und die werden jetzt alle sozusagen in den nächsten Jahren abgewickelt werden weil die Pleite gehen ganz einfach und so wäre es eigentlich auch mit Ländern eigentlich müsste Italien auch irgendwann mal bankarotter anmelden wenn ich die EZB wäre auch die die jetzt Startup Unternehmen junge Unternehmen die neue Ideen haben die haben eine Chance in seinem Umfeld zu wachsen zu gedeihen es ist ein absolut Fehlanreiz das zu null Prozent Zinsen Unternehmen die nicht wirtschaftlich arbeiten Geld bekommen es ist ein kompletter eine fehlall Allokation von Geld von Vermögen weil die Unternehmen die es wirklich brauchen die wirtschaftlich agieren die Arbeitsplätze schaffen die innovativ sind eben dann kein Geld bekommen weil es hat irgend so eine Internet putze in Berlin bekommt oder irgendwie so ein anderes Projekt was eigentlich zum Scheitern verurteilt ist deswegen diese dieses Argument muss ich ganz klar verneinen schlechten Unternehmen Innovation wird gestoppt das ist überhaupt keine Grundlage dafür ja und da wurde es einfach nicht mehr sachlich muss ich sagen überhaupt keine Grundlage dafür dass es wirklich genau in Deutschland stehen viele junge Unternehmen und klar wir haben Herausforderung aber wir sind weit gekommen und diese diese demologie es gibt ein gerecht Demagogie klar er muss wieder hier mich irgendwie vor dem Publikum diffamieren er geht nicht auf die Argumente ein wie siehst du das schreibt man unten in die Kommentare bitte mindestens jetzt schon gefällt Daumen nach oben das hilft dem Algorithmus und mit diesem allerersten mal hier bist und ähm ist gut finde dass ich auch selbstkritisch über meine Aussagen bin aber da lassen und Glocke aktivieren dann wirst du informiert wenn ein neues Video online geht für die Bundesbank und für die EZB also was wir erleben seit 2008 ist doch historischer Vertrauensverlust in das Geldsystem in die Banken weil uns alle betrogen haben in die Politik weil die die demokratisch legitimiert haben nicht uns vertreten haben in der Krise sondern den Banken zur Seite gesprungen sind und noch mit unseren Steuergeldern gerettet haben und Garantien vergeben haben parallel haben wir noch natürlich wir alle haften doch für den ganzen klar daran dass wieso sind die Tage zwei Seiten auf ihre wo wir keine Krise haben 2012 während der Griechenland Euro gewesen bei der Frage kann die EZB immer weiter Anleihe aufkaufprogramme machen vergemeinschaft unter Schulden ist nicht unser Weg wir teilen das nicht was da passiert und Brüssel kann man kritisch sehen also sie dürfen auch nicht weglassen dass sie Verantwortung in Europa sind mindestens auch umfasst dass wir auch die südosteuropäischen Staaten nicht einfach ihren Schicksal alleine überlassen konnten aber nein es macht doch keinen Sinn den Griechenland sich momentan günstiger Verschulden kann also ein Kapitalmärkten wie die USA wir wissen doch alle diese bankrot Italien genauso also die sind unregierter haben und trotzdem konnte sie so günstig Verschulden wie noch nie in der Geschichte 2023 spricht alles auch das natürlich absolut richtiger Punkt von mir also nur weil die EZB ihre schützende Hand über die südlichen Staaten gestellt hatte konnten sich die Länder günstiger Verschulden als manches Land mit einem Triple-A-Rating ne weil Deutschland halt gehaftet hat und das ist halt eine fehlalokation von Vermögen von Geld und die Tage zwei Seiten sind nach wie vor über eine Billion Euro die wir praktisch anderen Notenbanken in der Eurozone geschenkt haben weil das ist unsere wohlstandsleistung unser wohlstandseffekt den wir kostenlos weggegeben haben dass wir so wie wenn Bosch sagt ich verkaufe meine Kühlschränke nach Griechenland aber ich will nichts dafür schreibt es auf dem Papier und das gut sein 24 auch keine Lösung und was Sinn macht ist dass die die Verantwortung tragen immer auch Lösung bringen müssen auf jeden Fall die die Aussage stimmt hundertprozentig 100% Recht behalten in den letzten Jahren dass die Politik leider immer weiter versagt hat und Lösungen keine in ihrem Bundesland an die die die Rechten und die Linken haben da erstmalig die Mehrheit bekommen und wir werden weiterhin Tendenzen sind dass die Ränder immer stärker werden weil die Menschen das Vertrauen in die etablierten Parteien verlieren und es Lager völlig zu Recht weil sie den Tag ist sind und weil sie inkompetent sind stille keine Widerworte nicht mehr von Politiker und Probleme die Sie angesprochen haben einfach wegzusuchen es gibt unglaubliche Ungleichgewichte in der Eurozone es gibt ein riesigen Schulden überhand den gibt es die dem wissen sie auch also ich meine ich habe Sarah kommt mir zu Hilfe also wirklich die Artillerie ist da das freut mich natürlich dass sie mir da zur Seite springt und auch ein Fratze noch mal angeht und darauf pocht das Argumente liefert und nicht nur versucht alles mit stigmatismus und die Vermehrung abzuwenden beispielsweise und andere Länder sind natürlich seit Jahren nicht wieder auf die Beine gekommen also das Wirtschaft werden hängt natürlich von der Politik ab aber so lange ist in der gesamten Eurozone im Grunde nur eine Ideologie gibt man darf auf gar keinen Fall irgendwie kreditfinanziert Investitionsprogramme auflegen und die Staaten das Befolgen solange wird es auch nicht funktionieren tatsächlich aber nicht also wenn die Politik so weitermacht wie bisher und wenn sie immer noch an den falschen Ideologien falschen Modellen und falschen Interessen bei festhält und wenn sie es tatsächlich auch jetzt wieder wo sich die jetzt drückt sich ja die Wirtschaftslage gerade wieder ein und wenn sie immer noch nicht begreift dass sie tatsächlich eine Politik für die Mehrheit der Leute machen muss und nicht für Banken nicht für große Unternehmen nicht das was die Lobbyisten erzählen wenn das alles so weitergeht wie bisher dann ist die Gefahr groß ich finde es nur ein bisschen fahrlässig und das so mit einem wohligen Schauer zu erzählen und sozusagen als ging es gar nicht anders weil ich möchte mir nicht vorstellen welche politischen Konsequenzen ein solcher Finanzkrise hätte da haben sie nämlich tatsächlich recht wir wissen wie das nach den 20er 30er Jahren ausgegangen ist und deswegen brauchen wir eine andere Politik damit es genau zu diesem Horror Szenarien nicht kommt also es war nicht mein souveränster Auftritt im Fernsehen ich habe tatsächlich ein zwei Mal mich wie ich finde daneben benommen und auch im Ton vergriffen da muss ich ganz selbstkritisch sagen das würde ich heute so nicht mehr machen und würde mich auch entschuldigen natürlich war ich getriggert durch diese Situation drei gegen eins und natürlich die diffamierungsversuche von Marcel Fratzscher ich habe auch versucht mit Marcel fratzschen und meinen Kontakt zu treten habe ihn auch eingeladen zu einem Gespräch hier vor Ort habe auch versichert dass es absolut fair im Diskurs verlaufen würde leider hat er abgesagt aber vielleicht könnt ihr ihn ja mal anschreiben ob er nicht bereit wäre für eine Runde 2.0 vielleicht auch bei Ihnen oder sonst wo dann würde ich dann auch mit ihm darüber diskutieren wo lag er richtig wo lag ich richtig und vielleicht hat er auch so die selbstkritische Ader wie ich und sagt okay das war falsche friedlich gebe ich zu mehr kooper fakt ist aber auch einige Aussagen sind tatsächlich eingetroffen muss man ganz klar sagen ob der Euro besitzende 2023 umkippen wird definitiv nicht die werden den Kaugummi natürlich in die Länge ziehen aber nach wie vor bleibe ich meine Grundaussage treu indem ich sage dieses Finanzsystem dieses Geldsystem wird scheitern es gibt Lösungen und die Lösungen heißt unter anderem natürlich Bitcoin ja oder Sachwerte um seine Kaufkraft zu schützen also jeder der Zweifel am jetzigen Papiergeldsystem hat und Papiergeldsysteme tendieren immer dazu zu scheitern oder gegen Null zu tendieren dass wir große Kaufkraftverluste sehen werden sollte auf jeden Fall anfangen sein Vermögen umzuschichten wer Hilfe braucht kann gerne auch zu uns in die Honorarberatung kommen oder natürlich auch das ein oder andere Buch von mir lesen fakt aber ist wir werden in das Zeitalter der Sachwerte kommen und das sind wir eigentlich schon das heißt man braucht durch Natur durch die Mathematik limitierte Werte um seine Kaufkraft in den nächsten Jahren zu schützen wie siehst du das wie fandest du meinen Auftritt mit Marcel Fratze bei ihnen lass mal das Kommentar da und wenn ihr mich da bitte mal sehen wollt schreibt doch mal der Redaktion von Illner die Blenden wir auch gleich mal ein dann könnt ihr eine E-Mail schreiben nach dem Motto hey da hat Friedrich ein damit auch meine andere Stimme hören gegen den Mainstream oder gegen das narrativ beziehungsweise macht doch eine neue Auflage zwischen Fratzscher und Friedrich F&amp;F die neue Sendung im ZDF mit dem zweiten sieht man besser habe ich nicht verstanden weil gell mit dem zweiten okay also in diesem Sinne bleibt stabil bleibt souverän und denkt immer daran genau wegen solchen Sendungen und selbstkritischen Aussagen wird die Welt und ist die Welt da draußen besser als immer glauben herzlichst</t>
+  </si>
+  <si>
+    <t>yBLMMBfBe5A</t>
+  </si>
+  <si>
+    <t>ich bin wirklich wütend und ich habe über einige Monate überlegt was ich machen soll und ich habe mich jetzt entschieden dass ich und ihr habt das vielleicht gesehen dass die Videos auf diesem Kanal löschen Ich will euch sagen wie ich auf diesem Kanal weiter verfahren werde weil ich einiges ändern möchte und muss aber ich hätte dich all das erklären ich werde euch erklären welche Probleme wir hatten in der Vergangenheit mit YouTube wie wir unter anderem gegen Youtube geklagt haben und Recht bekommen haben aber mit welchen Problemen wie hier zu kämpfen haben und warum ich das ganze müde macht wenn man darüber zu sprechen dann ist das eine Sache die ich gehört aber von Dieter nur ich glaube bei Schüler in einem Interview aber gesagt hat dass er nicht zu denen gehört dir eine Demokratie Anzahl von hier er hat das Gefühl dass man immer noch alles sagen kann und das ist dafür Bereiche gibt und dass ich anders ich sehe es nicht so dass man Dinge nicht sagen kann aber schon so dass es vermehrt Konsequenzen gibt das sind Dinge die alle wisst sind Menschen die sich mit der Politik in Russland auseinandergesetzt haben die haben teilweise ihren Job verloren für das Informationen haben und es ist so dass wir wenn wir uns die Sanktionsliste anschauen damit das erste Mal Bestrafungen für Menschen die Medien Nachrichten verbreiten also egal wie wieder darüber sprechen wir sind auf jeden Fall für einen Punkt bei einem Punkt sind einig manche Dinge dürft ihr nicht sagen wie sie sind die Begründung will ich vollkommen aus dem vorlassen ob wir die Bevölkerung schützen wollen oder nicht ob wir uns lange Zeit damit gebrüstet haben alles sagen zu dürfen oder nicht dass er dahin gestellt es gibt aber garantiert Konsequenzen es war das erste Mal im Februar ich habe mir hier ein Rangliste gemacht das erste Mal im Februar das unser Kanal gelöscht wurde aus einem für mich fadenscheinigen Grund jeder von euch der mein Content verfolgt hat der weiß das aber wir sind gelöscht wurden für Sexualität und Nacktheit ich weiß nicht ob wir meinen Content verfolgt hat ich würde behaupten dass ich hier noch nicht einmal eine nackte Person hatte nichtsdestotrotz war das ein Problem wir haben den Widerspruch eingelegt und wir haben dann dagegen geklagt was gar nicht günstig ist ich habe Anwalt nach Anwalt gesucht und das war eine Sache die ich gesagt habe ich oder alles was ich finanziell zur Verfügung habe wirklich nutzen und gegen Unrecht vorzugehen das habe ich gemacht wir haben Recht bekommen aber es war das erste Mal für euch dass ihr das wisst wir haben gewonnen es war unrechtmäßig und jetzt muss man ehrlich sein es ist so auf dem Kanal dass ich Dinge sage wie sie sind ich will nicht sagen als einziger aber es ist dass ich Probleme wenn sie da waren angesprochen habe wir haben nicht einfach eine Vortrag gehalten ich habe sie emotionalisiert vielleicht vielleicht positiv vielleicht negativ ich habe gesagt wie ich dazu stehe und die habe ich gesagt wir wütend mich manche Dinge machen es gibt verschiedene Dinge die mich wütend machen es ist wenn wir zum Beispiel jetzt darüber sprechen ein Thema wegen dem ich zweifach gesperrt wurde auf Youtube jetzt deswegen nicht benennen aber ihr alle kennt das regierungssupplement das habe ich bemängelt was habe ich noch ich habe das Thema Einwanderung habe ich behandelt ich habe die verschiedensten Dinge benannt ich habe gesagt was für ein fatales und wegen das ist ich habe Fallbeispiele genannt ich habe gesagt welche Schicksale dahinter hängen ich habe gesagt dass man das nicht akzeptieren kann und dass kein normaler Mensch das akzeptieren kann ihr merkt dass ich bin bei solchen Themen emotional und ich habe mich manchmal in Rage geredet ich habe trotzdem versucht Leute nicht zu beleidigen ich habe vielleicht versucht sarkastisch manche Dinge darzustellen ich habe hinterfragt ob ein Gesundheitsminister der Problem hat mit seiner eigenen Zahngesundheit zurecht zu kommen und das wirklich die beste Wahl ist solche Dinge habe ich gemacht die man vielleicht als fragt würde ich unter der Gürtellinie da sehen kann schande über meine Haupt da habe ich vielleicht den Ton nicht getroffen aber dafür gab es keine Probleme bei den Sachen ist es aber so dass ich nicht einfach wiederlegbar war denn es gibt der den Fall dass man sagt schwurbler immer wenn ich mir irgendwelche Dokus da anschaue dann gibt es darum dass es Zusammenhänge gibt die dargestellt werden die anderen nicht sehen können aber die Dinge die ich gesagt habe die habe ich für rational gehalten ich habe sehr gut das ist doch gar nicht sprechen über dies und jenes lass uns darüber Dinge sprechen die wir garantiert sagen können die auslegungsringe sind 31 Menschenrechte die ist 31 ist die Auslegungsregeln das besagt wir dürfen niemals einen Menschenrecht das dürfen wir ausleben auch nicht um andere zu schützen kein Gesetz darf da eingesetzt werden dass Menschenrechte aussehen wird sondern alle gesehen das habe ich gesagt wir müssen uns auf Menschenrechte besinnen und wir können wütend sein wenn man uns das Wegnehmen möchte unser Grundrecht das habe ich gesagt was habe ich noch gesagt ich habe gesagt wir sollten uns an Gewerkschaften wenden ich habe Gewerkschaften geschrieben warum weil wenn wir irgendwie gegen vorgehen wollen wenn wir irgendetwas machen wollen dann müssen wir schaffen dass die Menschen ihre Arbeit niederlegen und das vollkommen offiziell wir wollen zu nichts illegalem aufrufen aber lass uns doch mal mit Gewerkschaften sprechen das ist nicht der Ansatz von vielen Sportler so ihr merkt das ich habe versucht im System das System zu besiegen das kann man andere Person die es gemacht hat ein Michael ballwig der hat die Spenden dir bekommen hat genutzt um Sendezeit zu kaufen und er hat Leute aufgeklärt im Fernsehen dem Medien dass die Regierung sonst nutzt ein glorreicher Schachzug das ihm am Ende unrechtmäßigerweise ins Gefängnis gebracht hat wie alle haben gesehen dass die Behauptung unrechtmäßig machen er war in Untersuchungshaft ohne Anklage welche Aufrufe hatten wir ich muss aufgeschrieben wir hatten allein auf YouTube zu diesem Zeitpunkt 15 Millionen Aufrufe pro Monat 15 Millionen ich weiß nicht wer jetzt der größte ist ich glaube Aktien mit Kopf ich weiß es nicht ich glaube er könnte ähnliche Aufruf Größen haben vielleicht auch weniger aber nur das hört wir waren damals wir waren mit die ersten und wir haben das dann gemacht und darüber sprechen ist es ja eine Sache andere verdient wenigstens Geld damit das heißt wenn die jetzt Videos gemacht haben dann ihr das vielleicht mitbekommen die haben ihre Einnahmen gepostet 40.000 50.000 60.000 also es war unglaublich das ist eine Sache die hatten wir nicht wir haben dann schnell Probleme bekommen wurden demonetalisiert ich wurde darauf hingewiesen dass ich manche Themen nicht nennen darf wie gesagt es gibt bestimmte Themen über die dürft ihr nicht sprechen ungern den Mund verbieten nicht dachte immer sobald wir das haben sobald wir das machen wenn wir das richtige tun dann ist Geld eine Sache die folgt ich muss mich nicht im ersten Schritt darum kümmern hier bei einer Sache die unrechtmäßig ist daran finanziell zu profitieren weil wenn wir mit den Leuten gemeinsam das machen dann haben wir allein über Youtube die Einnahmen möchte weil ich Dinge sage in ihren Augen die kann man später darüber andere werden Partner kriegen der Mann vertraut das heißt wir wurden dem monetarisiert aber so Überzeugung und dann hatten wir verschiedenste Probleme ich habe jetzt aufgeschrieben ständig irgendwelche Dinge für Copyright jeder von euch das weiß wir haben wie hier auf Dinge reagiert und euch Zeitungsausschnitte eingeblendet Copyright plötzlich von Videos vor Jahren das wollen unsere Videos durchgeguckt wo könnte man eventuell Schaden und wir wurden dafür angegangen was als nächstes gekaufte views wir kriegen die Nachricht dass wir runter reguliert werden warum weil wir vielleicht Videos gekauft haben Leute 15 Millionen Aufrufe organisch 15 Millionen wie viele Aufrufe haben wir gekauft haben es waren am Ende 5000 ihr glaube ich setze meinen meine Reichweite aufs spiel ich klage gegen Youtube und kaufe dann Klicks das heißt ich hole mir den YouTube-Kanal zurück um ihn dann zu botten um Computer da drauf zu schicken die nicht verstehen was ich sage wir haben allein auf Telegramm 50 000 Leute die Klicks die ich gekauft hätte kriege ich mit einem Link nämlich einmal etwas in die Gruppe schicken man hat unsere Impressionen eingeschränkt sondern Mitarbeiter gesagt damit aber das gesagt hat wenn ich nicht wüsste dass wenn ich das nicht besser wüsste hätte ich gesagt man hat dein Gesicht gebannt weil immer auf dem Hauptkanal auf dem wir gepostet haben sind wir immens eingeschränkt wurden ihr glaubt das vielleicht nicht wir haben Videos da haben wir tonnenweise Traffic drauf geschickt wir haben Leute drauf geschickt die sich das angucken die wir auf Telegramm etc gesammelt haben noch mal damit 53 000 Leute und youtube hat uns einfach nicht ausgespielt wir haben nach einer Stunde haben wir 300 Impressionen gehabt irgendetwas in dem Raum wir wurden einfach nicht angezeigt und die einzige Möglichkeit wie das möglich das haben wir nicht verstanden und immer dann wenn wir einen neuen Kanal gemacht haben dann liegt das wahnsinnig das erste Video hat 140.000 Klicks etc so wie YouTube normalerweise läuft aber wir wurden eingeschickt das nächste mal einen Monat später wir sind das nächste Mal gesperrt danach nicht mal 14 Tage wieder die nächste erneut die Drogen wir löschen deinen Kanal komplett also was mache ich die einzige Möglichkeit die mir bleibt um gegen diese große Gefahr vorzugehen dass ich nie wieder auf dieser Plattform zu sehen bin ich klage ich weiß nicht ob ihr wisst was ein Anwalt kostet in so einem Bereich aber sie Frage ist dann haben das gibt es hier wie Arbeiter ich glaube es waren 350 Euro dafür oder 500 Euro so pro Stunde und habe ich gefragt mir war das wirklich wichtig ich sage die Sachen die man angeht soll ich euch Quellen dafür nennt das ist ja alles belegbar die Sachen die ich sage das sind ja Sachen die heutzutage in der Tagesschau kommen das sind Dinge für die wir vor Gericht mussten ohne Erfolg ist nicht mal dass wir keinen Erfolg hatten wir haben einfach keine Antwort bekommen vom Youtube wir saßen dort und wenn überlegt klare wir haben geklagt aber das sind Monate lange Prozesse und es ist ein immenser Kostenfaktor und in diesem Punkt ist es so dass ich mich die ganze Zeit Frage warum um Himmel mache ich das eigentlich wie gesagt einige verdienen ja zumindest Geld noch damit wir sind die monetarisiert und damit sage ich nicht dass der Einzige bin zum Beispiel ich schätze ja immens zum Beispiel Carsten ja und die Heimat aber wenn ich Carsten Jahn anguckt der ist ja ebenfalls demonetarisiert weil wenn ihr manche Dinge sagt dann ist das erste was man versucht dass man nicht einschränkt ein Tim Kellner den schätze ich unglaublich der ist ebenfalls demonetarisiert wenn ihr Dinge sagt dann geht das nicht und seine Sache die ich von Ken Jepsen gehört habe der komplett de plattformiert wurde der hier nirgendwo zu sehen sein darf er hat gesagt dass jeder der an einem System mit verdient dass der Teil des System wie das System möchte dann zeigt euch das dass ihr vom System gewollt hat und wenn ich dann sehe dass manche Leute Dinger machen und sagen die dann aber eigentlich ist das Grundgerüst reinspielen die vielleicht sagen oh hier guck mal die Werbung ist die böse und dann geben sie den Leuten das Gefühl guck mal wir sprechen das Unrecht an aber wir ändern da gar nichts dran dann haben die Leute vielleicht das Gefühl oh endlich sagt das einer aber dann setzen sie sich hin und nichts passiert das heißt das sind Träger eines Systems ich habe gedacht das mache ich nicht ich habe überlegt kann man Dinge wirklich verändern ihr wisst das vielleicht aber wenn ihr anfängt gegen das System vorzugehen dann kriegt ihr Probleme was war bei Alina von Neues aus Russland ihr konntet das Konto ihrer Mutter wurde gesperrt und ich bin nach Deutschland geflogen nach Deutschland für eine für eine Demonstration um auf eine Demonstration passiert ist mein Konto ist gesperrt ich habe das damals bei Tele gegangen ich dachte ich spinne und ich habe mich gefragt okay wie gehe ich jetzt damit um und nochmal ich mache hier überhaupt keinen Angriff an die Leute die einfach Videos darüber machen und dann mit Klicks Geld verdienen weil exakt das ist ja eine Sache ich gönne jedem der mit der richtigen Sachen Geld verdient und seine Sache über die ich mich am Ende wirklich gestört habe weil ich frage mich warum tue ich mir das eigentlich an und deswegen ich habe überlegt wisst ihr ich habe jetzt zwei Videos gemacht ich habe keine Lust mehr mich mit diesem ganzen Unsinn auseinanderzusetzen ich bin müde ständig dass unser Kanal gestreikt wird dass wir gesperrt werden dass ich klagen muss und das am Ende nicht und dass wir dann um views kämpfen etc ich will niemanden angreifen aber ich hoffe ihr versteht das ich habe mich entschieden mein Content zu ändern und bis es den Punkt gibt und ich weiß dass es gerade immer schlimmer wird das jetzt in Frankreich plötzlich möglich ist dass mein Handy sein wird das all die Dinge hier auch durchgesetzt werden das ist die Forderung nach Strafen für viele Informationen gibt da will ich mich einfach rausnehmen aus diesem ganzen Zeug und ich werde hier auf dem Kanal berichten über Dinge die langweilig sind über die wirtschaftlichen Konsequenzen und ich werde es absolut unemotional machen wie die anderen ich will niemandem mehr erklären was er besser machen kann und ihr könnt alle ihr inzwischen Wissens das ist wirklich Dinge gibt die besser sind und ich glaube das ist ja in Deutschland auch noch eine Opposition gibt die sich vielleicht dafür einsetzt ich glaube das ist Möglichkeiten gibt aber ich werde hier anfangen langweiliger zu sein und wir werden Anfang ebenfalls so wie die anderen Probleme nicht mehr anzusprechen aber ich kann nicht mehr anders ich bin müde und ich werde vielleicht auf Telegramm mal meine Meinung teilen aber das war's ich hoffe ihr versteht dass ich wollte euch darüber in Kenntnis setzen danke dass ihr zugeguckt hat bis zum nächsten Mal</t>
+  </si>
+  <si>
+    <t>YAzCiDzBpuA</t>
+  </si>
+  <si>
+    <t>wir müssen jetzt in diesem Video einmal sprechen über ein Land in Europa das absolut eskaliert ist ihr wisst das ich habe das bei Telegramm geteilt es gab das erste Mal dass im britischen Parlament gefordert wurde dass man sich Russland frontal stellt dass man selber in den Krieg Eintritt ja in Wolf of life the current process this with gifting equipment we need to face Russia directly und der Hauptgrund dafür ist dass es der britischen Wirtschaft vermutlich am schlechtesten geht naturlich die ernsthaftesten Schwierigkeiten auch in Zukunft wird es unglaubliche Probleme geben die Inflation dagegen man keinen Mittel die häuserblase die Immobilienblase die könnte zusammenbrechen und ich möchte bei all diesen Dingen einmal darauf eingehen wir haben das vor vier Monaten noch diesen Kanal gemacht und ich habe jetzt gesagt dass die Aussichten für Europa düster sind es war unter anderem so dass damals vor vier Monaten Anfang 20 23 das vorausgesagt wurde das sogar Russland Wirtschaft schneller wächst als das von Großbritannien das damit ganz klar diesen niedriges Niveau aber wir sehen dass die ganze Welt auf eine Rezession zusteuert dass die EU des deutschen bereits in einer Rezession ist und es ist sehr sehr wahrscheinlich dass das nächste Land das ebenfalls in diese Liste Eintritt das eine Rezession erwarten wird dass das vereinte Königreich ist das Land steht vor einem perfekten Sturm aus hoher Inflation aus einer Hypothekenkrise und einem wahrscheinlich negativen BIP in diesem in diesem Jahr und die Situation ist so schlimm dass die Regierung jetzt anfangen musste Maßnahmen zu ergreifen wie beispielsweise hohe Zinssätze die Deckelung der öffentlichen Gehälter und Preisregulierung um den Konsum einbrechen zu lassen um einigermaßen alles in den Griff zu kriegen aber nicht nur dass das sehr sehr starke Maßnahmen sind sondern es ist auch so dass das vermutlich zu spät ist und das ich glaube dass die Inflation dort bereits außer Kontrolle zu sprechen ist es so dass das Vereinigte Königreich seit April 2022 an den Vertrauens gesagt die Inflation dort im Land lag kontinuierlich konstant über den Inflation der anderen g7-wirtschaften sie ist höher als in der Eurozone den USA höher als in Japan und obwohl die Inflation jetzt auf einem Abwärtstrend ist liegt sie immer noch bei 8,7%. das führt dazu das ist eine Art kostenkrise gibt man weiß nicht wie man den Lebensunterhalt bezahlen soll es ist so das nahezu das gesamte Geld und das ist nicht übertrieben einfach für den Lebensunterhalt dort ausgegeben werden muss das heißt es wird sogar mehr Geld teilweise ausgegeben für Lebensmittel für Unterkunft als für alles andere und ironischerweise ist es so dass dass die Infektion sogar oben hält die hat das vielleicht gehört Lohn Preisspirale das ist eine Sache die Dinge immer weiter nach oben treibt aber aufgrund dieser Situation wird sein dass die Bank auf England gezwungen sein wird die Zinsen noch weiter zu erhöhen und die Nachfrage zu denken ich will überhaupt dass es andere Wahl dafür gibt es sind andere Faktoren wie angebotsschwierigkeiten und Energiepreise die die nicht in der Kontrolle Großbritanniens liegen die Bank kann ich von heute auf morgen Lebensmittel produzieren man kann nicht mehr Häuser bauen oder mehr Öl fordern das heißt man muss als einzige Möglichkeit die britische Wirtschaft abwürgen um irgendwie jetzt mit den Problemen in Kontrolle zu kommen es ist aber so dass falls die Zinssätze steigern und das ist ja das ist mein Plan was man macht derzeit gezwungenermaßen wird es zu anderen Problemen führen es ist so dass gerade die britische Wirtschaft dass die anfällig ist frohe Kreditkosten es ist so dass im letzten Jahr ist der britische anderen Markt zusammengebrochen das hat dazu geführt dass es massivste Konjunkturprogramme gab es vielleicht mitbekommen von Boris Johnson der dann da zurück hat dann bevor richtig zu tun hat da kam da gab es ja noch die die Idealisten der ist mir der Name gerade entfallen aber was das nicht ein drunter und drüber war und das ganze recht sich jetzt das ganze hat dazu beigetragen dass wir dort eine weit höhere Inflation haben doch die größte Bedrohung für die britische Wirtschaft ist eine hypothekenkatastrophe und zwar geht es darum dass Millionen Haushalte davon in die Insolvenz getrieben werden können und dabei handelt es sich nicht um große Hedgefonds oder Banken die jetzt in der Krise sind das geht darum dass wirklich die durchschnittlichen Banken und Familien eventuell auf die Straße müssen das ist übrigens eine der Probleme die wir auch haben in Deutschland ich habe euch das in den letzten Videos vor einem Jahr ungefähr erzählt er hat euch vielleicht daran dass uns das einmal kurz erklären es ist so dass sollte sich der Wohnungsmarkt verbessern dann wird der Konsum der wird definitiv einbrechen und es wird zu mit Sicherheit zu einer zu einer schrecklichen Rezession führen die über Jahre andauern könnte länger als in jedem anderen jesident das uns dann einmal über die inflationskrise im Feinden Königreich sprechen wir wissen dass Sie dass die Inflation dass die eklatant hoch ist die Inflation im Vereinten Königreich geht auch nicht zurück der Verbraucherpreisindex der CPI wie konstant bei 8,7 Prozent für April und im Mai ist ja ebenfalls auf 8,7 Prozent geblieben und die schrecklichen Nachrichten für uns ist dass ich das nicht so verändern scheint das heißt nicht dass die Preise rapide steigen sondern auch dass die dass die Rate des Abfalls dass sie sich verlangsamt wenn man selbst die Kerninflation ansehen also diejenige die Energie und Nahrungsmittel ausklammert damit die eigentlich Dinge beinhalten sollte die nur langsam steigen die Preissteigerung nicht anfällig gegenüber sind dann können wir sagen dass die Inflation zu einer Krise geworden ist nicht nur dass sie tatsächlich auf 7,1% gestiegen ist sondern sie hat sich über Monate auf diesem Niveau gehalten damit wir darüber sprechen ist das eine Sache die auch häufiger gehört ich spreche häufiger über die Kerne Situation und das liegt daran dass die Zentralbanken gerne auf die Kerninflation achten das eben kurz angedeutet sie repräsentiert Güter deren Preisen und langsam steigen oder fallen deswegen wenn die Inflation in Großbritannien jetzt weiter steigt sagt uns das dass wir eigentlich mit hohen Zinssätzen und rechnen müssen weil das die einzige Möglichkeit sich jemand dagegen angehen kann und Inflation entgegenzuwirken muss normalerweise der Zinssatz über das Niveau der Inflation hinaus erhöht werden der Benchmark sind Satz für das vereinte Königreich liegt derzeit bei 5 % und die Kerninflation liegt bei 7,1%. wir können also sagen dass hierbei jetzt gerade eine massive Lücke dazwischen zu sehen ist je höher die Zinssatz jetzt allerdings steigen desto wahrscheinlicher ist dass man eine Rezession kommt aber falls ihr das nicht macht weil sie die Rezession nicht im Kauf nehmen wollt dann habt ihr das Problem eine dauerhaften Inflation und das ist für alle besonders aber für die Bevölkerung die kontinuierlich Dinge kaufen sollen die dann immer und immer mehr Probleme kriegt die damit dann anfängt unter anderem in die immer nur zu rutschen das ist das eine Sache die dadurch sehr sehr schlecht ist die nahrungsmittelinflation wenn wir jetzt die sehen dann ist das nicht dass die nicht steigt Gegenteil Zucker ist in Großbritannien um 50% gestiegen Käse ist um 33 Prozent gestiegen Eier sind 29% teurer geworden ich habe euch neulich die Zahlen von Frankreich genannt es ist hier genauso ist es unglaubliche das ganze steigt und das sind Dinge die in jedem Haushalt überall im Land zu spüren sind die Menschen dort geraten dann wirklich Bedrängnis sie geben mehr Geld aus gleichzeitig bekommen sie weniger aber wenn man bedenkt dass es dann nur die Lebensmittelindustrie wären dann liegt man leider falsch es ist derzeit so dass die Situation eine hässliche Wendung nimmt und Großbritannien ebenfalls wie wir von importiert im Gas abhängig war und da leidet Großbritannien auf massivste Art und Weise dass sie mitführen waren darin die Sanktion gegen Russland zu führen und darunter leidet groß wollen die jährliche energiepreisinflation im Vereinten Königreich liegt bei 40,5%. inzwischen fängt sie zwar wieder an zu sinken aber die Energiepreise sind bei weitem nicht so hoch wie in den Vereinten Staaten oder Deutschland aber in Deutschland liegt die energieinflation zumindest nur bei 5% in den Vereinigten Staaten ist die ins Negative sogar gefallen das heißt das ganze wird günstiger und es ist jetzt so dass im Vereinten Königreich dass sie damit das schlechteste aus beiden Welten habt also jeder Faktor der zur CPI zum consumer Preisindex beiträgt also kerngüter kerndienstleistungen Nahrungsmittel Energie all diese Dinge sind massiv gestiegen und wenn ich das vorstellt dann merkt das Volk das es gibt also jetzt kein Ausweg das heißt für Lebensmittel Gas oder verdienstleistung alle Preise werden steigen und die Preise steigen stark an und sie mindern damit das was das Volk an den Wohlstand hat oder an der sparnisse ist die Frage welche Möglichkeiten hat die britische Regierung was kann sie tun versuchen dass sie Regulierung bringen das können wir schätzen es wird vermutlich Maßnahmen zur Preiskontrolle bringen aber wenn ihr mich fragt dann ist das immer ein externer Griff und der wird dazu führen dass mehr Lebensmittel Knappheit gibt unter anderem weil Leute anfangen werden zu horten weil sie Angst haben morgen wir dürfen das und das nicht mehr haben und es wird zu wie nennt man das diesem Eichhörnchen Falten kommt Supermärkte werden dann ihre Preise schneller umstellen oder sie werden die die Qualität ändern die das Vorgehen das wird noch mehr Problem finden die einzige Lösung die es für höhere Preise gibt sind höhere Preise das heißt wenn ihr dem Volk sagt dass es bereit sein muss dafür zu zahlen aber wenn ihr glaubt dass das Schlimmste ist dass das falsch weil dadurch sehen wir die Zinssätze müssen um diese ganze Wirtschaft am Laufen zu halten müssen die weiter steigen und die Bank auf irgendetwas hat sich dazu geäußert sie hat gesagt die Zinssätze werden um 50 Basispunkte auf 5 % angehoben und das ziemlich schockierend weil man auf den Märkten mit einer geringer Erhöhung gerechnet hat die Bank of England hat aber keine Wahl wenn wir ehrlich sind sie muss extrem hoch wenn wir uns das anschauen wenn wir uns die Zinssätze anschauen dann sind wir ziemlich nah mit dem was wir an den historischen Höchstständen von 2008 hatten und dort hat das ganze fast sechs Prozent erreicht und wir wissen was damit passiert ist damit der komplette Immobilienmarkt kollabiert und die Leute haben ihre Häuser verloren aber wenn wir uns dieses Problem Anschauen von damals sind es das gleiche was wir mit den Bankenkrise haben dieses Problem hat sich nicht verändert in den letzten 15 Jahren oder so das vereinte Königreich fast nullzinsen genossen nochmal ich habe das gesagt fast so wie in Deutschland das heißt man hatte noch nie so billiges Geld in der modernen Geschichte und was hat das gewirkt es kam dazu dass ihr eine hohe Menge hattet an spekulationskäufen es gab eine enorme Menge an Menschen die plötzlich angefangen haben Geld zu investieren fremdes Geld Banken Geld zu nutzen und es kam zu einer Art Spekulationsblase und das wenn ich das anschaut dann die Menschen sich zwar ein bill Geld gewünscht sie haben aber massenhaft Kredite aufgenommen und jetzt wird das Ganze sich umkehren so wird zusammenbrechen weil jetzt werden die Zinssätze weiter erhöht und eine Sache die ihr vielleicht gehört habt eine Sache die viele deutsche Unternehmer als Problem hatten ihr habt euch darauf verlassen dass das die Zinssätze ewig niedrig bleibt ihr habt aber jetzt Kredite wo irgendwann anfangen wird das so wie die Prognosen das sagen dass die Zinsen ansteigen da müsst ihr mit einer höheren Rate das Zurückzahlen es ist so dass unter anderem das gesagt wurde das dann Prognosen das bis Ende des Jahres dass die Inflation auf 8,7 % liegt das heißt dass die Preise dementsprechend gesteigert werden sollen das war ein Königreich das wird dadurch dass eine Sache die wir sagen können die höchsten Zinssätze aller entwickelten Länder haben und es wird höher sein als der Zinssatz jetzt mit dem Fett pflanzensatz der bei 5 % liegt und das ist schlechte Nachrichten denn je höher die Zinssätze steigen desto stärker wird der Wohnungsmarkt brechen und die Unternehmen oder die Wirtschaft die Konjunktur die wird sich noch weiter langsam diese Zusammenbrüche von Stürmen wird die britische Wirtschaft schmettern und die Rezession ist so gut wie garantiert und wir wissen das weil wir zuverlässigste Indikator für eine Rezession und Vereinten Königreich der schreibt förmlich nach Rezession ihr habt das vielleicht gehört es gibt die Rendite Differenz das heißt den hier spread und für die UK online befindet er sich derzeit auf extrem niedrigen Niveau er liegt unter 100 Basispunkten das heißt das für euch das heißt die Rendite der zehnjährige Staatsanleihen ist weiter unter diejenigen der zweijährigen gefallen und der Rückgang jetzt noch extremer als der Rückgang 2008 das ist ein Punkt wo wir alle sagen müssen Moment es gibt überhaupt keinen Sinn warum kriege ich mehr Rendite wenn ich das Geld kurz anlege das zeigt euch immer dass das irgendwie verrückt spielt dass die das irgendwas da nicht stimmt im Grunde genommen geht ihr ja in höheres Risiko mit einer höheren mit einer höheren Anlagezeit geht ein aber in diesem Fall ist es so dass ihr eine höhere Rendite bekommt das und Rendite kommt von Risiko wenn ich kürzer anlegt also hier merkt ihr jetzt die Märkte spielen verrückt und das liegt daran die Anleger haben so viel Angst vor einer Rezession dass sie ihre zehnjährigen annehmen dass sie die langfristig drängen und ihre Gelder binden wollen aber gleichzeitig verlieren sie den Glauben an die britische Wirtschaft man hat einfach bessere Orte gefunden um Geld zu binden und wir können das beobachten wir können sehen dass die dass die Kosten dass die Kreditkosten Vereinten Königreich im Vergleich zu den G7 Ländern wie dem Vereinigten Staaten und sogar zu Deutschland verglichen gestiegen sind das heißt ein Kredit ist um 25 Basispunkte teurer als in Amerika und fast 200 Basispunkte teurer als in Deutschland und das sind schlechte Nachrichten der die Industrien im Vereinten Königreich werden Kapital zu bekommen weil es einfach zu teuer ist im Gegensatz dazu können amerikanische und sogar deutsche Unternehmen günstigeres Geld bekommen um den Sturm zu überstehen als Investoren offensichtlich damit welche Märkte man sein Geld über Antwort trauen möchtest du es Wirtschaft ist eine weit bessere Wirtschaft als das vereinte Königreich und ja das ist der Hauptgrund warum ich glaube dass uns eine Rezession im Verhalten Königreich bevorsteht und auch wenn das Baby im ersten verteilen mit 0,1% positiv waren glaube ich nicht das Großbritannien in einer schrumpfen im dritten oder im vierten Quartal vermeiden kann deswegen ich glaube noch mal dass wir vor einem massiven Salami an Hypothekenfinanzierung stehen und dass das Ganze bald aufbrechen wird es gibt ein erschütternden Bericht von The Guardian und er hat gesagt dass 2,4 Millionen Hypotheken jetzt vor der Refinanzierung stecken vor höheren Zinssatz ich das gesagt es gab günstiges Geld jede Familie ist hat sich überlegt Mensch hier man könnte das das was wir erarbeitet haben und da könnte man ein Kredit aufnehmen es gibt keinen besseren Zeitpunkt um Geld aufzunehmen dass die Menschen aber kurzfristig denken dass ich diese Zeiten irgendwann ändern das wurde hier nicht bedacht und jetzt stehen wir davon dass Menschen dann plötzlich vor Kosten stehen diese nicht kennen jetzt wenn wir für diesen Refinanzierung stellen dann lass uns da ein Beispiel machen falls ihr jetzt beispielsweise eine Hypothek abbezahlt hätte dann könnte es gut sein dass das Ganze von Tausend und dir vor diesen Problemen bezahlt hat dass sie jetzt dass das Ganze auf 1.300 von steigt das ist eine riesen Erhöhung das bedeutet ihr versteht vielleicht das Ausmaß das Problems es gab vor wenigen Jahren vor sieben Jahren hat vermehrt hat man angefangen Kredite aufzunehmen und man wollte das ganze mit niedrigen Zinsen machen und jetzt plötzlich werden alle neu bewertet und wenn ihr vorher schon finanzielle Probleme hattet dann kommt jetzt die Unsicherheit auf dem Arbeitsmarkt und das ganze wird wieder zusammenbrechen und dass das was wir hier als Teil des grünen Diagramms sehen werden ihr seht dort sind die variablen Zinssätze repräsentiert und diese haben dramatisch drastisch abgenommen für fest sind Hypotheken das ganze geht übrigens auch für fünfjährige fest sind Hypotheken die in den letzten sieben Jahren stark gestiegen sind und es gibt eine große Anzahl an Hypotheken welche zu niedrigen Zinssätze für eine längere Zeit festgeschrieben sind und über 80% der Hypotheken Darlehen müssen früher oder später geht finanziert werden es besteht also eine sehr sehr hohe Wahrscheinlichkeit dass dies früher oder später zum massiv hören muss und dass der Grund warum Kreditnehmer jetzt vor einem von der riesigen Hypotheken Schockwelle stehen und das kann Hässlich werden und dass das was ihr bedenken müsst wenn ihr zu einem Zinssatz Leid dann muss das nicht unbedingt zum Leitzins stehen weil die Leute werden jetzt wenn die Zahlen müssen das sehen wir da sechs oder sieben Prozent zahlen wenn du zur Bank gehen und Kredit aufnehmen und es ist faktisch jetzt so dass Sie also vor einem Problem stehen das ist nur zu explodieren scheint weil wenn ich das anschaut in dieser Grafik sehen wir das dezember 2023 über 2,8 Millionen Hypotheken ihre festzinsphase beenden werden und diese Situation wird noch schlimmer bis 20 25 werden über 4,4 Millionen Hypotheken zu hören Zinssätzen refinanziert werden und es gibt keinen Ausweg das heißt wenn ihr jetzt eine neue fest sind Hypothek aufnimmt dann sind sie erledigt für das nächste Jahr das zweifach oder vielleicht sogar dreifache zahlen wie sieht's mit variablen Zinssätzen aus ihr könnt ja auch sagen okay Moment was ist richtig hinsetzen nicht festsetzen was ist wenn ich bei einem variablen Zins bleibe ihr könnt darauf hoffen dass die Wirtschaft besser wird aber es kann auch sein dass ich das ganze viel viel schlimmer für äußert die Zinsen Einschränkung das sind noch mehr Zeit also das hier ist jetzt eine Situation bei der Menschen die ihr Leben lang gespart haben alles zu verlieren scheinen das sind Dinge die wir nicht besprochen haben als dann um die Sanktionen normal wenn wir jetzt auf die Märkte zu sprechen kommen dann wetten die Märkte darauf dass die Bank auf England gezwungen sein wird den Leitzins auf 6,25% anzuheben das bedeutet dass die Bank Zinsen am Ende leicht bei 7 bis 8 % liegen werden das wäre ein Albtraum für Kreditnehmer die Kreditnehmer stecken so in der Zwickmühle sondern heute höhere Zinssätze für die nächsten 5 Jahre festlegen oder sondern bei einem bei einer Variablen kreditvereinigung des Risiko bei der Bank of England eingehen wenn die Zinssätze dann weiter steigen dann wenn sie doppelt in der Klemme stecken und das ist ungefähr so schlimm wie Dinge für ein Haushalt werden können das heißt lasst uns diesen Albtraum einmal quantifizieren bis 2026 sollen die jährlichen Auszahlung um 15,8 Milliarden von steigen und bis 20 24 durchschnittlich aushalten eine zusätzliche Erhöhung der hypothekenzahlung um 1900 verkauften müssen noch mal der durchschnittliche Haushalt wird bis 1900 mehr zahlen müssen das bedeutet monatlich wenn es ausrechnet eine zusätzliche Belastung von 300 von Monat für jeden x normalen Menschen da wird es Herausforderung für kein Wohlstandsgewinn etc das heißt die Ausgaben für den frei verfügbaren Konsum wenn einbrechen und sind massive Einschnitte geben anders geht es nicht die Leute haben weniger Geld also britische Haushalte Schränken jetzt schon ihren ihren Konsumer in ihre Luxusgüter etc und das Einsparen startet bei Kleidung geht weiter über Reisen über Luxusgüter und es ist einfach nicht genug Geld für das ganze fahren und was wir deswegen sehen ist hier wie der Konsum der Verbraucher einbricht und das ganze wird noch schlimmer werden soweit die refinanzierungswelle losgeht die Dinge werden dann wirklich schlecht weil rekapitulierend ist so dass die Briten jetzt mehr Geld ausgeben müssen aber das ist nicht alles der durchschnittliche Verdienst der dritten ist in den letzten Jahren deutlich gesunken Grafik einblenden und dann seht ihr den Einbruch des Lebensstandards der ist schlimmer als die unmittelbare Krise von 2008 und der Lockdown von 2020 das Durchschnittseinkommen ist seit Mitte 20 22 und fast vier Prozent gesunken und das wird noch schlimmer laut dem Office von Budget das kommt ability wird das reale verfügbare Haushaltseinkommen in den nächsten Jahren um 5,7% einbrechen das ist die größte Rückgang seit dem Zweiten Weltkrieg und deshalb sage ich immer das Inflation das Schreckgespenst ist sobald es aus der Flasche gelassen wird wird es wirtschaftliche Verwüstung Anrichten das Verbraucher Ausgabeverhalten ist von entscheidender Bedeutung für das Wirtschaftswachstum und in den letzten zehn Jahren machen die Haushaltsausgaben mehr als 60% des BP entfalten Königreich aus wenn die Verbraucher anfangen den Gürtel enger zu schneiden wird das BP Wachstum stecknieren oder sogar schrumpfen schaut euch die schockierende Statistik an im Jahr 2022 sind die verfügbaren Einkommen der britischen Haushalte um 0,6 % auf 32.300 gesunken aber der größte Rückgang kann bei den Armen die muss um 3,8 % eingebrochen ist und das alles passiert noch vor der großen hypothekenzeit Bombe die kurz vor der Explosion steht und wir wissen dass die Hypotheken rief Finanzierung denn Verbraucher und 300 Pfund im Monat belastend das verfügbar reinkommt außer sie singt also weiter und ein großer Teil musst du die hypothekenzahlung oder für die Miete aufgewendet werden das ist der Grund warum der Konsum die Verbraucher abstützen wird soweit der Tsunami der Refinanzierung losbricht die Dinge werden wirklich schlecht entfalten Königreich hier soll ein Artikel von Blumberg der berichtet dass die britischen Banken vor einer zwölf monatigen zwangsversteckungspause dass die zugestimmt haben das ist eine bedeutsame Warnung für die britische Wirtschaft den Banken sind selten nachsichtig und die Banken haben sich jetzt darauf geeinigt dass Menschen eine Gnadenfrist von 12 Monaten eingerichtet wird jetzt verkürzt und sollten Sie dann die hypothekenzahlung nicht mehr leisten können dann wird das Ganze um höchstens ein Jahr verzögert und das tut man sicherlich wenn die Verbraucher stark sind der einzige Grund warum Jeremy Hand eine 12 Monate Pause durchgesetzt hat ist weil die Verbraucher derzeit schwach sind und dieses Mal wird aber keine Unterstützung geben das wird keine finalen Gelder geben der Staat kann nicht eingreifen sondern die britische Regierung kann sich ein Geldgeschenk zum jetzigen Zeitpunkt einfach nicht mehr leisten die britische Regierung ist praktisch breite man das Gebäude von den von den hohen Energiekosten die man selber herbeigeführt hat und die einzige Möglichkeit die man jetzt eigentlich noch hat ist diesen Sturm zu durchfahren aber gut sehe ich nicht dass das ganze endet es gibt ja einfach zu viele Probleme die dastehen es gibt einfach zu viel Nebenwirkungen die dann dazu führen dass am Ende ein großer kallax kommt und wir sehen jetzt hier wie eine der größten Nationen faktisch sich immer mehr radikalisiert einfach weil sie merken dass das Ganze schwierig ist und das ist das was ich dazu denke ich bin gespannt wie ihr das seht bis zum nächsten Mal</t>
+  </si>
+  <si>
+    <t>ehfKPooubfU</t>
+  </si>
+  <si>
+    <t>Operation porschenko hatte die Chance alles zu wenden unter anderem auch selensky du bist doch ganz neu du bist nicht verantwortlich für das was vorher passiert ist dann setzt dich doch mal hin und denk nach was besser ist für den eigenen Staat für sein eigenes Volk also warum führst du jetzt diesen Krieg ich habe ihn extra diese Karte mitgebracht also jetzt wird Russland euch dort zermahlen das Personal und die Technik all diese motivierten und ideologisch eingestellten Nazis Simon sie nennt diese ideologisch gefestigten Leute sind gar nicht mehr da sie sind alle schon gestorben wer kämpft da jetzt diejenigen die hier auf den Straßen einfängt und hierher bringt sie sind nicht vorbereitet ja und auch ein paar Militär sind darunter sie werden mit dieser Maschinerie nicht fertig werden russland hat sich umgestellt heute sind an der Frauen schon die modernsten Waffen jetzt gibt es auch keinen Mangel mehr an Drohnen inzwischen ist das schon eine ganz andere Armee und das aller gefährlichste ist also ich weiß ja nicht ob ich ihn das sagen soll oder nicht sie haben ein freiwilligen Korps von 250.000 Mann russland hat 250.000 ein freiwilligen Korbs welches jetzt vorbereitet ist und sich in der Reserve befindet verstehen sie das was das heißt 250.000 Mann die Russen haben jetzt gerade weniger an der Front und da sitzen sie in der Verteidigung und das nicht weil sie nicht in der Lage sind anzugreifen sie brauchen es einfach nicht und ihr rennt verstehen sie wie oft Drogen und alkoholisiert stürmt ihr einfach darauf los so wie man die Deutschen damals in den Filmen gezeigt hat er rennt auf die Barrikaden zu aber ihr schafft es noch nicht einmal und das sehen wir und das ist auch so ihr kommt ja noch nicht einmal bei den Minenfeldern an ihr werdet einfach zu Tausenden vernichtet ihr habt während der Gegend Offensive in dieser Zeit 45.000 Mann Tote und 45.000 und sie verteidigen sich und ihr habt Verluste im Verhältnis von eins zu acht eins zu acht sind die Verluste an der Front und 250.000 in der Reserve und die sind ausgestattet mit der modernsten Technik also sie werden euch hier erstmal zermalen und danach werden sie das tun was ihr am meisten fürchtet und die Führung sie marschieren in Richtung Moldau und transvestieren und dann schneiden Sie euch ab was werdet ihr dann machen und hier genau hier im Westen reiben sich die Polen schon die Hände an geschüttet von den Amerikanern sie werden euch den Westen abschneiden und für euch wird dann nur dieses Stück hier übrig bleiben wenn überhaupt das wird mit euch passieren und den Start Ukraine unseren gemeinsamen Staat Ukraine wird es dann nicht mehr geben das Heimatland von uns von ihnen und von mir ist das denn schon ein Stein gemeißelt diese Geschichte also wenn ihr jetzt nicht anhaltet dann wird das passieren wenn ihr euch jetzt nicht an den Verhandlungstisch setzt und Russland bietet das ja an aber ihr wollt nicht also wenn ihr nicht wollt dann halt nicht die Kraft Russlands wird ausreichen und kein Westen wird euch hier helfen man muss den Kopf in die Hand nehmen und Handeln ausgehend von den Realitäten aber Handeln im Interesse dieses riesigen schönen Territoriums Alexander gregoryovic also noch mal um das hier zu fixieren sie haben von den 250.000 gesprochen und so wie ich es verstehe sind das die die nach Odessa marschieren könnten warum dann nur nach Odessa also erstens setzen sie euch hier im Gebiet Hardcore ordentlich unter Druck also hier setzen sie euch unter Druck und hier sind die Russen einmal erfolgreichsten sie rücken vor sie fahren schon gegen offensiven gegen euch wir haben gestern erst unsere Leute das vorgetragen wir sehen das ja was dort passiert wir sehen die gesamte Front nicht mit den Augen der Russen wir sehen das der wesentliche Krieg sschauplatz ist rund um bachmut dort finden gerade schwere Kämpfe statt hier im Süden schon weniger dort hat sich die Frauen schon stabilisiert aber hier bei Kalkhoff drehen sie euch zurück und wenn sie aus der regionalkauf Richtung hier ist marschieren was werdet ihr dann tun hier gibt es ja nicht solche Hindernisse von daher werden sie auch hier ihre Hauptstadt neutralisieren aber das aller gefährlichste ist wenn Sie von hier und jetzt sonnenlos schlagen in diese Richtung von welchem Zeitrahmen kann man denn hier sprechen wann kann das geschehen also das weiß ich nicht das wird auch davon abhängen inwieweit ihr in der Lage sein werdet hier zu kämpfen und hier habt ihr nicht mehr ganz so viel übrig 45.000 also das sind ja nur ungefähre Angaben und wie viel Technik wurde schon verbrannt der Westen beginnt auch schon langsam zu verstehen dass hier nichts bei rumkommen wird selbst mit der Hilfe des Westens wird die Ukraine das nicht durchstehen können</t>
+  </si>
+  <si>
+    <t>WJZweaHpepA</t>
+  </si>
+  <si>
+    <t>China und die USA haben der us-finanzministerin Janet yellenzufolge Fortschritte gemacht und sahen in der Lage eine gesunde Beziehung zu führen kein einzelner Besuch wird unsere Herausforderungen über Nacht lösen aber ich hoffe dass mit dieser Reise ein solider und produktiver Kommunikationskanal mit Chinas neuem Wirtschaftsteam aufgebaut wird sagte yellen am Sonntagmorgen in China vor ihrer Abreise 10 stündige bilaterale Treffen mit hochrangigen chinesischen Beamten in den vergangenen Tagen sein direkt substanziell und produktiv gewesen die Vereinigten Staaten und China haben erhebliche Meinungsverschiedenheiten diese müssen klar und direkt kommuniziert werden aber Präsident beiden und ich sehen die Beziehungen zwischen den USA und China nicht im Rahmen eines Großmacht Konflikts wir glauben dass die Welt groß genug ist damit unsere beiden Länder gedeihen können so yellen die USA würde in allerdings Bedenken über bestimmte wirtschaftspraktiken weiterhin direkt kommunizieren und gezielte Maßnahmen zum Schutz ihrer nationalen Sicherheit ergreifen</t>
+  </si>
+  <si>
+    <t>z79qg_YTd2M</t>
+  </si>
+  <si>
+    <t>die Ukraine sollte nach Auffassung von Nato-Generalsekretär Jens deutenberg jetzt ein deutliches Signal für eine Aufnahme in die transatlantische Allianz erhalten daher sollte das Bündnis auf den sonst üblichen membership Action planen zu Heranführung von Beitrittskandidaten im Fall der Ukraine verzichten sagt es deutenberg vor Beginn des Nato-Gipfels in Vilnius die Ukraine hat einen langen Weg zurückgelegt seit wir 2008 beschlossen haben dass der nächste Schritt einen Aktionsplan für die Mitgliedschaft sein würde die Ukraine ist der Napo viel näher gekommen also denke ich dass es an der Zeit ist dies auch in den nato-beschlüssen wieder zu spiegeln der russische Angriffskrieg gegen die Ukraine steht im Mittelpunkt des zweitägigen NATO-Gipfels in der litauischen Hauptstadt dabei will die Nato festlegen wie die Ukraine konkret an die transatlantische Allianz herangeführt werden kann am Ende dieses Prozesses soll der Beitritt des Landes zu dem Militär Bündnis stehen dass die Ukraine zur Kriegszeiten Mitglied werden könnte schließt die Allianz aus wie genau der Prozess einer weiteren Annäherung ausgestaltet werden und welche Sicherheitsgarantien die Ukraine nach einem Ende des Kriegs erhalten soll blieb bis zuletzt allerdings offen die Regierung in Kiew wir auch zahlreiche osteuropäische NATO-Staaten wollen einen möglichst verbindlichen Fahrplan bis zur Mitgliedschaft festzurren die USA und auch Deutschland sind diesbezüglich skeptisch und bevorzugen einen zurückhaltenden weg</t>
+  </si>
+  <si>
+    <t>iriTxAs0QNo</t>
+  </si>
+  <si>
+    <t>die ampelfraktion haben unterschiedlich auf die von bundesinnenministerin Nancy fazer angekündigten punktuellen stationären Grenzkontrollen zu Bekämpfung illegale Einwanderung reagiert wenn das Innenministerium die Innenministerium Innenministerin sagt es geht darum die schleuserkriminalität einzugrenzen und das können wir mit diesen Mitteln ohne wiederum auch die Polizei zu überfordern so ist das ein Teil möglicherweise auch eines konstruktiven Weges wenn wir überall stationäre Kontrollen machen würden Personal abziehen was woanders gebraucht wird an Bahnhöfen an vielen anderen Orten und deshalb ist für mich und uns klar die einfache Antwort kann nicht einfach sein stationäre Grenzkontrollen überall weil einfach klar ist dass wir so ein sowohl für den Lebensalltag von Menschen eben der Freizügigkeit in Europa massive Probleme kriegen es geht ganz konkret um Polen und Tschechien gleichwohl natürlich vorübergehende Grenzkontrollen nur eine Notfallmaßnahme sein können mittelfristig brauchen wir ein eu-außengrenzenschutz ich sagte vorhin auf europäischer Ebene könnte dieser Durchbruch jetzt endlich gelingen Phaser selbst äußerte sich am Dienstag bei einem Besuch im Frankfurter Bahnhofsviertel zu dem Thema also ich habe mich für zusätzliche Grenzkontrollen ausgesprochen die Schleierfahndung in der Fläche muss bleiben sein ganz wichtiges Element der Grenzkontrolle und ich habe meine Zusammenarbeit wie sie gestern auch der DP1 nehmen konnten mit den Nachbarländern noch mal intensiviert ich habe mit Tschechien jetzt den Beginn dieser guten Zusammenarbeit die ich mit der Schweiz habe wo wir die meisten Zurückweisung haben wie Sie wissen insofern ist das ein wichtiger Schritt für mehr Begrenzung der irregulären Migration unionsfraktionschef Friedrich Merz forderte die Innenministerin auf die Grenzkontrollen in Brüssel auch zu notifizieren und sie nicht nur anzukündigen allerdings hieß es in Regierungskreisen dass dies gar nicht nötig sei denn geplant seien nur vorübergehende stationäre Kontrollen auf Schleuse Routen die dann alle paar Tage die Orte wechseln sollen dies sei nicht anzeigepflichtig in der EU</t>
+  </si>
+  <si>
+    <t>n-kaYmTYpA8</t>
+  </si>
+  <si>
+    <t>[Musik] guten Morgen da sind wir wieder und wie schön dass Sie diesen Tag mit uns beginnen hier ist der FAZ frühdenker heute ist Montag der 14 August und das sind die Nachrichten an diesem Morgen im Berufungsprozess um Schmerzensgeld nach einer corona-impfung könnte das Urteil fallen nach der Feuersbrunst von Hawaii ermittelt die Justiz und zum Ende der Sommerferien in vielen Bundesländern stellt sich die Frage nach einem Handyverbot an den Grundschulen gleich mehr dazu vorher noch sie wissen das die Kurzmeldungen der Nacht in der Nacht gab es erneute Angriffe auf Odessa durch russische Raketen und Kamikaze Drohnen Anna Lena bärburg hat ihre Reise nach Australien vorerst abbrechen müssen nach einer Zwischenlandung zum Auftanken in Abu Dhabi musste die Maschine mit der Außenministerin an Bord wegen technischer Probleme umkehren Doppelnamen ohne Bindestrich die auch an die Kinder weitergegeben werden können Paare sollen künftig wesentlich größere Freiheiten bei der Wahl eines gemeinsamen Nachnamens haben das Gesetz soll Ende des Monats verabschiedet werden und bei den Wahlen in Ecuador ersetzt einen Journalist den kürzlich ermordeten Kandidaten [Musik] die Redaktion heute früh hat Sebastian Balster ich bin Jan malte Andresen in allen einen schönen Montagmorgen [Musik] muss Astra Seneca Schmerzensgeld zahlen heute gibt es wohl die Antwort auf diese Frage das Oberlandesgericht Bamberg will über den Fall einer Klägerin entscheiden die nach einer corona-impfung eine Darm Venenthrombose erlitten hat sie lag mehrere Tage im Koma und leidet seitdem unter Schmerzen und Depressionen sie wirft astrasenica vor das Thrombose-Risiko systematisch verharmlost zu haben für die Impfung habe es kein positives nutzen risikoverhältnis gegeben das Thema Risiken und Nebenwirkungen war ja schon bei dem Vertragsverhandlung im Raum das war der Grund warum die Farbenindustrie doch verstanden hat dass sie die Haftung nicht haben wollen das heißt aber im Umkehrschluss dann mussten noch eine bescheid das Risiken gibt das sagte der Wiesbadener Anwalt Joachim Caesar Preller der ARD er führt für seine Mandanten momentan mehrere Prozesse in Deutschland gegen Corona Impfstoffhersteller das tut er zwar nicht den Bamberg aber falls die Richter dort heute ein Urteil verkünden wäre es das erste in einem Berufungsverfahren wegen vermuteter corona-impfschäden in erster Instanz wurde die Klage nämlich abgewiesen Astra Senica argumentiert die Klägerin sei zum Zeitpunkt der Impfung hochgradig adipös gewesen und habe ein sehr hohes Risiko eines schweren Verlaufs einer corona-infektion gehabt zudem sei der Zulassung des Impfstoffs eine Studie mit mehr als 24.000 Probanden vorausgegangen die keine Hinweise auf einer erhöhtes vorkommen thrombotische Ereignisse ergeben habe die Zahl der Klagen wird in ganz Deutschland auf etwas mehr als 200 geschätzt bei rund 64 Millionen geimpften in der Bundesrepublik Deutschland steht eine ausgiebige Debatte um die Lieferung von Marschflugkörpern an die Ukraine bevor danach klang jedenfalls was Bundeskanzler Olaf Scholz am Abend in seinem Sommer Interview mit dem ZDF sagte der Vergangenheit werden wir viele einzelne Entscheidungen immer sehr sorgfältig überprüfen was geht was Sinn macht was unser Beitrag sein kann wir erinnern uns im Fall von Panzern Flugabwehrraketen und Kampfflugzeugen hatte dieses sorgfältige überprüfen Wochen lang gedauert dazu kommt die Ampelkoalition ist sich in der Sache uneins während der Kanzler des zögern zur Tugend erklärt haben sich führende Politiker von FDP und Grünen am Wochenende dafür ausgesprochen die von der Ukraine erbetenen Flugkörper vom Typ Taurus umgehen zu liefern Taurus kann Bunker in bis zu 500 km Entfernung zerstören der ukrainische Außenminister Kollegah sagte der Bild am Sonntag sein Land brauche zur Verteidigung gegen Russland diese Taurus Flugkörper um mehr leben ukrainischer Soldaten und Zivilisten zu retten eine größere Reichweite der Raketen bedeutet eine kürzere Dauer des Krieges kannst der Scholz sieht sich in dessen seinem zögern bestätigt und mein Eindruck ist die Bürgerinnen und Bürger das in der ganz großen Mehrheit sehr sehr richtig finden das nicht jedes Mal wenn einer irgendwo in einer irgendwo in einem Gesprächen fragt und sagt das noch das noch dann immer gleich gesagt und ja sondern dass wir uns schwer machen wir werden es uns weiter schwer machen sollten Handys in der Schule verboten werden das ist eine Debatte heute in der FAZ pünktlich zum Schulbeginn diese Woche nun auch in Bremen Niedersachsen und Sachsen-Anhalt deutschlandweit gibt es keine einheitliche Regelung ob Handys in der Schule benutzt werden dürfen das liegt bisher jede Schule selbst fest eine Realschule in Nordrhein-Westfalen hat gute Erfahrungen damit gemacht Handys vor dem Unterricht einzusammeln dem ZDF sagten Schüler ich fand es erst ein bisschen doof das ist ja auch das unser Handy meint ja auch ein Recht auf das eigene Handy einmal so über denkt was so alles passiert ist es gab Schlägereien es wurde gefilmt natürlich schon besser jetzt mit diesem Handyverbot es wurde auch viel mehr Fotos von Lehrern Schülern auf der Toilette Videos halt so Sticker von Whatsapp hergestellt ein generelles Handyverbot gilt in keinem der 16 Bundesländern aber das könnte sich ändern Schleswig-Holsteins Bildungsministerin Karin Prien gleichzeitig stellvertretende CDU Bundesvorsitzende sieht die Handynutzung kritisch Kinder brauchten dringend Räume in denen sie sich auch ohne digitale Endgeräte bewegen könnten in der FAZ von heute kündigt Prien an ein Verbot von Handys in Grundschulen zu prüfen ein Vorbild für eine strengere Regelung findet sich in Frankreich an den Schulen dort dürfen Schüler bis zum Alter von 15 keine Mobiltelefone benutzen viele viele offene Fragen jetzt ich glaube ich lebe immer noch in einer in einem Vakuum wo ich eigentlich wirklich noch nicht realisiert habe was wirklich passiert das sagte ein deutscher Auswanderer der auf der hawaiianischen Insel Maui ein Restaurant betrieben hat auch das ist der verheerenden Feuersbrunst vergangene Woche zum Opfer gefallen heute hören wir die Justiz ermittelt denn in der zu großen Teilen zerstörten Stadt La Heiner gibt es mehr und mehr Kritik am Katastrophenschutz zu Beginn der Brände seien keine waren Sirenen zum Einsatz gekommen und die von den Behörden per Mobiltelefon Radio und Fernsehen verbreiteten Warnungen hätten nicht alle Bewohner erreicht doch am Donnerstag habe es geheißen das Feuer sei unter Kontrolle wir haben dann mehr oder weniger Notfallplan gemacht weil die Straße die kleine Straße wegen den Telefonleitungen mehr oder wenig gespart worden und viele Autos haben probiert draußen zu fahren weil das der einzige Weg war und das Restaurant so ungefähr 120 m vom Meer fahren also wir haben uns einfach gedacht im schlimmsten Falle wenn wir einfach ins Meer und und schützen uns auf dieser Art und Weise mehr als 2000 Gebäude wurden zerstört mindestens 93 Menschen sind gestorben das war bis gestern die Bilanz der Brandkatastrophe die am Dienstag begonnen hatte bislang ist nicht klar was die brennende verursacht hat einige Fachleute äußerten die Vermutung umgestürzte Strommasten könnten zu dem Feuer geführt haben der DAX bekommt einen neuen Spitzenverdiener regelmäßig berechnen die deutsche Schutzvereinigung für wertpapierbesitz und Forscher von der TU München was die DAX-Konzerne ihren Vorständen gezahlt haben heute werden die Ergebnisse für 2022 vorgestellt im Jahr zuvor lag Steve Angel vom Gase Hersteller Linde an der Spitze der Tabelle mit einem Jahresverdienst von 19 Millionen Euro in diesem Jahr wird auf jeden Fall ein anderer Name ganz oben stehen denn Angel hat seinen Posten geräumt und Linde auch den Dachs verlassen weil 2022 viele DAX Unternehmen hohe Gewinne erzielt haben dürfen die Manager Gehälter insgesamt gestiegen sein vorne in der Rangliste erwartet werden der Chef von Merc Oliver Zipse von BMW und Theodor Weimer von der Deutschen Börse auch fünf Jahre danach sind es Bilder die einen das Blut in den Adern stocken lassen ein Augenzeuge sieht wie die Autobahnbrücke von Genua einstürzt um 11 Uhr 36 am 14 August 2018 brach die Morandi Brücke auf 250 Metern Länge zusammen mehr als 30 Autos und drei Lastwagen stürzen in die Tiefe 43 Menschen kamen ums Leben dieser Mann hatte Glück er konnte seine LKW kurz vor der Abbruchkante stoppen das ist meiner da vorne ich habe es krachen gehört bin ausgestiegen und gerannt nicht lange nach dem Einsturz stellte sich heraus dass ich die 1967 fertiggestellte Brücke in einem schlechten Zustand befand und dass die private Betreibergesellschaft darüber schon länger Bescheid wusste das Verfahren gegen 59 Angeklagte den eine Mitschuld am Einsturz der Brücke vorgeworfen wird hat vor einem Jahr begonnen die Sprecherin des Opferverband sagte der Arda angefangen haben eine enorme Arbeit geleistet aus unserer Sicht mit all den Informationen die vorliegen könnte man den Prozess schon abschließen weil der rote Faden ist klar der zum Zusammenbruch geführt hat viele Leute von einem schnellen Ende des Prozesses kann aber keine Rede sein beobachter rechnen damit dass ein Urteil erst in fünf Jahren fallen könnte heute gedenken Politiker und Hinterbliebene der 43 Toten im Hafen von Genua lassen um 11:36 Uhr alle Schiffe ihr Horner klingen während dem Flusstal eine schweige und Trauerminute eingehalten wird und dann lassen Sie uns wie immer montags noch kurz darauf schauen was in dieser Woche wichtig wird das Bundeskabinett trifft sich am Mittwoch zu seiner ersten Sitzung nach der Sommerpause die Themenliste ist lang Waffenlieferungen in heizungsgesetz und Cannabis Legalisierung stehen zum Beispiel auf der Tagesordnung am Donnerstag kommen die südafrikanischen Staats- und Regierungschefs zu einem Gipfel zusammen am Freitag beginnt die neue Bundesliga-Saison mit dem Spiel der Bayern in Bremen nur noch vier Tage zeit also für spitzenstürmer Harry Kane seine neuen Bayern Kollegen kennen zu lernen place on the Harry Kane gestern bei seiner offiziellen Vorstellung in München am Sonntag dann Hessenderby in der Bundesliga Eintracht Frankfurt gegen Aufsteiger Darmstadt und auf der anderen Seite der Erdkugel wird das Finale der Frauenfußball WM ausgetragen das war's für uns an diesem Montag morgen heute Nachmittag gibt's wie immer den FAZ Podcast für Deutschland und den nächsten frühdenker mit den Nachrichten am Morgen dann morgen früh wieder ab 6 bis dahin einen schönen Tag [Musik]</t>
+  </si>
+  <si>
+    <t>5FhGc-P_Vms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Musik] zusammen in das Setting hier diesen schönen wir haben extra ein bisschen Strand für sie aufgebaut herzlich willkommen moin zum kanzlergespräch zum ersten kanzlergespräch mit dem Bundeskanzler Olaf Scholzen großen Applaus gab es schon vielen Dank herzlich Willkommen an alle Gäste hier im Publikum und auch an die Zuschauer die uns heute Abend mit begleiten schön dass Sie alle da sind und dass sie heute die Möglichkeit auch haben ihre Fragen zu stellen die Ihnen auf dem Herzen liegen 100 55 Gäste haben wir hier Sand unter den Füßen so ein bisschen Wind im Haar und das Wasser vor der Nase so gehört das hier in Lübeck in der Hansestadt wir sind hier im strandsalon und die Fragen dürfen Sie gleich Stellen an unseren Bundeskanzler Olaf Scholz und sein Gastgeber möchte ihn auf die Gelegenheit geben ein paar Worte zu sagen zu Begrüßung moin moin befühle mich hier ziemlich wohl zu Hause im Hafen ist da Hanse ist auch da hier erinnere mich an Willy Brandt also es passt alles zusammen das Wetter ist auch sehr gut das letzte Mal als ich hier war was irgendwie auch warm aber es war alles drin und dunkel und insofern sehe ich jetzt wie es hier wirklich aussieht und das gefällt mir wir haben Licht und Sonne das ist schön tatsächlich es ist der Auftakt zu einer ganzen Reihe von kanzlergesprächen die es mit dem Bundeskanzler geben wird in den kommenden Wochen und Monaten heute der Auftakt hier in Lübeck dann in den anderen 15 Bundesländern auch Termine und die Chance den Bundeskanzler zu sprechen ins Gespräch zu kommen in größeren und kleineren Städten auch im ländlichen Raum warum Herr Scholz ich sind es wichtig mit den Menschen ins Gespräch zu kommen die beste Form sich über Probleme und Sorgen die man hat auszutauschen ist dass man miteinander redet und das muss ja auch real möglich sein und insofern hoffe ich dass wir hier auch ein gutes Gespräch statt Zustande kriegen das Gucken zwar zu aber man sollte es so machen als wären wir ganz alleine und dazu möchte ich sie auch gerne muntern dass keine Frage offen bleibt und wir möglichst viele Fragen miteinander besprechen können Vertrauen entsteht dadurch dass man erläutert was man auf dem Herzen liegt was man im Kopf hat das gilt für diejenigen die regieren genauso wie für die Bürgerinnen und Bürger 150 in Lübeck ausgewählt ausgesucht und hergestellt durch die Lübecker Nachrichten das ist ja unsere Zeitung vor Ort das heißt die Fragen sind jetzt auch nicht vorher gecheckt oder getestet worden sondern hier ist alles frei zu fragen an den Bundeskanzler heute Abend eine Frage habe ich noch warum starten wir denn in Lübeck warum haben wir die Ehre in der Hansestadt ich habe es ja eben schon gesagt das gibt viele Dinge die mich hier heimisch sein lassen Willy Brandt habe ich erwähnt der hat hier seine Jugend verbracht es geht um den Hafen die Hanse das finde ich auch gut und hat jemand der in Hamburg aufgewachsen ist und da mal die Stadt regieren dürfte weiß ich auch was für ein Scham solche Städte haben und ich bin gespannt Kanzler richten oh da gehen die Arme hoch herrlich wir haben Mikrofone die kommen einmal ins Publikum direkt bitte so lange immer warten und ich würde gerne einmal bitten den Herrn hier im blau-weiß gestreiften Hemd zu hören dauert eine Sekunde dann ist das Mikrofon da und dann dürfen sie die Frage gerne direkt an den Bundeskanzler stellen ist der Ton da ja mein Name ist Wolfgang Kurs ich komme aus Hamburg Berge bei Lübeck und bin gestern ein 80 Jahre alt geworden ich freue mich sehr dass ich hier sein darf sehr geehrter Herr Bundeskanzler ich denke wir alle teilen im Augenblick dieselbe Frage woher nehmen sie den Mut die Kraft und vor allem die Zeit einen solch strapaziösen verhandlungs ein Veranstaltungsmarathon auf sich zu nehmen in einer Zeit die ohnehin für Sie persönlich besonders strapaziös ist das verdient alles unsere Hochachtung unsere Respekt und unsere Bewunderung und dafür erstmal ganz herzlichen persönlichen Dank trotz der sich fast explosiv auf türmenden Probleme und Krisen in den letzten Monaten wirken sie auf uns Menschen wieder berühmte Fels in der Brandung und trotzdem fallen in der letzten Monaten immer mehr so genannte Experten neun Mal kluge in den Print und TV Medien über sie her die Besserwisser Auto Opposition und wir alle Fragen uns eigentlich können Sie noch gut schlafen ja schönen Dank erstmal für die netten Worte aber als allererstes herzlichen Glückwunsch nachträglich zum Geburtstag wenn ich mit 81 aussehe wie sie dann habe ich alles richtig gemacht aber das glaube ich sind schon sehr sehr ernste Zeiten in denen wir jetzt leben und ich bin ganz sicher die Bürgerinnen und Bürger des Landes wissen dass auch ganz genau und sie wissen auch dass das eine Situation ist in der man wirklich nichts falsch machen darf es gibt ja manchmal so Vorschläge man soll Vorgehen nach Trial and Error aber ein Error ein Fehler in dieser Situation wäre ja furchtbar und deshalb ist es schon wichtig dass man besonnen bleibt sich mit vielen spricht und dass man für Deutschland ein Prinzip verfolgt dass mir ganz wichtig ist nämlich dass wir keine allein Dinge machen sondern uns mit unseren Freunden und Verbündeten immer besprechen und deshalb Entscheidung aus dieser Gesprächssituation heraus treffen damit wir gemeinsam handeln können das haben wir in der Vergangenheit getan und das werden wir auch weiter tun und ich finde es gehört dann auch dazu dass wenn die Zeiten sehr aufgeregt sind man trotzdem klar und fest bleibt dass man den Boden unter den Füßen immer behält damit man sicher ist dass die Entscheidung richtig sind und da kann ich Ihnen nur versprechen das werde ich weiter so machen denn das ist eine Zeit in der es nicht darum geht was steht morgen in der Zeitung wie ist die nächste Umfrage sondern was machen wir für die Sicherheit und was machen wir für den Frieden in Europa Dankeschön für die Antwort erfordert auch ein bisschen mehr Konzentration im Moment weil aber doch im Hintergrund ein paar Menschen nur die auch ihre Meinung kund geben wollen aber es geht Dir heute hier um Ihre Fragen auch so viele Fragen ich weiß dass es ganz ganz viele von ihnen gibt und ich möchte gerne einmal zu der jungen Dame hinter mir kommen stellen Sie an Ihre Frage mein Herr Scholz Jessica geh mal mein Name ich bin 25 studiere hier in Lübeck und bin stellvertretender erster Vorsitzende hier in der Uni und tatsächlich 30 Prozent der Studierenden leben unter der Armutsgrenze und die Inflation wird das ganze noch verschärfen was gedenken Sie zu tun um die Studierenden vor der Inflation zu schützen auf alle Fälle haben alle Bürger und Bürger mit den Preissteigerungen zu kämpfen und diejenigen die wenig haben natürlich am allermeisten wer viele Rücklagen hat der kann vielleicht das ein oder andere auffangen aber wer keine hat für den wird das ganz ganz schwer und deshalb gilt das für alle Bevölkerungsgruppen aber eben auch die für diese hier sprechen die Studierenden und deshalb muss das auch so sein dass wir die Situation immer wieder genau bewerten und auch stets bereit sind nächste Schritte zu gehen ein Schritt haben wir schon gemacht mit dem was wir mit dem bafög-reform auf den Weg gebracht haben auch Verbesserung für viele die auf Ausbildungsförderung angewiesen sind aber das wird sicherlich nicht das Ende der Dinge sein die wir tun können wir hoffen ein bisschen dass wir vielen Studierenden auch mit dem neuen euro-ticket drei Monate lang ein bisschen Erleichterung verschafft haben aber das ist ja nur ein Zeichen dafür dass wir uns überhaupt sehr klar darüber sind es ist eine schwierige Situation und wir müssen zusammenstehen und 30 Milliarden Euro waren die ersten Rakete die wir auf den Weg gebracht haben aber wir werden weiter gucken was zu tun ist ein Instrument dazu ein Weg ist die sogenannte konzertierte Aktion wo wir sagen wir wollen jetzt nach den ersten beiden Entlastungsmaßnahmen die wir ergriffen haben den Paketen den 30 Milliarden die nächsten Schritte im Gespräch mit möglichst vielen entwickeln und nicht einfach nur als Regierung verkünden und deshalb wird da geredet zunächst mal mit Arbeitgeberverbänden Wirtschaftsverbänden Gewerkschaften mit der Bundesregierung mit der Bundesbank dem Sachverständigenrat aber wir werden auch viele andere einbeziehen und die Lage von Studierenden gehört auf alle Fälle dazu genauso wie die von Rentnerinnen und Rentnern und vielen anderen und das wird noch ganz herausfordern das wird nicht einfach die Preise werden auch nicht schnell wieder sinken sondern das wird lange ein Problem bleiben mit dem wir lange zu kämpfen haben und deshalb ist es unser gemeinsames Thema wo niemand alleine gelassen werden darf eine Frage beantwortet ich habe das Gefühl da ist noch eine kleine Nachfrage ich hätte noch eine Rückfrage und zwar wird die Studierendenschaft denn in diese Gespräche mit einbezogen ist das geplant die konzertierte Aktion ist erstmal auf das Arbeitsleben bezogen was die Gesprächspartner betrifft aber natürlich wollen wir einen großen gesellschaftlichen Gespräch organisieren dazu zählen die Studierendenschaft genauso wie andere gesellschaftliche Gruppen Arbeitsleben ist zentral aber viele haben auch andere Perspektiven und die gehören dazu die nächste Frage gerne ich glaube jeder hat jetzt noch eine wahnsinn ich würde gerne einmal den Herrn in der roten Hose ganz vorne in der ersten Reihe hören ja guten Tag Herr Bundeskanzler schön dass sie gekommen sind meine Frage ist eigentlich keine richtige Frage aber ich muss Ihnen sagen ich bewundere die am meisten dafür wie sie auf diese unfledige Art und Weise des ukrainischen Botschafters reagiert haben das haben sie ja so abprallen lassen ich hätte den schon vor zwei Monaten nach Hause geschickt wenn ich der Bundeskanzler wäre danke ja aber das ist eine Entscheidung der ukrainischen Regierung damit es jetzt kein Missverständnis gibt mein Name ist Jens behrendtmeier ich komme aus Ratzeburg Herr Bundeskanzler ich habe eine frage zum energiegeld für mich ist nicht klar warum dieses energiegeld auch versteuert wird ich bin sehr dankbar wirklich von Herzen dankbar dass wir das bekommen aber das noch 33 Prozent davon weggehen das finde ich ein bisschen schwierig das ist so wie meine Tante Christine uns irgendwas schenkt und dann sagt ja aber ihr müsst das Fahrwerk mit einberechnen ja das finde ich schwierig das tut mir leid dann könnten sie es auch behalten na ich glaube dafür ist es ein bisschen teuer dass er hat schon vielen als Entlastung gewinkt noch ist es ja nicht gezahlt oder nicht angekommen bei den Bürgern und Bürgern aber es wird ich will sagen was wir überlegt haben wie kriegen wir möglichst schnell an alle anderen möglichst viele so ein eine kleine Unterstützung für die steigenden Preise wir haben noch viele andere Sachen gemacht 9 € Ticket habe ich schon gesagt dass wir drei Monate die Steuern vom Benzin runtergenommen haben waren andere Sachen dass wir den Grundfreibetrag angehoben haben bei der Steuer so dass es ja eine Entlastung für alle dass wir die arbeitnehmerpauschale erhöht haben die Pendlerpauschale alles Entscheidungen die da getroffen worden sind Zahlung für Leute die keinen Einkommen haben also zum Beispiel an Heizkostenzuschuss für Wohngeld Empfänger oder für diejenigen auf Grundsicherung angewiesen sind 200 € und auch für Familien haben wir was gemacht wo wir sagen ab Juli gibt es 20 € im Monat für Kinder aus Abend Verhältnissen zusatzlich jeden Monat und für alle 100 €, als Zuzahlung zum Kindergeld aber wir haben eben auch dieses energiegeld zahlen wollen und warum haben wir das so gemacht wie wir es gemacht haben wir haben überlegt wie kriegen das hin eigentlich müssten wir den Gerechten Betracht machen der würde eigentlich lauten Leute die viel Geld verdienen ich zähle übrigens dazu die brauchen eigentlich nichts und Leute die ganz wenig Geld verdienen die brauchen viel mehr aber dann hätten wir eine Verwaltung aufbauen müssen die das ganz sorgfältig ausdifferenziert und das können wir noch nicht wir haben uns vorgenommen dass wir Gesetze machen und Verwaltung aufbauen dass wir irgendwann mal sagen können wir wollen allen Bürgern 100 Euro überweisen und das auch können aber das ist heute technisch noch gar nicht möglich und deshalb haben wir diesen Weg über die Steuer bei den Arbeitgebern bei den Unternehmen gewählt und das führt dazu dass ich auf diesen Betrag um es sehr persönlich zu sagen eben den Steuersatz zahlen den ich zahle der ist viel höher als ihrer und andere die ganz wenig verdienen eben viel weniger und das haben wir versucht dadurch etwas gerechnet zu machen danke schön für diese Antwort gibt es noch eine Frage zum Bereich Energie oder zum Bereich Geld melden sich alle und das ist doch recht wenige Hände hätte gern den Herrn deiner zweiten Reihe mit dem karierten Hemd da kommt das Mikro hallo ich bin Sascha ich bin ein Pfleger in Lübeck und habe vor acht Monaten ein Kind bekommen und ich hatte nie gedacht dass das finanziell so teuer ist ein Kind zu unterhalten hier meine Frage ist wieso kriegen Eltern nicht mehr Kindergeld oder nicht also auch eine Steuererleichterung wie z.B ein Kind 1 % weniger Steuern zwei Kinder drei Prozent wie ist das nicht möglich wir haben verschiedene Dinge die wir tun das eine ist das was ich eben schon erzählt habe jetzt in dieser ganz konkreten Situation dass wir sagen wenn das Geld sehr knapp ist gibt's pro Kind 20 € mehr und das wäre eine Einmalzahlung von 100 € machen aber es gibt das Kindergeld darauf haben sie ja schon Bezug genommen das für alle Familien gezahlt wird und natürlich gibt es auch noch steuerliche Freibeträge die allerdings eher bei denjenigen zu Buche schlagen die sehr hohe Einkommen haben deshalb ist immer wichtig dass man mit dem Kindergeld auch eine Leistung zur Verfügung stellt bei denen diejenigen auch profitieren die im unteren Bereich der einkommenskala Leben was wir uns vorgenommen haben für diese Legislaturperiode ist aber das ganze gerechter zu machen es hat dann Wort gegeben dafür wir nennen das jetzt eine Kindergrundsicherung das klingt vielleicht ein bisschen abstrakt aber gemeint ist eigentlich dass wir wollen dass mehr auf die Leistungsfähigkeit geachtet wird dass Kinder in Haushalten nur wenig Geld ist mehr kriegen und das ist eine bessere großzügigere Unterstützung für die Familien gibt das ist also letztendlich aus Ihrer Frage heraus geboren ich will jetzt nicht sagen sie waren das aber wir haben unbedingt das Gefühl da muss man was ändern und das ist das große Vorhaben dass wir in dieser Legislaturperiode zustande bringen wollen aber mehr drauf gerichtet viel mehr schaffen kann das ist mehr Kinder geben kann also auch für später für die Renten Einzahlung weil 200 €, das ist ja eigentlich gar nichts er muss irgendwie viel mehr investieren würde dann würden auch viel mehr Familien mehr Kinder haben wollen so meinte ich das ja den pflichte ich bei wobei ich finde es gibt keinen Staatsauftrag dass man Kinder kriegen soll das ist schon etwas was Eltern aus Liebe und Zuneigung und auch im Hinblick auf die Kinder entscheiden sollten da gibt's keine gesellschaftlichen Kriterien aber was ich wichtig finde ist dass wir die Familien besser unterstützen zum Beispiel indem es ausreichend Angebote gibt an Krippen und Kitaplätzen da haben wir jetzt als Bund auch noch mal weiter Geld bereitgestellt damit die Länder und Kommunen den Ausbau weiter vorantreiben können und auch die Qualität verbessern können ich persönlich finde auch immer wichtig dass die Gebühren für die Kindergärten nicht so hoch sind das habe ich ja schon mal als ich Bürgermeister in Hamburg war durchgesetzt dass das Standardangebot gebührenfrei ist das hat vielen Familien wirklich geholfen die sonst genau rechnen müssen was ob sie sich das leisten können ob sich das lohnt und ich bin sicher in Deutschland wird sich das immer mehr verstärken als Bund tun wir das was wir können nämlich mit den Mitteln die ich eben schon gesagt habe danke schön sie haben sich direkt während der Frage noch gemeldet ist das mit zum Thema weil sie ihnen in der zweiten Reihe dann gerne bitte einmal das Mikrofon mein Name ist Antje lennertz ich bin in Pölitz in der Gemeindevertretung und im Kita-Bereich den sie gerade angesprochen haben gibt es ja nicht nur das Problem des Geldes und der Beiträge sondern auch das Problem der Fachkräfte und die Ausbildung zu einer Erzieherin ist ja im Moment eine schulische Ausbildung gibt es Pläne daran etwas zu ändern um diesen Fachkräftemangel zu begegnen es gibt ja auch schon es gibt sehr unterschiedliche Ausbildungswege das ist der eine über den See dort berichten und wir versuchen natürlich viele Möglichkeiten zu schaffen dass viele diesen Weg gehen das ist ja ein toller Beruf und ich glaube da spielt auch eine Rolle dass wir vielen einen Weg finden beschreiben wo sie sagen können ich möchte diesen Beruf ergreifen ich finde den dann auch am Ende ordentlich bezahlt so dass man lange dabei bleibt das ist ja auch ganz wichtig wir haben ja ganz viele die sich für den Beruf entscheiden und dann irgendwann wechseln und wenn wir das ändern können würden wir auch schon das Fachkräfte Problem nicht mehr so viel haben wie das jetzt der Fall ist also ich stimme Ihnen muss ganz viel dafür tun dass sich viele junge Leute dafür entscheiden und auf alle Fälle sollte es keine Gebühren kosten wenn man eine solche wichtige Ausbildung beschreiten will soweit so viele Fragen noch wie schau mal auf die andere Seite aber den Herrn in der dritten Reihe mit dem dunkelblauen Shirt Hemd ja guten Tag Herr Bundeskanzler mein Name ist Peter rutzige komme aus Mölln und ich habe eine Frage bezüglich der Transaktionssteuer die Preise gehen durch die Decke an ein Teil dieser Kostensteigerung sind ja begründet durch Spekulation Gewinne und es gab ja mal Aktivitäten weltweit hat ja nicht geklappt europaweit auch nicht dann gab es Frankreich sie haben mit mit macron ja darüber gesprochen das war glaube ich 2021 sollte die Transaktionssteuer kommen und warum wird diese Steuer nicht eingeführt das ist ja alles wir haben von diesen sag mal waren Termingeschäften Leerverkäufe allein was für ein Wort das schon ist davon haben wir alle nichts und warum wird dem nicht ein Riegel vorgeschoben und ein Teil wäre doch sicherlich möglich wenn man die Transaktionssteuer einführen würde damit ein Teil dieser geht dieser Gelder die uns uns entnommen werden auch wieder an den Start zurückkommen ich würde ab bitte dass sie auch konkret antworten und sagen wann sie kommt wenn es möglich ist ja diese Frage würde ich ihnen gerne ganz konkret beantworten können aber was jetzt die Besteuerung von Finanztransaktionen betrifft gibt es ja gegenwärtig keine gesetzgebungs Mehrheit dafür das zu machen das glaube ich gehört der das muss man wahrheitsgemäß berichten wir konzentrieren uns deshalb im Augenblick also die Besteuerung von Verkaufen von Aktien und anderen Sachen darum geht es ja was sie vorgeschlagen haben sondern wir würden uns jetzt gerade um was anderes nämlich eine Vereinbarung umzusetzen um die ich mich sehr bemüht habe dass sie weltweit zustande kommt nämlich dass wir eine Mindestbesteuerung von großen erfolgreichen Unternehmen durchsetzen das haben wir geschafft zu vereinbaren und es fehlt jetzt noch an der letzten Zustimmung eines Landes in Europa aber wir sind dran das auch noch zu überzeugen so dass wir demnächst eine europäische Regelung haben werden die dazu führt dass insbesondere die ganz großen globalen Internetplattformen und Unternehmen diese Art die riesige Umsätze haben und in den Ländern wo sie das Geld verdienen nicht so viele Steuern zahlen etwas mehr herangezogen werden und diesen Weg wollen wir jetzt erstmal umsetzen und es scheint zu klappen dass das jetzt was wird weil es sind die USA dafür es ist Großbritannien dafür es ist weltweit viel unterstützt worden und die EU ist auch dafür jetzt müssen noch einmal 27 Jahre sagen und dann sind wir fertig die Antwort konkret genug nicht so ganz konkret also das Mikro geht das jetzt wieder ja nicht so ganz konkret aber ich würde im nächsten Jahr wieder kommen und die Frage wiederholen sehr schön und dann hoffe ich dass ich Ihnen sagen kann das mit der globalen Mindestbesteuerung das haben wir schon weltweit umgesetzt wunderbar wenn Sie sich einmal umdrehen mögen Herr Bundeskanzler dann hätte ich von der Dame hier in der Mitte nach einer Frage für Sie ja ich bin Josephine Wahl ich bin Gesundheits- und Krankenpflegerin leider nicht mehr aktiv weil es für mich einfach nicht mehr auszuhalten war und ich würde gerne wissen was sie zu den Geschehnissen in NRW sagen und ob die PPR 2.0 das Ende der fahnestange ist also ja wir haben uns fest vorgenommen dass wir die Situation in der Pflege verbessern und dazu gibt es ganz ganz viele Dinge die dringend notwendig sind das eine ist etwas wo ich mich schon lange für eingesetzt habe dass wir im Bereich der Pflege ein Mindestlohn durchsetzen den es jetzt nun schon einige Zeit lang gibt aber der natürlich niemals genug sein kann das zweite ist dass wir alle diejenigen die Pflegeleistung insbesondere im Bereich der Altenpflege anbieten verpflichten dass sie das wenigstens entsprechend zu Tarifverträgen tun weil es viele Unternehmen gibt die weiter drunter bezahlen was ein furchtbarer Zustand ist und das ist jetzt Gesetz geworden und das wird jetzt Stück für Stück umgesetzt und wir werden jetzt zum Jahreswechsel kontrollieren wer das alles wie gemacht hat weil man kann ansonsten als Anbieter von Pflegeleistungen nicht mehr abrechnen wenn man nicht entsprechend der regional wirksamen Tarife bezahlt und das dritte ist dass wir erreichen wollen dass die Zahl der Mitarbeiter und Mitarbeiter im Pflegebereich nicht so knapp bemessen ist wie das heute der Fall ist deshalb wollen wir über Personalbemessung Regeln und entsprechende Vorschriften machen damit das auch funktioniert und haben das jetzt ganz konkret vorbereitet da gibt es jetzt auch die entsprechenden Schritte wie so eine Gesetzgebung auf den Weg kommt damit das am Ende was wird das ist also das was in dem Bereich passiert und für die Krankenhäuser haben wir schon eine Regelung die theoretisch helfen könnte umgesetzt sogar schon nicht in diesem Jahr sondern vorher wo drin steht dass die eigentlich für den Bereich der Pflege im Krankenhaus keine Obergrenze haben und nicht nur abrechnen können nach den dort geltenden Fallpauschalen sondern dass sie die einfach einstellen können die sie finden Problem weil die Bedingung schon so viele Jahre so schwierig sind so dass man so viele Vorschläge machen muss wie ich sie eben skizziert habe sind natürlich nicht genug Frauen und Männer da die sagen hier ich möchte gern sofort eingestellt werden und deshalb ist das glaube ich eine große langfristige Aufgabe dass wir viele überzeugen dass sie es machen letzter Satz sie wissen das besser als ich aber die durchschnittliche Verweildauer von jemandem der die lange Ausbildung zur Pflegefachkraft gemacht hat zur Pflegerin zum Pfleger ist sieben bis acht Jahre das heißt nachdem sich Frauen und Männer mit ganzem Herzen für den Beruf entschieden haben den ausgeübter bleiben sie dann nicht so lange wie in vielen anderen Berufen und das ist ja eine Mahnung dass wir die Arbeitsbedingungen verbessern müssen damit mehr lange Leute länger bleiben Unikliniken gerade streiken und die Geschichten sind so dramatisch die da erzählt werden die habe ich erlebt die haben pflegende Angehörige erlebt und Bekannter aus meinem Freundeskreis ich glaube einfach dass das was jetzt gerade angedacht ist zu tun zu langsam geht also weil eben so dramatische Geschichten erzählen und damit stelle ich jetzt gar keine Frage mehr sondern vielleicht einfach eine Bitte ja und diese Bitte ist angekommen deshalb konnte ich ihn schon viele Maßnahmen nennen die wir auf den Weg gebracht haben und der von Ihnen zitierte Arbeitskonflikt ist ja ein Zeichen dafür dass da was los ist und es ist wirklich was los in der Pflege wir können jetzt nicht nur das machen was in der corona-zeit passiert ist dass man den Pflegekräften Beifall klatscht sondern da muss jetzt auch was anderes passieren nämlich dass das langfristig an Beruf ist der nicht nur toll ist wo wir tolle Frauen und Männer haben die sich für den entscheiden weil sie ja immer auch etwas für andere tun wenn Sie diesen Beruf ausüben sondern dass sie auch das so gut finden dass sie gerne in diesem Beruf lange bleiben wollen Dankeschön für diese Antwort die Dame hinten in der dritten Reihe ich glaube sie meldet sich schon fast von Anfang an Arm wird schon schwer was ist ihre Frage an den Bundeskanzler ja hallo ich komme von ambulanten Pflegedienst Delta mein Name es geht um Tarif drohe Gesetz was sie gerade angesprochen haben Finanzierung ist schon passiert das weiß ich aber nur für stationäre Bereich 25% für ambulante Pflegedienste oder Pflegeanbieter wurde das gar nicht geplant das heißt dass innerhalb von ein paar Monate werden mehr als die Hälfte ambulante Pflegedienste pleite gehen ist das von der Regierung so geplant oder einfach nicht durch gedacht schönen Dank erstmal für ihr Engagement und für die Arbeit die sie leisten das finde ich muss ja einfach immer wieder gesagt werden und in der Tat ist es so wir haben einmal die stationären Pflegeangebote in der Altenpflege in der Behindertenpflege aber auch zum Beispiel im Bereich der Krankenhäuser und dann haben wir auch die ambulanten Angebote und das kann nicht so sein dass die Bedingung dort viel schlechter sind deshalb gehört natürlich dazu dass man in dem Augenblick in dem man bessere Tarife zahlt bessere Löhne gezahlt werden auch dafür sorgt dass das refinanziert wird das Geschäft ist verteilt auf die zuständigen Einrichtungen bei den Pflegeversicherung die das verhandeln müssen aber ich kann ihn versichern dass das ein Thema ist dass die Bundesregierung auch im Blick hat ich habe mit dem Minister sehr oft darüber gesprochen kann Ihnen sagen das ist nicht vergessen und da kümmert sich darum die nächste Frage sehr gerne Nachfrage schaffen sie das tatsächlich innerhalb von zwei Monaten oder gar nicht mehr weniger als zwei Monaten es ist ab 1 September und ich habe zum Beispiel kein Geld die Gehälter dann am 9 im 9 Monat bezahlen so ich höre Gehälter ist unmöglich ich nehme jetzt mal ihre Dringlichkeit noch für das nächste Gespräch mit Herrn Lauterbach mit toller Lösungsansatz vielen Dank dann gerne eine Frage von einem Herrn zur Abwechslung mal wieder ich hätte gerne den Herrn in der zweiten Reihe im dunklen Anzug ja guten Abend Herr Bundeskanzler mein Name ist Sascha Jahns ich bin 43 Jahre alt komme aus Ratzeburg und bin hier Unternehmer in Lübeck und meine Frage an Sie sie haben gemeinsam mit Herrn Habig sportliche Ziele vereinbart was die Energiewende angeht die Folgejahre bis 2030 sollen eine Million Wärmepumpen im Jahr verbaut werden wo kriegen wir die Fachkräfte her ich habe es eben von der Dame gehört wir haben dort einen hohen Notstand in der Pflege was absolut erste Priorität hat aber auch im Fachhandwerk spiegelt sich das wieder wie wollen wir das gelöst bekommen wie wollen wir die Energiewende letztendlich gemeistert bekommen gerade zu der jetzigen Krise wo wir auch so eine große gasknappheit haben die Frage haben wir genug Fachkräfte wird uns noch länger beschäftigen übrigens ein Hinweis darauf dass nicht alle Berechnungen die irgendwann mal angestellt worden sind stimmen also ich erinnere mich noch ziemlich genau an Vorhersagen aus den 90er Jahren wo uns gesagt wurde wie die Zahl der Beschäftigten runter geht wie sogar die Einwohnerzahl runtergeht beide haben nicht gestimmt wir haben heute etwa sechs Millionen Arbeitskräfte mehr und dann Allzeithoch bei der Erwerbstätigkeit in Deutschland das ist schon etwas was man immer mit dem Kopf haben muss dass die Dinge anders gekommen sind als die pessimistisch von vielen vorhergesagt wurden trotzdem stellt sich das Problem wieder und aus meiner Sicht gibt es zwei Dinge die man tun muss erstens viele junge Leute begeistern dass sie sich am Ende ihrer Schulzeit für eine berufliche Ausbildung zum Beispiel Handwerk auch in dem wo Sie tätig sind entscheidend das sind ja tolle zukunftsberufe mit guten sicheren arbeitsplatzperspektiven und sicherlich so wie die Dinge liegen auch guten einkommensperspektiven für diejenigen die da anpacken wollen und das funktioniert am besten wenn man schon in der 8 9 und 10 Klasse anfängt darüber zu reden welche Berufe es so alles gibt auch möglich macht dass sich junge Frauen und Männer dafür entscheiden und das bei denen wo es nicht geklappt hat wir dann noch mal Nachfassen deshalb gibt es zum Beispiel eine Idee die ich lange verfolgt habe eine jugendberufsagentur überall zu etablieren einzurichten wo dieser Übergang besser organisiert wird weil das ist ja oft so wenn man so die Bewerbungsunterlagen anguckt auch als Handwerksbetrieb zum Beispiel denkt man stelle ich nicht ein oder aber wenn man die sieht und da war mal drei Monate im Praktikum dabei oder sie dann denkt man den nehme ich oder sie und das gleiche gilt übrigens auch umgekehrt viele Themen gar nicht auf die Idee dass sie sich für diesen Beruf bei der Firma entscheiden würden aber wenn man sich schon mal getroffen hat gelingt das auch also da müssen wir gucken dass wir das besser hinkriegen damit möglichst viele die Wege auch nutzen die in offen stehen und damit eine gute Perspektive bekommen und das zweite ist natürlich dann immer wieder und dass wir auch bereit sind zu gucken wer die Fähigkeiten hat die wir hier brauchen und dann andere einladen aus anderen Ländern der Europäischen Union aber auch von außerhalb hierher zu kommen das hat ja in den letzten Jahrzehnten auch geklappt in großem Umfang und ich bin ziemlich sicher das wird auch in den nächsten Jahren eine große Rolle spielen und deshalb wird die Bundesregierung noch in diesem Jahr Gesetze auf dem Weg bringen womit das dann einfacher wird als das heute der Fall ist für Leute die sich mit Theorie beschäftigen könnte man sagen theoretisch haben wir schon fast das großzügiges Gesetzeswerk der Welt praktisch nicht also müssen wir jetzt Theorie und Praxis mehr zusammenbringen danke schön wir haben noch so unglaublich viele Fragen wollen wir gleich mal zur nächsten gehen bei Ihnen hier vorne im in der weißen Bluse gerne einmal das Mikrofon Sekunde bitte noch Sekunde jetzt mein Name Annelie tescher aus Berkenthin ich wir haben noch nicht genug Ton bitte mein Name Annelie Tesche aus ich komme aus Berkenthin ich bin um CO2 Einsparung mittragen zu können auf die Bahn umgestiegen verstärkt auf die Bahn umgestiegen und ich erlebe das Züge ausfallen ich erlebe dass ich fast nie pünktlich irgendwo ankomme meine Frage an Sie wie weit sind die Pläne mit Ihnen und dem Verkehrsminister dass da eine Änderung kommt der Verkehrsminister hat mit mir neulich sehr sehr lange über die Frage gesprochen was er machen will um die Sache in Ordnung zu bringen er weiß das geht nicht von einem Tag auf dem anderen aber es gibt viele Dinge die man tun kann also da reicht es aber nicht aus zu sein das soll jetzt morgen alles pünktlich werden sondern wir müssen zum Beispiel dafür sorgen dass wir ganz viel in die Gleisinfrastruktur investieren dass wir bei Reparaturen dafür sorgen dass es mehr Möglichkeiten gibt dies auf den Straßen auch gibt zum Beispiel das Züge einander überholen können aber nicht einmal am Anfang der Strecke und einmal am Ende der Strecke biegen Sie wieder ein sondern so wie auf der Straße kurz ausschwenken ausscheren und wieder ein Scheren weil man ja sonst die entgegenkommenden Züge beeinträchtigt und dann kann man das alles noch unterstützen mit viel Digitalisierung so dass man Wagen kann das Züge aufeinander zu fahren ohne dass die kollidieren das gehört ja auch dazu bei großen Strecken wäre das möglich wir haben das immer noch ein bisschen so wie ganz früher gemacht während andere Länder genau das was ich eben geschildert habe schon gemacht haben wie Österreich z.B und die haben jetzt mehr Pünktlichkeit im Bahnsystem also werden wir das auch so machen und nebenbei natürlich auch die Gleise ausbauen und dafür sorgen dass es mehr gute Züge gibt aber das ist ein Projekt nicht von ein zwei Jahren okay dann hat es sich schon erledigt ich wollte fragen welchen Zeitraum geben Sie uns das wird wohl einiges geht schnell aber vieles wird auch noch viele Jahre dauern wir wollen das aber in diesem Jahrzehnt alles auf den Weg bringen das einzige was man jetzt anders machen muss als früher nämlich sofort anfangen weil die nächsten zehn Jahre sind immer die nächsten 10 Jahre wenn wir jetzt anfangen sind sie irgendwann zu Ende und hat das meiste ja sich schon verbessert zwischendurch in zehn Jahren wenn man in 10 Jahren anfängt sind das die zehn Jahre danach also sofort anfangen von dem Herrn da </t>
+  </si>
+  <si>
+    <t>t9Ts6JLthZ4</t>
+  </si>
+  <si>
+    <t>liebe Geschwister und willkommen zum heutigen Vortrag wir machen weiterhin Charlotte alle an der Stelle wo wir aufgehört haben das letzte Mal und zwar haben wir über die Ehefrau von heilig aber wir machen eine gesprochen also die Tochter des Propheten alle ihre und da gibt es noch einige Aspekte die ich erwähnen wollte und zwar eben über sie und auch über die beiden Söhne alhassan und das Thema ist natürlich wichtig dass wir auch erklären unsere Haltung gegenüber der Familie des Propheten alle Histamin bate denn die Schiiten behaupten unterstellen dass die Sunniten die Familie des Propheten salomona verachten nicht respektieren oder sogar hassen und das ist natürlich eine Unterstellung ganz im Gegenteil wir dienen allosa damit dass wir die Familie des Propheten und dass wir sie ehren und dass wir die Segenswünsche auch für Sie aufsagen wenn wir sagen was soll die alle Mohammed Ali Mohammed also auch für die Familie des Propheten sondern machen eigentlich nur wir sagen zur Familie des Propheten sondern morgen alle über salam gehört auch die von den Schiiten beleidigt wird und zur Familie des Propheten sondern machen alle ihre Selm gehört auch Abu Baker der Vater von ah ich ja aber wir machen an und auch Oma auch ein Schwiegervater des Propheten sondern machen der Vater eben von Hafner also wir sagen wenn schon denn schon also wenn wir die Familie des Propheten sondern machen sollen dann bitte ohne Ausnahme also von den Gläubigen ja und deswegen sagen wir wir lieben die Familie des Propheten at sondern die Schiiten aber die lieben nicht die Familie des Propheten Radios wenn sie eben unterstellen dass er über Korona Heuchler waren und das ich habe auch eine Heuchlerin war und das eigentlich alles so habe Heuchler waren außer zwölf oder mehr oder weniger und das ist eben ein Aspekt den wir auch erwähnen müssen und zwar Fatima Iran Fatima Radio war eine genügsame Frau eine tugendhafte Frau und eine Geschichte die zeigt wie schwierig ihr Leben war bzw wie hart auch ihr Leben war ist dass der Prophet von der lachen [Musik] eines Tages kamen Sklaven also aufgrund von Kriege und so weiter gab es ja Sklaven das hat sich ja schon öfter erwähnt und als uns Sklaven kamen ging ja ich ja aber wir machen einen Herr zum Propheten sondern und sagte sie würde gerne jemanden also eine Frau haben die ihr hilft zu Hause ja beim Haushalt und sie ging also zum Propheten da fragte er was bringt dich zu mir meine Tochter da sagte sie ich bin gekommen um dich zu besuchen um dich zu begrüßen und sie schämte sich zuerst einmal ihm zu sagen ich würde gerne eine Haushilfe haben und da sagt der eine also dann hat er gesprochen er war dabei da sagt er oh gesamter wir sind erschöpft also wir brauchen Unterstützung ja im Haushalt und deswegen und wir haben gehört das kamen Sklaven ja und wie wäre es wenn Du uns einige geben würdest oder zumindest jemand der uns hilft da sagte der Prophet soll man machen und schaut euch an wie edel der Prophet Salal und dass er nicht aufgrund von Familien Beziehungen andere Menschen benachteiligt hat was sagt er alles er sagte bei Allah ich werde euch niemanden geben und er muss sofort die in der Propheten Moschee gab es hinten einen Platz eine überdachten Platz und da saßen die armen hinten aus medinen die armen Muslime und man wusste okay dort sind sie dann jemand der spenden wollte oder essen geben wollte und so weiter das heißt die haben nichts und da sagte er und ich kann euch diese nicht geben und ich habe arme Menschen hier das heißt ich muss die versorgen erst einmal das heißt die Sklaven werden dann verkauft und noch einmal das war internationales Recht das hat der Islam nicht eingeführt aber der Islam hat erlaubt diese Gesetze die bei allen Muslimen und nicht Muslimen vorhanden waren diese Gesetze auch zu nutzen bis eben Sklaverei abgeschafft wurde er und der Islam kam mit geboten damit Sklaverei abgeschafft wird auf jeden Fall also gab es Sklaverei damals und da sagt er der der die Erträge die Einnahmen die sollen zugunsten dieser armen benutzt werden dann sagte der Prophet sondern machen soll ich euch nicht etwas sagen was viel effektiver ist der braucht Unterstützung zu Hause ich gebe euch einen Tipp und wenn er das macht dann wird die Arbeit erleichtert er sagte ihr sollt nach dem Gebet immer wenn ihr mit einem Pflichtgebet fertig seid sollt ihr nach dem Gebet zehnmal zum Herrn sagt und zehnmal haben du lila und zehnmal allahu akbar und wenn ihr schlafen geht sollte ebenfalls sagen und zwar 33 mal zum hannelor und 33 mal alhamdulillah [Musik] und 34 mal allahu akbar und das ist dann effektiver dann wird Allah euch eben diese Erschwernis aufheben ja dass er Kraft findet und das zeigt also dass ein ganz normales Leben führte also das heißt nur weil sie Tochter des Propheten sondern lade selber war hatte sie keinen VIP leben ja sie ist natürlich eine besondere Frau aber weltlich lebte sie so wie alle anderen das ist kein Wunder denn der Prophet selbst der seller lebte wie jeder andere er hungerte manchmal manchmal hat er was zu essen und so weiter das heißt er war er lebte so wie alle anderen habe auch gelebt habe kommen wir nun zu einigen Aussagen des Propheten Salon und zwar sagt der er jene die ich am meisten liebe von meiner Familie ist Fatima aber wir lachen anhören und er sagte Fatima ist ein Stück von mir wer sie sauer macht der hat mich sauer gemacht also wer sie erzählt der hat mich erzürnt und ich hatte ja letztens schon erwähnt dass der Prophet sondern gesagt hat also das war in welchem Kontext das war im Kontext dass er mitbekommen hat das heilige aber wir machen an eine zweite Frau heiraten sollte neben Vater und das hat der Prophet Salalah nicht erlaubt und ich hatte ja gesagt das ist eine Ausnahme gewesen wegen Vater immer oder dir so dass sie eben in der Zeit in der sie gelebt hat so dass er Lehrerin keine zweite Frau hatte dann sagte der Prophet Salomon machen alle ihre auch über Fatima Arabia dass er das ist ein Stück von mir ist und wer sie eben sauer macht der wird mich auch sauer machen ja das sind mehrere Wortlaute über diesen in dem das erwähnt wurde aber sonst immer dass sie zusammen mit anderen Frauen zu den besten Frauen des Paradieses gehören welche waren die anderen Frauen ja welche Erzieher die Frau des Pharao und also sind vier salam sagte die besten Frauen sind Mariam bintuaimera Mariam also die Mutter von Elisa Alisa die erste Frau des prophetens von der Johannes und Erzieher immer für Frauen also die Ehefrau von Frauen in einem anderen Wortlaut heißt es viele Männer sind vollkommen und von den Frauen sind wenige vollkommen dazu gehören eben diese vier was soll das heißen viele Männer sind vollkommen ein Propheten also gemeint ist also von den Männern gab es vollkommene Welt vollkommen als Mensch ich all vollkommen ist nur Allah aber als Mensch die Prophete aber es gab ja keine Prophetinnen und doch gab es Frauen die eben von kommen waren als Mensch sehr sehr gute Frauen waren und das waren eben diese vier Frauen sagte Vater ist die ist die Anführerin der Frauen im Paradies neben Mariam bintu hämorran und in einem anderen Wortlaut wurde nur erwähnt Vater ist die Anführer also sei jeder tonissa also die wichtigste oder wie nennt man sowas wird übersetzen in der Dunja wissen wir die ja die geehrteste genau also wenn man die Königin ja das ist die Miss irgendwas ja im Land ja die wichtigste also so die geehrteste eben ist Fatima aber wir lernen eine deswegen wir lieben Dich noch einmal die Schiiten unterstellen uns wir würden die Tochter des Propheten sondern alles selber machen was für ein Quatsch ja und das erober karazadi karabi Lama an eben Fatima schlecht behandelt hat und dass er sie vom Erbe des Propheten Salami ausgeschlossen hat und es werden wir jetzt gleich sehen oder auch später in charlotteile der hat das nicht einfach so gemacht ja er hat ja auch seine Tochter ausgeschlossen ja ich es ja aber auch ein er bin des Propheten es ist ja die Frau erbt die Tochter erbt also es ist ja nicht nur die Tochter die erbt und da ich hatte auch nichts bekommen warum ja weil der Prophet sondern er sagte das Prophetin nichts vererbe also bekommt niemand von den Angehörigen ein Erbe die Schiiten stellen das so da ja erobaker hat Fatima ausgeschlossen ja dann mach doch weiter und er ist ja ausgeschlossen und das ausgeschlossen und alle Verwandten also keiner hat was bekommen ja und wenn das nicht stimmen würde was die Schiiten sagen ja das war unrechtmäßig warum hat es dann eigentlich dann wieder gut gemacht also wieder korrigiert dass er dann gesagt hat okay hier meine Kinder warte mal war ja dann tot also sie ist ja gestorben sechs Monate nach dem Tode des Propheten soll alleine aber wenn sie ein Recht gehabt hat an dem Erbe des Propheten sondern machen so und dann stirbt sie wer ist wer bekommt anders oder nicht und er selbst nun an der Macht war weil die Schiiten sagen heidi hatte Angst und hat war still muss man sich mal vorstellen dieser mutige ganze Zeit Angst unter der Macht von der bobaccount öffnen ja und hat sich nicht getraut zu reden Alter richtige Filme haben die und dann ja okay gehen wir davon aus und jetzt ist er Kalif geworden warum hat das nicht hat er nicht gesagt so und jetzt krieg ich und meine Kinder Hassan Erbe von Propheten Salomon das ist also und deswegen ist es halt so wichtig dass man seine Religion lernt weil diese Scheinargumente wenn du das nicht weißt dann soll oh wie konnte nur Abu aber wenn du dann lernst Hörzu rosa hat gesagt Propheten vererben nichts und so weiter und ich habe auch nichts bekommen und so weiter dann weißt du dass das einfach nur Unterstellungen sind kommen wir nun zu alassen Hunger den Enkelkindern unseres Propheten war der ältere Sohn Hasan und dann Hussein wurde geboren wie man Historik also muslimische Historiker sagen im Jahre drei nach der hinterach und immer Ramadan andere sagen es war im Jahre 4 oder 5 und ein bisschen nannte ihn gab ihm den Namen all Hessen und zwar alle aber hat ihm den Namen herb gegeben zu Beginn der Name früher und da kam der Prophet Salon und sagte zeigt mir mal mein Kind also mein Enkelkind was hat wie habt ihr ihn genannt dann sagten sie herb wir haben in Harb genannt dann sagte er nein er ist Hassan ist natürlich ein schönerer das soll ja Mut zeigen ja normalerweise aber ein viel schönerer Name ist Hassan Hassan ist was schön ja hast du nun ist gut schön richtig ja also etwas Positives und was soll man ja bedenken bei der Namensgebung man soll Bedenken bei der Namensgebung dass die Bedeutung etwas Gutes ist ja da gibt's Leute die nehmen sich die Namen nach dem neuesten Filmen und Serien und so weiter je nachdem wie der Hauptdarsteller ist oder die Hauptdarstellerin aber weißt du ganz genau wann der geboren ist und zwar in dem Jahr wurde diese eine Serie ausgestrahlt wurde ja und oder auch Namen die überhaupt nichts bedeuten weiß gar nicht wir hatten einen Musk sein Sohn bezeichnet irgendwie so ein XY 3,0 blablabla Käse aber ich befürchte das auch Muslime dann irgendwie auf diesen auf diesen Geschmack kommen obwohl man Geschmack ist das auf jeden Fall weil Muslime Armen wieder die Prophet soll langsam wieder Prophet Salon sagte sie haben den anderen nach nenne dein Kind mit einem schönen islamischen Namen ob Sohn oder Tochter und machen geboren wurde hat er ihn genommen und den erwärmen auf gesagt ins rechte Ohr von Hassan und das ist auch eine Stunde bei der Geburt dass man das macht und aber sol salonale Selena sagte dann auch sie sollen die Haare schneiden und mit dass diese Haare wiegen und im Gewicht ja dieser Haare Silber Spenden und das ist eine Stunde bei Neugeborenen bei jungen ob man das auch bei Mädchen macht also einige Gelehrte sagen nein das macht man nur bei jungen was macht man nur bei Jungen die Haare schneiden bei Mädchen werden die Haare nicht geschnitten und ich auch gewogen und so weiter sondern du schneidest bei Jungen die Haare und die werden gewogen und die dieses Gewicht in Silber gespendet oder also der Betrag eben ja der Wert aber das Selam sagte überall Hessen ich liebe ihn so liebe ihn ja ja liebe liebe ich liebe ihn also liebe auch du ihn und der Prophet your Allah ich liebe ihn so liebe jenen der ihn liebt ja und wir bezeugen Allah dass wir ein Hassan leben ja möge Allah uns auch dafür lieben und dies wurde auch überliefert eben bei Hussein ja dass er gesagt hat oh Allah ich liebe sie beide Hassan und Alkohol sein also liebe jenen der sie beide liebt ein wichtiger hatif überall hassen als er noch klein war und diesen werden wir noch und Scharlach noch einmal benötigen in später und zwar war der Prophet Salalah normal auf dem mimba ja also während der gepredigt hat auf dem mimba und el Hassan kam zu ihm ein Kind als Kind als Hassan kam zu ihm und da sagte der Prophet sondern mein Sohn also Enkelsohn meinte mein Sohn dieser Sohn ist ein Anführer und vielleicht wird Allah durch ihn Frieden unter zwei oder zwischen zwei Parteien stiften das ist wichtig in Charlotte alle wenn wir uns mit dem Konflikt unter den so habe beschäftigen dass Ebene Hessen raviolo an zurückgetreten ist vom Kalifat er war nur sechs Monate Kalif und damit sind die 30 Jahre recht geleitete kalife vollendet mit genau mit diesen sechs Monaten damit es nicht weiter zum Konflikt oder dieser Konflikt nicht weiter andauert ja das werden wir zahlen noch detailliert sehen also was soll alles salam hat erklärt dass also er hat prophezeit und vorher gesagt aufgrund dessen dass er die Offenbarung bekommt Alexa das Hessen Grund sein wird dafür dass Frieden gestiftet wird unter zwei Parteien also die Partei von Aldi oder an und die Partei von Ali war ja dann schon lange tot dann schon lange tot sechs Monate ist ja ja vorher gestorben ermordet worden von den Trauer ehrlich und dann aber die Anhänger meine ich von heilig aber an und die Anhänger von nur an wir auf ihn im Gegensatz zu den Schiiten die ihn gar nicht als Muslim sehen oder in beleidigen und so weiter und so fort nicht je nachdem welche schiitische Strömung es ist auf jeden Fall wurde dann Frieden gestiftet unter den Muslimen dass es kein Konflikt mehr gab denn er trat zurück alassen und ja war dann der Kalif ja das war das was Hasan gemacht hat das werden wir noch sehen eine weitere Besonderheit von den Hassan ist das er den Propheten Salomon sehr ähnlich aussah wie ein lauter überlieferte dass eine 77 sagte es gab keinen der den Propheten sondern machen ähnlicher war als ein Hassan ebenso Ali aber wir machen immer und in einem anderen heißt es und zwar das Abu Baker als eines Tages ein Hessen getragen hat und bubaka sagte wie sehr er dem Propheten ähnelt alle dann kommen wir zu einer Hussein der Bruder von Al Hassan Radio wurde ermordet so wie auch Hassan man muss sich mal vorstellen und Hasan und Hussein wurden ermordet ja äh äh Heili und Hassan von den Howard ja undurchlässigen wir noch sehen ihr sieht damals der Sohn von Maria war da der Kalif und ein General von von seinen Leuten der hat Hussein in carbälle dann getötet das werden Charlotte alle noch alles detaillierter und betrachten sagte auch über Hussein Hussein ist ein Teil von mir und ich bin ein Teil von Hussein wo Allah Liebe jenen der Hussein liebt und Hussein ist einer meiner Enkelkinder das heißt also auch Hussein erwähnte der Prophet Salon Salome dass er ihn liebt und es wurde überliefert dass er Hussein dem Propheten Salomon am ähnlichsten war so jetzt haben sich die gefragt und wie können wir das jetzt in Einklang bringen und hier ist natürlich wieder der Fachmann für solche Angelegenheiten immer noch jemand der sehr viele solche die offensichtlich ja auf dem ersten Blick und Widerspruch darstellen dass er dir erklärt nein nein guck mal das ist so zu verstehen und zwar das eben er Hussein nach dem Tode von derjenige ist der den Propheten am ähnlichsten ausgesehen hat ja also die die in den erwähnt werden dass er sein den Propheten sondern machen am ähnlichsten ist also nachlassen ja also nach Hessen und aber so einiges Solar to Salem sagte el hassanuel Hussein sind die Führer der Jugendlichen im Paradies also die Anführer die besten der Jugendlichen im Paradies und rossoul Ali salato Salem war einst auf dem mimbo auch während der Predigt und da kamen hassanol Hussein und die waren noch klein und sie hatten ein Kamis an ein Kleid an aber das war zu groß und hier sind wir gestolpert also kleine Kinder haben eine eine Kleidung die etwas größer ist und da hat der Prophet sondern unterbrochen und sie getragen und da sagte der Prophet sondern Allah sagt die Wahrheit in never locomoreuler du konfettner also euer besitzt und eure Kinder sind Versuchung also alles zu einem konnte nicht also er als Großvater und man sagt ja ähm einem also lieber als die Kinder sind einem die Enkelkinder ja also die Enkelkinder haben um so einen größeren Platz in den Herzen ähm als die Kinder selbst ja und da hat der Professor noch eine SMS eben sie gesehen und da sagte er ich habe diese zwei Jungen gesehen und da konnte ich nicht geduldig sein und so habe ich meine Predigt unterbrochen alles genau wir reden über Ali also über seine Familie gerade seine Frau und seine Kinder und dann geht's weiter mit der Geschichte doch es geht jetzt weiter in aber jetzt geht's erstmal um die Kinder von Aldi aber wir machen und arasula aliiz sola Tour Selam hat auch Hussein ab und zu mal oder immer wieder mit Organ oder mit AVK behandelt also Ruki gemacht und sah er sagte zu ihnen euer Vater und er meint damit also er sagte was euer Vater hat ist Meryl und ist hart so behandelt also er meint euer Urgroßvater ja Ibrahim Ali salam den der Prophet Salomon ist ja von der Abstammung ist eine isara und da sagte er euer Vater also Urgroßvater hat Ismail und ist her so behandelt also die Ruck her gemacht also ich suche Zuflucht bei den Worten Allahs die vollständig sind ich suche Zuflucht bei diesen Worten oder durch diese Worte vor jedem scheitern und jedem Tier oder alles was gefährlich ist und vor jedem Auge also das tadelt ja also vor jedem bösen Blick wie man auch sagt das waren also einige Aspekte bezüglich der Kinder von von einem also die Familie des Propheten hatten Besonderheiten war nicht so wie andere zu diesem Besonderheiten gehört dass sie keine Verkehr erhalten dürfen also jeder arme Mensch darf sein kehr bekommen außer wenn er ein Enkelkind des Propheten ist alles und das gilt bis sie auch nicht nur damals also wenn jemand von der Abstammung des Propheten ist alles voller dann darf er keine bekommen Geschenke dafür bekommen aber keine Säcke ebenso also der Prophet Salon sagte als sodaka gemeint ist hier auch im Koran manchmal oder wird bezeichnet oder gemeint damit ist dieser Kerl also nicht immer wenn sadaka steht ist die freiwillige Spende gemeint sondern meint auch als sacker also assada gebührt nicht der Familie Mohammed salam den sie sind Abfall der Menschen was heißt Abfall der Menschen also der Rest eben den die Menschen nicht benutzen und warum hat Allahs panatale das so bestimmt das niemand einem Familienangehörigen des Propheten sondern normal erniedrigen kann damit guck mal ich habe jetzt Geld gegeben ja diese Wecker eben ein Geschenk das ist ein Geschenk wieder was anderes das ist du bist ja nicht was besseres deswegen oder du hast ja nichts was eine höhere Stellung deswegen wenn du einem schenkst dass du ein Geschenk aber wenn du jemanden spendest dieser Kerl das bedeutet er braucht Dich ja und ein Familienangehöriger des Provinz soll eben nicht diese Situation erleben zweitens das hatte ich vorhin erwähnt dass sie den Propheten nicht erben alles soll er tun was salam der Prophet Salal sagte wir also Propheten werden nicht wir vererben nicht was wir hinterlassen wird gespendet und das war der Grund warum niemanden nicht nur dass er nicht Vater immer was gegeben hat aber wir haben sondern er hat niemandem von der Familie des Propheten was gegeben sondern es wurde gespendet was sie aber bekommen ist ein Fünftel des fünften der Kriegsbeute also die Kriegsbeute Allah solltet sagt so wissend dass das was ihr erbeutet habt das Allah ein fünfte zusteht und seinem gesamten und den Verwandten und den Weisen und den Bedürftigen und den Reisenden die im Arm sind ja du bist auf Reise man nennt ihn auf Arabisch Sohn des Weges also die deutsche Übersetzung glaube ich sagt gar nichts aus sondern deswegen das bedeutet also dass ein Reisender und der hat nichts mehr ja der hat zum Beispiel sein Geld verloren oder sowas ähnliches ist auf jeden Fall also das sind die Gruppen Personengruppen die von der Kriegsbeute auch etwas bekommen und ein Fünftel von dem was für Allah ist ein also es werden in fünf Teile geteilt ein Fünftel ist für Allah keiner teil und von diesem Fünftel ein Fünftel ist für die Familie des Propheten dann dass man die Segenswünsche auf sie sagt ja wie ich vorhin auch erwähnt habe und dass man sie lieben soll also wenn du mitbekommst jemand ist ein Enkelkind des Propheten salamar eine Cent dann musst du ihm Respekt zeigen und erweisen ja also heutzutage gibt es natürlich auch immer noch solche Menschen das muss nicht heißen dass sie gute Menschen sind ja also es kann sein dass man zwar von der Abstammung des Propheten von alleine ist aber trotzdem sündigt ja das ist ja nicht dass das dass sie dann heilig sind diese Menschen aber es sie verdienen Respekt aufgrund ihrer Abstammung vom Propheten sondern machen eine Sache sagt ich erinnere euch ähm an meine Familie also ich erinnere euch oder ich ermahne dass ihr meine Familie respektiert und das wiederholte er dreimal ja die Sache hat ich liebe Geschwister ist natürlich ein authentischer HD den wir auch berücksichtigen aber das heißt nicht wie es dann die Schiiten benutzen dass das ein billiges das heilige besser ist als die anderen zu haben also das was haben das eine jetzt mit dem anderen zu tun der Respekt gegenüber all ihrer an ja das das ist ein Bestandteil der Religion das müssen wir machen das ist ein Bestandteil unserer glaubenslehrerin aber heißt dass das jetzt Ali aber ein besser ist als nein denn wir haben ja öfter gesagt wir müssen so glauben wie die Farbe geglaubt haben und dieser habe haben oft erklärt wie die Reihenfolge der so habe ist eben ein normal dann Ali aber dir lang ein das ist keine Degradierung von Heiligabend sondern das ist eben so wie es dieser habe von Propheten sondern normalerweise verstanden haben die haben sie auch nicht selbst erfunden die Tatsache dass er immer vor beten ließ zeigt dass er eben einen höheren Rang hat in der Religion als andere und diese achadit in der es heißt dass wir die Familie des Propheten salarios Selen respektieren sollen die nehmen wir natürlich auch gerne an und umsetzen es auch um aber das heißt nicht dass wir sagen Ali Arabia lang wäre besser als die anderen eben terminierer sagt zu den Grundlagen von einer gehört dass sie erlull bate lieben und dass sie sich für sie einsetzen und dass sie den die Aufforderung des Propheten Salomon also dass wir sie respektieren berücksichtigen und dementsprechend sagte und wir lehnen es nicht ab dass der Prophet sondern erklärte dass wir eine lieben sollen und dass wir gut zu Ihnen sein sollen und sie respektieren sollen und großzügig zu Ihnen sein sollen denn sie sind eine paar Jahre also sie sind reine Abstammung also sie sind makellose Abstammung vom Besten Menschen überhaupt eben vom Propheten sol la long early wir werden an Charlotte alle noch ausführlicher sprechen über die Haltung der Schiiten auch gegenüber Ali und ihre Fehler aber heute geht es ja weiter mit der mit dem Amtsantritt von Ali Adler wir waren ja stehen geblieben bei der Ermordung von durch die hawaris durch diese Aufständigen und wie ging es jetzt weiter alkari Abu bakriminarabi der Meli kitische Gelehrte sagte und als die Bestimmung Allahs eintrat also das eben als ein ermordet wird gingen die Leute zügig zu all ihrer also sie wussten also das darf überhaupt nicht lange dauern dass wir den nächsten Kalifen haben warum ansonsten kommt einer von diesen traurig sagt ich bin der Kalif das heißt wenn jetzt nicht sofort dieses Amt wieder besetzt wird dann wird einer von diesen Aufständigen sagen einer dieser Anführer so und hiermit bin ich der kalife und deswegen sind sie zügig zu Ali aber wir machen einen gegangen sagte als Rossmann getötet wurde gingen die Menschen zügig zu heilig aber an und sie sagten wir brauchen unbedingt einen immer hier im Sinne von Kalif nicht immer vor Peter sondern gemeint ist der Imam also der Kalif der das Staatsoberhaupt anwesend waren voll Herr über aus und andere von denen und Anfahrt und so haben Sie die Bär abgegeben also ihren äh Schwur ihr Eid Treue Einheit zu heilig aber wir machen einen und zu den ersten gehörte doch und dann kamen die anderen nach und nach und das war am Freitag und zwar der 18 von solice ermordet das muss man sich mal vorstellen ja also in diesem heiligen Monat in dem Kriege verboten sind kommen diese hauerisch und bringen Rossmann um Rabia in anderen Überlieferungen heißt es und zwar das später gesagt hat ich sage mich los vom Blut restment also ja ich habe mit dem Blut von was man nichts zu tun ja ich war nicht eine Unterstützer dieser Sache und ich habe meinen Verstand verloren an diesem Tag also er meinte damit ich ich war ganz außer mir an diesem Tage und und da kamen sie zu mir die Leute und da sagte ich also ich sagte zu denen ich schäme mich vor Allah jene Anführer jener zu sein die öffnen umgebracht hat also ich soll jetzt Kalif sein also natürlich gab es auch dieser habe und die anständigen und so weiter aber er sagte ich soll jetzt diese Leute regieren ja diese Leute die oder für Männer umgebracht haben und deswegen war es so als sie als Mensch getötet wurde ging zu Alija auf der Lohan erst einmal nach Hause wie gesagt er konnte das nicht aushalten nicht ertragen wird umgebracht und dann ging in dieser Farbe zu ihm und das heißt sogar in einigen Überlieferungen so dass sogar die Tür also mit Gewalt aufgemacht wurde denn noch einmal es ging um den Bestand dieses dieses Landes ja dieses Kalifat und deswegen wird es durfte nicht zugelassen werden dass die Trauer nicht nun die Oberhand gewinnen also gingen sie zu Ali Arabia um ihn zu bitten aber eine wollte zu Beginn gar nicht also Ali wollte das gar nicht sondern er sagte es soll baldile der nächste calife ich mach's nicht balha soll das mal okay dann gehen wir zu Pala Hauptsache wir haben jetzt ein Kalif als sie dann bei toll heran und Irland sagte strecke deine Hand aus damit mein treuer Eid der ablegen kann da sagte nein nein du du bist derjenige der es mehr verdient als ich da sagte Ali nein ich mache das nicht also sind sie zu also bei ihr angegangen um ihm zu erklären hör mal zu weder willst noch Ali will es übernehmen du musst es übernehmen oder so wer hat gesagt nix da Ali du bist derjenige der es übernehmen soll warum ja weil sie wussten der vier beste Mensch ist wer nach dem Propheten das bedeutet nach dem Tode von man aber ein wer war der beste Mensch auf Erden heiliger Mann also wird kein Ballraum kein so weit und kein irgendein anderer halbe sagen ich bin besser die hat mir diese aride die wussten ja das also haben sie gesagt das geht nicht du bist derjenige der es übernimmt da sagte Ali Adapter an wenn es sein muss also wenn ich unbedingt das übernehmen muss dann bitte schön vor allem Leute warum vor allem Leuten ist ja sowieso gang und gäbe ja oder so eine Präsident oder einen König oder ein Staatsoberhaupt wird er nicht geheim gehalten normalerweise aber warum wollte er sofort offenkundig sagen die brauchen 100 Leute die sollen das mitbekommen dass dieser habe sich geeinigt haben dass sie aber wir machen an der Vertreter der Muslime ist nach der Ermordung von Rossmann aber also ging es dann so weiter das Öffnen dann der Kalifa schauen wir uns nun ganz kurz noch mal einige Vorzüge von heilig aber an ich hatte ja schon ein paar erwähnt aber noch ein paar zum Abschluss und schauen Leute aller und zwar einmal dass er zu denjenigen gehört denen das Paradies versprochen wurde wieder Prophet Salon erwähnte die zehn denen das Paradies zu Lebzeiten versprochen wurde aber Baker gehörte dazu und Rama dann hoff man dann war der 4 ebenso sagt der alliierer an dass der Prophet Salon sagte wer heilt nur ein Gläubiger liebt Ali und nur ein Heuchler hast Ali oder wir machen also nur wer ein Heuchler ist der wird verlieren hassen und verabscheuen und es die hauerisch damals zum Käfer erklärt ja und sie haben ihn ja dann auch getötet und das zeigt also dass sie auf dem Irrweg waren das heißt deine Haltung zu den habe ist das ist ein Indikator ein Maßstab um zu wissen ob deine AIDA richtig ist oder nicht und der Prophet sondern sagte ali ist ein Stück von mir und ich bin ein Stück von heilig aber an also die Enge Verbundenheit hat er damit erklärt und arasularis Solar Tour Selam sagte derjenige dem ich ein Gefolgsmann bin also derjenige der mir folgt also auf der auf Arabisch der Wortlaut wenn kundtun Mola also derjenige der sagt ich folge dem Prophet sondern machen dann ist es auch so dass er Ali folgen soll aber wir machen Liebe jenen der ihn liebt und Feinde denjenigen an der ihn anfeindet das ist auch so ein Hadis den die Schiiten gerne erwähnen um zu erklären bitteschön siehst du du musst all die lieben hallo Wir lieben hat dir mal was anderes gesagt aber kann man aus diesem Handy ableiten dass er besser ist als steht doch gar nicht mehr die Tatsache dass wir eine lieben aber wir waren und dass wir ihn lieben müssen und dass wir ihn nicht hassen dürfen das eine hat mit der anderen Frage wer der nächste Kalif ist nach dem Tode des Provinz von der Larsen hat überhaupt nichts damit zu tun ja und deswegen sagen wir diese kennen wir natürlich bestätigen wir aber das hat nichts damit zu tun dass alle ihre voran der rechtmäßige Vertreter des prophets nach seinem Tode sondern ebenso ein Hadit der den Vorzug erließ aber wir machen anzeigt ist in der Rasur von der Schlacht von haiwa dass der Prophet Salon sagte ich werde morgen die das Kommando jemandem geben dem Erlass panotale den Weg öffnen wird den allah liebt und den der gesamte liebt der allah liebt also er dieser Kommandeur ja der Anführer der liebt Allah und den gesamten und Allah und der gesamte Leben ihn also eine gewaltige Bestätigung so sehr dass er damals gesagt hatte ich hatte mir nie die Führerschaft gewünscht aus an diesem Tag warum ja weil dann kriegt dann habe ich ja die Bestätigung dass Allah mich liebt und die Bestätigung dass ich Allah richtig Liebe am nächsten Tag hat's mehr bekommen Ali Adler und das zeigt also was für ein Mann alia Arabella was für ein gläubiger Mensch und wie sehr sein Glaube war und also die der hatif geht ja weiter das am nächsten Tag eigentlich gar nicht anwesend war er war krank er hatte Augenschmerzen also rief er sagt er wo ist also hat man ihn gerufen der spuckte der professionelle auf das Auge von Aldi aber wir waren dann war wieder gesund aber wir machen dann sagte der Prophet Salalah gehe und wende dich nicht zurück dreh dich nicht um bis Allah dir äh den Weg öffnet also bist du im Freibad nach einigen Schritten rief nach einigen Schritten blieb er stehen ohne sich zurückzudrehen weil aber es wird alles salam sagte dreh dich nicht um ohne sich zurückzudrehen sagte er wozu soll ich sie aufrufen dann sagte er rufe sie auf oder Kämpfe bis sie eben an Allah glauben bis sie Lehrer sagen und haben wir darauf wenn sie dann dies getan haben dann ist ihr Blut und ihr Vermögen aufgrund dessen bewahrt und ihre Abrechnung obliegt bei solchen ARD wo es da was da heißt und kämpft bis sie sagen noch einmal haben wir gesagt wir müssen alle ARD und er hat uns betrachten das ist eine Form warum es zu Kriegsende kommt oder warum ist nicht so einem Krieg kommt dass sie Muslime werden das ist aber nicht die einzige Form ja es könnte ein Friedensvertrag entstehen wie es tatsächlich war mit den mekanern zum Beispiel das heißt also es ist eine Form nicht das die Islamkritiker machen ja was sie nehmen solche Archiv und sagen seht ihr die Muslime die wollen alle umbringen ja bisschen Muslime werden ja weil darunter ist immer sagt kämpft und kämpft gegen sie ein bisschen sagen ja dann müssen alle umgebracht werden nein sondern wenn sie nicht mehr sagen nicht Muslime werden gibt's noch eine Möglichkeit Friedensvertrag ja dass sie ihre Religion beibehalten können nur bei was waren das noch mal ja [Musik] bitte [Musik] genau das war das Problem bei das waren ja ein jüdischer Stamm und die haben die Muslime verraten es gab bereits ein Friedensvertrag mit ihnen mit den Juden in Medina gab es ja ein Friedensvertrag zwischen ihnen und den Propheten Salal eines aber sie haben dann die mechaner unterstützt damit die Muslime bekämpft werden und deswegen mussten sie dann eben auch bekämpft werden das waren also einige Vorzüge von Heiligen ei</t>
+  </si>
+  <si>
+    <t>FhHgf_n59PI</t>
+  </si>
+  <si>
+    <t>[Musik] Walk willkommen in Brasilien und vielen Dank dass Sie sich die Zeit genommen haben heute mit uns zu sprechen danke klären es war mir ein echtes Vergnügen ich kenne ihre Arbeit und ihre Person schon seit vielen vielen Jahren und natürlich hatte ich lange Gespräche mit Julian über Glen greenwold und ihren Beitrag und wie wir zusammenarbeiten und so weiter ja das ist sehr nett und natürlich unterstütze ich das Anliegen die Verfolgung von Julien zu beenden das ist eines der Dinge die wir in den Fokus rücken wollten abgesehen davon hatten sie etwas Zeit dieses wunderschöne Land zu besuchen was haben sie hier gemacht was werden sie in der verbleibenden Zeit hier tun um sich für juliensache einzusetzen im Prinzip verfolgen wir die Ereignisse des Films evaka in dem es um den weltweiten Aktivismus für Julien Assange geht wir führen also eine Frage Runde durch und entwickeln Argumente die zu dem Land passen in dem der Film gezeigt wird [Musik] so sprechen wir zum Beispiel in den Vereinigten Staaten mit aller Entschiedenheit über die Verteidigung der Bill of Rights und des ersten verfassungszusatzes in Brasilien sprechen wir ebenso nachdrücklich über die bricks und den Sonnenaufgang der lateinamerikanischen Staaten American States Luder das Silva ist ein langjähriger Verteidiger ihres Sohnes schon in den ersten wichtigen Bemühungen im Jahr 2010 als Lula noch Präsident war bezeichnete er diese Indiskretionen als wichtige Beweise für die Kriegsverbrechen der Vereinigten Staaten und ihre Verbündeten auf der ganzen Welt in der Zeit zwischen seine Amtszeit als Präsident und seine erneuten erfolgreichen Kandidatur für das Amt des Präsidenten war er ein entschiedener Verteidiger und beschreibt die Anklage gegen Julien weiterhin als eine Art Verfolgung wobei er die Regierung beiden sowie die britische Regierung sehr scharf für die Inhaftierung von Julien verurteilt hat hatten sie die Möglichkeit mit Lulas Regierung mit Vertretern seiner Regierung entweder in Brasilia oder im ganzen Land Kontakt aufzunehmen und wenn ja was haben Sie von ihnen erfahren können uns mit dem Außenminister der sehr hilfsbereit war und sich eine halbe Stunde Zeit für das Treffen nahm und dann Fotos machte die er über seine Möglichkeiten ins Internet und an die Pressedienste weiterleitete das war also sehr gut aber das wichtigste ist dass wir eine kristallisierte Unterstützung in der Bevölkerung erzeugen werden wir wissen dass Politiker und Politik sozusagen auf dem Willen des Volkes beruhen also vor allem im Sinne von Wählerstimmen und die Zuneigung zu Julian ist in Lateinamerika sehr groß wir haben auch den mexikanischen Präsidenten oprador als einen sehr starken Unterstützer gemeinsam haben diese beiden Männer die Verfolgung von Julien groß machen können und jetzt ist sie zu einer diplomatischen Angelegenheit zwischen den Nationen geworden dies ist eine Geschichte über die ich seit langem berichte ich würde sagen dass ich fast von Anfang an über Wikileaks berichtet habe sogar noch vor den eben erwähnten leaks dadurch konnte ich ein echtes Gefühl der Bewunderung für Julien und seine Arbeit und schließlich unsere Freundschaft entwickeln es ist also etwas das mich in all den Jahren auf vielen Ebenen sehr interessiert hat und was mir zumindest am wichtigsten erscheint ist dass ihre und seine Regierung die australische Regierung man bedenke dass Julian nie ein Bürger der Vereinigten Staaten war und auch jetzt nicht ist da er ein Bürger Australiens ist sich endlich für die Rechte seiner Bürger einsetzt die australische Premierminister einzuni albernies hat sich mehrmals mit deutlichen Worten geäußert genug ist genug es ist an der Zeit die Sache zu beenden was glauben Sie wie aufrichtig diese öffentlichen Einwände australischen Regierung sind und wie viel sie in Wirklichkeit tun um ihre amerikanischen Verbündeten unter Druck zu setzen damit Sie Julien freilassen hervorragende Frage da warst du zunächst einmal haben wir bei der letzten Wahl bei der Anthony albanis in die Labor Regierung die linke Regierung an die Macht gewählt wurden die Bezeichnung einer Assage Wahl verwendet die Unterstützung für Julian liegt bei etwa 88% der Bevölkerung in Australien sie wollen dass er nach Hause kommt also bis zu einem gewissen Grad von positiven Äußerungen über Julian ab und wir wissen dass in der Politik Worte taten sind wenn er also sagt dass er eine Lösung diese Angelegenheit erwartet und wünscht dann verstehe ich dass dies zu einer diplomatischen Angelegenheit Zeit für die Beziehungen zwischen den Vereinigten Staaten und Australien wird Kennedy Caroline Kennedy hat sich mit einer Delegation australischer Parlamentarier getroffen und dabei gesagt dass es eigentlich keine diplomatische Angelegenheit ist außer dass sie als Vertreterin der Vereinigten Staaten mit Ihnen spreche es ist eine rechtliche Angelegenheit aber so wie ich es verstanden habe ich zitiere so wie ich es verstanden habe beträgt die Höchststrafe die Julien für das Eindringen in einem Computer erhalten kann 60 Monate und diese Zeit hatte jetzt mehr oder weniger abgesessen dass jemand einen Deal anbietet jemand im US-Justizministerium bietet eine Art Deal oder Verständigung im Strafverfahren an wovon ich auch schon gehört habe ich wollte Sie fragen ich weiß nicht wie verlässlich das ist aber ist es das worauf sie sich im Wesentlichen beziehen dass es einen Deal für Julien gibt sich schuldig zu bekennen im Austausch dafür dass er die maximale Zeit für dieses Verbrechen bereits abgesessen hat ja genau aber ich würde es ein bisschen anders formulieren als einen Deal ich sehe es als eine diplomatische Vereinbarung zwischen den Vereinigten Staaten und Australien die beide aus den diplomatischen Umständen des Konflikts zwischen Australien und den Vereinigten Staaten herausführt und dem Opfer die Last auferlegt zu akzeptieren bevor ich sie dazu befragen möchte ich noch nachhaken dass die Beziehungen zwischen den Vereinigten Staaten und Australien durch die Konzentration der Vereinigten Staaten auf China und spezifikraum viel wichtiger geworden sind als je zuvor Australien ist wie ich gerade in dieser Woche in einem Artikel im Economist gelesen habe zu einem zentralen Punkt der militärischen Haltung der USA gegenüber China geworden sie wollen Militärbasen errichten sie bauen Militärbasen und zwar in Australien und versprechen Australien alles mögliche es gibt also sehr ernste Verhandlungen sehr ernste Handelsbeziehungen zwischen diesen beiden Ländern die für die Regierung höchste Priorität haben man sollte meinen dass Australien allein schon aus Gründen der nationalen würde mehr als genug Druckmittel hätte wenn es ihnen ernst wäre und deshalb frage ich mich wie auf richtig dies ist abgesehen von der Notwendigkeit die Bevölkerung politisch zu beschwichtigen und dies als eine Art Sieg zu werten den die Australien der Bevölkerung demonstrieren können dass wir nicht nur ein Vasallenstaat der Vereinigten Staaten sind sondern dass es sich um eine echte Partnerschaft auf Augenhöhe handelt hier äh Teig that point bitte ja ich verstehe diesen Punkt aber ich sehe das etwas anders denn es dauert eine Weile bis diese Vorkehrungen getroffen sind und die Vereinigten Staaten haben in den letzten 13 Jahren so viel Aufwand in die Verfolgung von Julien und das Profil dieser Anstrengung investiert und auch die Zweckmäßigkeit der Bedrohung Einschüchterung und Unterdrückung von potentiellen Verlegern und Journalisten erkannt ich erkenne auch instinktiv dass bestimmte Sektionen der US-Regierung die Fähigkeiten des ersten verfassungszusatzes zum Schutz von Verlegern und nun ja zum Schutz aller Menschen in den Vereinigten Staaten in Fragen der freien Meinungsäußerung beseitigen wollen lassen Sie mich noch einmal auf die Frage zurückkommen ob es einen Ausweg für die USA und Australien in Form von Eingeständnis und eine Stil es gibt Australien kann sagen dass wir unseren Bürger zurückbekommen haben und die us können sagen dass wir Julien Assange für die Verbrechen verurteilt haben für die er sich schuldig bekannt hat und dass dies unsere Vorgehensweise rechtfertigt ich glaube nicht dass irgendjemand beurteilen kann was Julian tut er war zuerst acht Jahre lang in einem effektiven Gefängnis in der ecuadorianischen Botschaft und jetzt ist er in einem sehr harrischen Gefängnis in belmarsch für wie lange mehr als vier Jahre nachdem mehr als ein Jahrzehnt seines Lebens von diesen Kampf aufgezählt wurde gleichzeitig habe ich Julian glaube ich im Jahr 2018 besucht und obwohl das das letzte Mal war dass ich mit ihm gesprochen und ihm persönlich gesehen habe war er definitiv von den Ereignissen betroffen er war auch sehr sehr entschlossen und Prinzipien treu zugleich er ist offensichtlich jemand der in seinem Leben die Entscheidung getroffen hat sich mit den mächtigsten Menschen der Welt anzulegen und der verstanden hat was das wahrscheinlich mit sich bringen würde glauben sie dass er dazu bereit wäre nämlich sich für Verbrechen schuldig zu bekennen die er nach allem was ich über diesen Fall weiß nicht begangen hat um endlich aus der Haft zu entkommen ich kann es nicht sagen kennen das kann ich nicht beurteilen ich glaube es ist sehr schwierig das zu beantworten ich kann das nur aus meiner eigenen Persönlichkeit meinem Charakter und meiner Vorstellung heraus beantworten was ich jedoch sagen kann ist dass die Umstände die dem Opfer die Last der Entscheidung auferlegen nicht angenehm sind nordkampfte und zweitens das im Fall von Assange jedes einzelne Menschenrecht dass sich aus den Konventionen des Asylrechts ergibt außer Kraft gesetzt worden ist [Musik] der Person Julien assange wird nun ein arrangement-angeboten bei dem er den Vereinigten Staaten nach seiner Erfahrung nach 13 Jahren Erfahrung mit den Vereinigten Staaten und dem Justizministerium vertrauen muss dass sie ihr Wort halten das ist wirklich sehr schwierig damit meinen sie dass er in die Vereinigten Staaten zurückkehren sich vor Gericht verantworten oder vor einem Bundesgericht in den Vereinigten Staaten erscheinen würde um sich schuldig zu bekennen und dann auf ihr Wort vertrauen würde dass er auf der Grundlage diese Vereinbarung wieder nach Australien entlassen würde ist das das Element des Vertrauens von dem sie sprechen eine Reise in die Vereinigten Staaten kommt einfach nicht in Frage man kann sich nicht Menschen ausliefern die offensichtlich versuchen einen zu töten aber das ist die eine Seite zweitens sagen sie okay du kannst nach Australien zurückkehren du kannst gehen und in dem Moment in dem Du in Australien ankommst heißt es dann oh aber wir haben diesen Anklagepunkt vergessen wir haben es versäumt dies vorzubringen und so weiter und so fort bis ans Ende deiner Tage ich kann mir vorstellen dass Julian den Umstand für sich nutzen kann dass die Unterstützung für eine Lösung in dieser Angelegenheit auf diplomatischem Wege weiter wächst ein bisschen Geduld könnte also von Vorteil sein du andere sagen zu mir weißt du da ist ein Fenster oder eine Tür da öffnet sich eine Tür oder ein Fenster und es wird sich bald schließen man muss eine Entscheidung treffen und also etwas aber ich sehe dass die Aktivitäten von Präsident Lula und Präsident operator in Abstimmung mit den Interessen Australiens eine richtige Lösung bringen werden damit meine ich nicht dass sich die Vereinigten Staaten entschuldigen werden und sagen es tue ihnen schrecklich leid dass sie hier einen Fehler gemacht haben aber ich sehe die Möglichkeit dass das Weiße Haus das Justizministerium bittet die Spionage Vorwürfe unter dem Vorwand zu prüfen dass sie den ersten Zusatzartikel der Verfassung der Vereinigten Staaten gefährden und in Verruf bringen die Hypothese die seit einiger Zeit vertrete und ich frage mich was sie davon halten ist dass die Regierung bei den überhaupt kein Interesse daran hat Julian Assange auf amerikanischen Boden zu bringen ihn in einem Bundesgericht im östlichen Bezirk von Virginia vor Gericht zu stellen wo er angeklagt werden würde und zuzulassen dass dieser Medien Zirkus von den Bemühungen ablenkt Joe Biden eigentlich unternehmen wollte dass Julien in den Zeugenstand treten kann dass die Welt erfährt dass Joe Biden als erster Präsident überhaupt versucht einen Verleger nach dem e-spionage Act zu verfolgen und dass jede ausländische Staatschef auf diesen Fall verweisen kann wenn die Vereinigten Staaten versuchen andere Regierungen mit weicher macht soft power zu kritisieren was sie wirklich wollten haben sie bekommen nämlich die Zerstörung von Wikileaks die körperliche und geistige Entmündigung von Julien über all die Jahre und sie wollen tatsächlich einen Ausweg sie waren sehr zufrieden damit dass ich die Sache durch das britische Gerichtssystem schlängelte wo Julian einfach nur festgehalten und nicht vor Gericht gestellt wurde aber ich kann mir keine Szenario vorstellen indem Sie Julien tatsächlich in die USA bringen und ihn vor Gericht stellen wollen sehen Sie dies auch so ja sehr sogar es gibt eine Anwaltskanzlei in Washington die WoW Holland eine Organisation für freie Presse und Wohltätigkeit mit Sitz in Deutschland 1,2 Millionen Dollar in Rechnung gestellt hatten Germany sollte diese Anwaltskanzlei eine Regelung finden erhalten Sie 1,2 Millionen Dollar aber die Regierung wird Ihnen einen Vertrag nach dem anderen in dreistellige Millionenhöhe geben wir verstehen also dass diejenigen die eine Lösung in dieser Angelegenheit für die Regierung finden Vorteile erhalten werden ja ich stimme mit diesem Szenario überein mit Ausnahme von folgen die Vereinigten Staaten haben in den letzten 21 Jahren siebeneinhalb Länder zerstört laut Brown University sind 4,6 Millionen Menschen direkt gestorben eine andere Studie der Brown University spricht von 38 Millionen Flüchtlingen wir können in keiner Weise guten Gewissen S oder in gutem Glauben für bestimmte Aspekte diese Regierung eintreten diese Teile der Regierung der Tiefe Staat wenn Sie das FBI die CIA und die NSA so nennen wollen sind die Urheber dieser Verfolgung sie sind also sehr fähig einfallsreich und in einigen Fällen bösartig und Sie werden einen Weg zu Durchsetzung ihrer Interessen finden das ist das Gegenargument zu der Annahme dass sie wirklich einen Ausweg aus diesem schmutzigen Schlamassel suchen das sie selbst angerichtet haben aber andere Akteure sehen den Ausweg aus dem Dilemma dass sie weiterhin anrichten oder aus den Tragödien in die sich Stürzen aus den Katastrophen die sie verwalten darin den Einsatz zu erhöhen ich erzähle Ihnen eine Geschichte die mich immer sehr beeindruckt hat und von der ich damals nicht einmal ganz überzeugt war das war bevor ich meine eigenen Verwicklungen mit der Regierung der Vereinigten Staaten hatte die jedoch die Wahrheit dieser Geschichte erwiesen einer der ersten Beteiligten am Wikileaks Projekt einer der Leute die 2010 an der Veröffentlichung der Irak und Afghanistan kriegsprotokolle der diplomatischen Kabel gearbeitet haben ist ein echter überzeugter Verfechter der Sache und besuchte Brasilien er war Bürger eines europäischen Landes und erzählte mir dass er beschlossen hatte zurückzutreten und sich nicht mehr an der Arbeit von Wikileaks zu beteiligen nicht aber weil er in irgendeiner Weise weniger an das Projekt glaubte im Gegenteil er glaubte mir denn je an die Fähigkeit des Projekts Transparenz zu schaffen aber er berichtete mir dass er keineswegs befürchtete dass seine Regierung eines Tages an seine türklopfen und sagen würde wir haben erhebliche Probleme mit ihrer Arbeit er war besorgt dass seine Regierung eines Tages an seine Tür klopfen und sagen würde die US-Regierung hat ein Problem mit dem was sie tun und wir sind hier um sie zu ihnen zu bringen und sie in ihrer Obhut zu geben und ich glaube manchmal fällt es den amerikanischen Bürgern sogar den Menschen im Westen schwer zu verstehen dass es wie eine Art konspirative oder übertriebene Einschätzung der US-Regierung klingt wenn man sagt dass sie zu allen fähig sind aber als jemand der ein Mitglied der Familie von Julien Assange ist oder der das aus nächster Nähe gesehen hat der es aus nächster Nähe von meiner Quelle Edward Snowden erlebt hat und die Dinge in die sie nicht nur unternommen haben sondern die sie planten ihnen beiden anzutun halten Sie sie für eine Art skrupelloses Subjekt den sie nicht vertrauen selbst wenn es so aussieht als ob das gesetzlich verankert wäre strong heute werden um noch einmal auf die von ihnen hervorgehobene strategische Bedeutung der Beziehungen zu Australien und die Strate die Position Australiens in sich entwickelnden Wettbewerb zwischen den Vereinigten Staaten und China zurückzukommen und das ist von Bedeutung es gibt wirklich gute Leute in den Vereinigten Staaten also das möchte ich nicht sagen die Regierung ist zu der Einsicht gelangt dass es eine gute Idee ist einen Ausweg zur Zufriedenheit der australischen Bevölkerung und Regierung zu finden denn wenn wir nur ein Beispiel nehmen dann verlaufen alle strategischen Kommunikationslinien die Indonesien China Indien Pakistan und Saudi Arabien den Golf dienen alle über den indischen Ozeanen indianische Australien als stabiler Verbündeter der Vereinigten Staaten oder wenn Sie so wollen als beständiges Gefährt sitzt im Indischen Ozean und überwacht die Gesamtheit dieser strategischen Verbindungslinien dies ist ein großer Vorteil für die Vereinigten Staaten in ihrem Wettbewerb mit diesen drei Nationen im Rahmen des machtpolitischen Verständnisses auf dass sie vorhin in unserem Gespräch eingegangen sind liegen die Lösungen meines Erachtens darin diese Vereinbarungen eindeutig zu treffen das Weiße Haus erklärt einfach oh ja wir haben bald eine Wahl wir müssen die Wirksamkeit und den tiefgreifenden Nutzen des ersten verfassungszusatzes für die Menschen in den Vereinigten Staaten in Betracht ziehen [Musik] diese Anklagen gegen Julien Arsch und das wird die Sache einfach verblassen lassen einige Leute werden sich empören und sagen das hätte man schon vor zehn Jahren tun können ich würde jedoch sagen dass sich die Umstände damals noch nicht zu entwickelt hatten wie wir es heute begreifen dass der erste Verfassungszusatz unterstützt werden muss letzte Frage die vermeintliche Quelle für die Veröffentlichungen die Julien zur Last gelegt werden und an denen er mitgewirkt hat Chelsea Manning wurde zu einer sehr langenhaft Strafe verurteilt und nach acht Jahren in einer wirklich harten Haftanstalt ich habe sie dort im militären Gefängnis in Fort Oliven Bros mitten in Kansas besucht hat Präsident Obama ihre Strafe aus humanitären Gründen aufgehoben wobei er im Wesentlichen sagte dass sie eine so harte Zeit abgesessen habe dass es an der Zeit seine sie aus humanitären Gründen frei zu lassen im Laufe der Jahre haben Juliens Ärzte berichtet dass er körperlich geschwächt sei sein geistiger Zustand habe sich verschlechtert sie haben Zweifel ob er ein US-Gefängnis überleben könnte sie haben gesagt dass sie echte Bedenken hätten was meinen Sie nach allem was Julien durchgemacht hat nach der Art und Weise in der ich sage nicht gern dass sie ihn gebrochen haben denn wie ich Julien kenne glaube ich nicht dass sie dies geschafft haben aber sie haben sicherlich sehr gute Arbeit geleistet um Wikileaks und Julians Arbeit stärkt zu behindern überflüssig dies zu sagen was ist Ihrer Meinung nach das Motiv der Regierungsseite die weiterhin darauf besteht dass er verfolgt bestraft inhaftiert und am Ende seine Person gebrochen wird [Gelächter] es ist ziemlich eindeutig dass sie verhindern wollen dass Glen green wollt bei der Verbreitung von Informationen und Wissen in den Vereinigten Staaten eine so bedeutende Position einnimmt wie sagen wir die New York Times und als Folge davon in englischer Sprache auf der ganzen Welt wieder heil findet sie hoffen dass man Angst bekommt was wie ich glaube in den Konzernen schon ziemlich effektiv ist in corporate media um es in Bezug auf die Konzernmedien deutlich zu machen sie haben die Konzernmedien unterdrückt das sehen wir die ganze Zeit die Fersen aber es gibt jetzt 50.000 andere die Informationen herausgeben und unter diesen 50.000 gibt es herausragende Persönlichkeiten wie Glen greenwold und andere zum Beispiel und so weiter die jetzt ins Gespräch kommen und erst neulich habe ich gesehen dass Tacker Carson 195 Millionen Aufrufe seiner Sendung erreicht hat bei Fox hatte er nie mehr als 6 Millionen wird das ist also die neue Welt die sich vor unseren Augen auftut und ich hoffe dass Julien wieder in dieser Welt willkommen geheißen werden kann das hoffe ich auch und ich glaube ich war noch nie so optimistisch dass wir zu einer Lösung kommen werden es klingt danach dass sie zumindest mit Vorsicht die gleiche Ansicht vertreten hoffentlich ist Julien dann wieder frei und kann seine Arbeit erledigen ich hoffe dass Ihre Reise hier nach Brasilien in Kürze auch dazu beitragen wird und lassen Sie mich fragen denn normalerweise versuchen die Menschen die dies hören und die meisten Zuschauer unserer Sendungen sind definitionsgemäß Anhänger unabhängiger Medien und unterstützen die Idee dass Menschen der US-Regierung gegenüber feindlich gesinnt sein sollen was können diese also zur Unterstützung von Julien Sache tun zwei Dinge das eine ist der Logos sprechen Sie weiter über die Angelegenheit und insbesondere über die versuchte Zerstörung des ersten Verfassungszusatz des der Vereinigten Staaten in Bezug auf Julian Assange das andere ist mit den Menschen im Kongress zu sprechen schließlich leben sie von den Bürgern der Vereinigten Staaten und sie müssen ihre Politik an die Umstände anpassen nochmals vielen Dank für die großartige Arbeit diese Leisten und danke dass Sie sich an einem Sonntag die Zeit nehmen um mit uns zu sprechen ich weiß das wirklich zu schätzen danke klären es ist der falsche Mann der in diesem Stuhl sitzt es sollte Julien sein das wird in Kürze der Fall sein davon bin ich überzeugt vielen Dank dass Sie sich diesen Clip von System Update angesehen haben unsere Live-Show die jeden Montag bis Freitag um 19 Uhr Ostküste exklusiv auf Rumble ausgestrahlt wird sie können die kompletten nächtlichen Sendungen live sehen oder sich den Bestand an Episoden kostenlos auf unserer Seite ansehen außerdem finden Sie die vollständigen Episoden am Morgen nach der Ausstrahlung auf allen wichtigen Podcasting Plattformen einschließlich Spotify und Apple alle Informationen die Sie benötigen sind unten verlinkt wir hoffen Sie dort begrüßen zu dürfen [Musik]</t>
+  </si>
+  <si>
+    <t>LZ6Ms_zp3Vo</t>
+  </si>
+  <si>
+    <t>Arnsberg im Hochsauerland es ist die Heimat des Friedrich Merz und es ist der Ort an dem der CDU-Vorsitzende die Brandmauer seiner Partei endgültig ins Wanken bringt im zdf-sommer Interview erklärt märz die Zusammenarbeit mit der AFD auf kommunaler Ebene für möglich wir sind doch selbstverständlich verpflichtet demokratische Wahlen zu akzeptieren und wenn dort das noch mal ein Landrat ein Bürgermeister gewählt wird der der AFD angehört ist es selbstverständlich dass man nach Wegen sucht wie man dann in dieser Stadt weiter arbeiten kann im Netz ist das Entsetzen groß Rechtsruck und wäre den Anfängen lauten die Hashtags und auch aus der Partei selbst kommt klare Kritik die AFD kennt nur dagegen und Spaltung wo soll es dazu Zusammenarbeit geben die CDU kann will und wird nicht mit einer Partei zusammenarbeiten deren Geschäftsmodell hat Spaltung und Ausgrenzung ist so der Regierende Bürgermeister von Berlin und die stellvertretende Bundesvorsitzende und Bildungsministerin aus Schleswig-Holstein erklärt die Beschlusslage ist klar und ich kann mir für meine Partei nichts anderes vorstellen keine Zusammenarbeit mit Extremisten was sie meint ist der Parteitagsbeschluss von 2018 in dem die CDU jegliche Zusammenarbeit mit der AFD ausschließt und den auch Friedrich Merz immer wieder verteidigt hatte klares Kalkül gerade in Zeiten wie diesen trägt jede demokratische Partei und damit auch jede demokratische Politiker Verantwortung wenn es um die Verteidigung der Demokratie geht und wenn solche Aussagen alle drei Tage von Friedrich Merz kommen muss man ganz klar sagen dass er diese Verantwortung nicht gerecht wird Friedrich Merz hat in seinem Sommer Interview klar gemacht dass die CDU weiter nach rechts rutschen wird das was sich vor einer guten Woche mit dem Generalsekretär in einer Person festgemacht hat macht sich jetzt eben auch thematisch fest tatsächlich folgt März Erklärung einem Kurs der sich schon in den letzten Wochen angedeutet hatte erst die Rede von den Grünen als Hauptgegner die Hauptgegner sein dann der neue Generalsekretär Abteilung law and order und vor einer Woche die Forderung nach einem schärferen Kurs in der Migrationspolitik und einer Abschaffung des individualrechts auf Asyl auch hier legte März gestern nach das ist ein konstruktiver Beitrag wir werden das in der Bundestagsfraktion auch noch mal Vertiefen der Ton wird also rauer die politische Richtung klarer das Ziel die afd-zahlen runter zu kriegen und die eigenen hoch doch ob der Weg der richtige ist daran haben auch innerhalb der CDU manche Zweifel und nicht nur da sprechen wir über all das jetzt mit dem Generalsekretär der SPD Kevin Kühnert schönen guten Morgen guten Morgen aus dem schönen Allgäu Herr Kühnert sie haben die Äußerungen von Friedrich Merz ja auch schon kommentiert das Argument von Friedrich Merz ist ja der Pragmatismus wir sein verpflichtet demokratische Wahlen anzuerkennen sagt er und dazu gehören auf unterster also auf kommunaler Ebene auch mit den Umfrage oder besser gesagt mit den Wahlergebnissen der AFD umzugehen das abzulehnen nach dem Motto hauptsache nicht mit der AFD das ignoriert doch den WählerInnen sie sprechen die Passage in dem sommerinterview von Friedrich Merz an die mir am meisten Kopfzerbrechen bereitet denn den Kurswechsel den eher als Vorsitzender offensichtlich jetzt für seine CDU anstrebt die baut er auf einer totalbrüchige Argumentation auf er sagt wir müssen doch demokratische Wahlen anerkennen aber wer spricht denn dagegen der Landkreis Sonneberg hat jetzt einen AFD Landrat raguhnjeßnitz hat jetzt einen AFD Bürgermeister die AFD ist zu demokratischen Wahlen zugelassen sie kann Mandate erringen Sie ausfüllen hat alle parlamentarischen Rechte sie profitiert aus der Parteienfinanzierung nur auf eines hat sie die alle anderen Parteien auch kein Anrecht nämlich das politisch mit ihr kooperiert wird dass sie Teil der Mehrheiten vor Ort sein muss und genau hier stößt Friedrich Merz rein und sagt jetzt dass seine CDU vor Ort eben doch mit der AFD nach Mehrheiten offenkundig suchen kann und das ist der Tabubruch und hier muss klar und deutlich widersprochen werden aber Herr kühn hat mancherorts weiß man doch gar nicht wie man überhaupt gegen die oder ohne die AFD eine Regierung bilden soll ist das nicht ganz pragm atisch gesehen teilweise unumgänglich im Moment ist die Lage so in jedem Landtag in Deutschland in jedem Kommunalparlament gibt es Mehrheiten ohne die AFD und März versucht sich jetzt hier an Ablenkungsmanövern natürlich kann man mit dem AFD Landrat in Sonneberg und muss man auch nach der Geschäftsordnung mit ihm über das zustande kommen der Tagesordnung beispielsweise im Kreistag sprechen welche Anträge wann beraten werden aber schauen wir uns doch einmal die Aufgaben eines Landrates an es gibt übergeordnete Aufgaben da geht es um die Erfüllung von Vorschriften und von Gesetzen von Bund und Ländern das muss der Landrat machen er kann sogar disziplinarrechtlich herangezogen werden wenn er das nicht tut und das andere sind die inneren Angelegenheiten eines Landkreises die Aufstellung des Haushaltes und anderes mehr schulträgerschaften das entscheidet der Kreistag mit seiner Mehrheiten nirgendwo steht geschrieben dass das alles im Einvernehmen mit dem Landrat oder mit den Abgeordneten der Partei des Landrats passieren muss und so gibt es in Sonneberg in jedem anderen Landkreis in Deutschland Mehrheiten unter demokratischen Abgeordneten und die können genutzt werden wenn wir uns allerdings den Zulauf zur AFD anschauen und die Umfragewerte sind wir vielleicht bald von der ganz anderen Frage dann reden wir nämlich nicht mehr über kommunale Ebenen wie will man dann Politik gestalten wenn die Realität nach einer Wahl ist einfach nicht zulassen das können wir ja ein Stück weit im thüringischen Landtag See noch dort gibt es eine Mehrheit ohne die AFD aber es ist eben gerade die CDU die sich schwer tut eine Regierung die von einem linken Ministerpräsidenten Bodo Ramelow angeführt wird konstruktiv in der parlamentarischen Arbeit zu begleiten und da sehen sie das ganze Dilemma der CDU eine Partei die nicht in der Lage ist wenn Sie die Wahl zwischen Demokraten Ramelow hat und dem Faschisten höcke sich klar zu entscheiden mit wem man politische Mehrheiten hat bei führen will der ist tatsächlich nicht zu helfen und deswegen ist es jetzt Zeit wenn ich mir das erlauben darf als spd-generalsekretär zu sagen für eine Richtungsstreit in der CDU Herr Merz wollte gestern etwas klarstellen das Gegenteil ist der Fall das Netz ist voll mit Tweets von CDU Abgeordneten vom Regierenden Bürgermeister von Berlin vom Chef des arbeitnehmerflügels von Abgeordneten und vielen anderen mehr die empört sind die auf die Beschlusslage der CDU Verweis König ohne Land er wollte Dinge klarstellen das ist jetzt noch klar unklarer ich möchte jetzt gerne mal auf ihre Partei und die ampelregierung schauen ist die Stärke da AFD die Schwäche der ampelregierung nein die Stärke der AFD ist die Entscheidung von Menschen im Land die AFD zu wählen man kann unzufrieden mit einer Regierung sein und muss deshalb nicht AFD wählen ich bin gegen diese Entmündigung von Bürgerinnen und Bürgern bei denen wir so tun als würden höhere Mächte einen dazu zwingen eine großen Teilen rechtsradikale Parteien zu gehen die Mehrheit der Menschen im Land richten irgendwo müssen diese Umfragewerte herkommen und sie wissen auch dass viele Menschen im Land nicht zufrieden sind mit der Regierungsarbeit also die Frage stellt sich schon ob Ihre Partei zumindest eine Mitschuld am Erstarken der AFD trägt wir wissen sehr wohl wo wir auch Fehler gemacht haben da haben wir auch hier auch in ihrem Format regelmäßig in den vergangenen Monaten drüber gesprochen die Diskussion über das zustande kommen das heizungsgesetzes und anderes mehr da wollen und müssen wir besser werden das ist unser eigener Anspruch als SPD als Ampelkoalition aber nicht wegen der Stärke der AFD sondern weil es uns darum geht gute Politik in diesem Land zu machen aber es wird schwer das zu tun wenn wir von morgens bis abends nur noch über die AFD reden Herr März hat eine Viertelstunde gestern über die AFD geredet an die breite Mehrheit der Gesellschaft an deren Fragen zu lohnen Wirtschaft Fachkräfte Einwanderung hat er keine Worte verloren wir reden über wenigen im Land und vergessen dabei die vielen die sich langsam die Frage stellen ob man hier eigentlich AFD wählen muss damit die eigenen Probleme auch mal besprochen werden in der Gesellschaft und deswegen mein Appell lassen Sie uns in der zweiten Jahreshälfte stärker über Lohnfragen sprechen über die Wirtschaft ankeln und die Energiepreise bezahlbar machen da sind demokratische Parteien richtig aufgehoben gut dann noch eine Frage die nichts mit der AFD zu tun hat zum Schluss die Union sorgt ja auch für Wirbel mit neuen Forderungen zum härteren Umgang mit Flüchtlingen auf dem Mittelmeer und nach flächendeckenden Kontrollen an deutschen Außengrenzen wie kommentieren Sie das die Ampelkoalition kümmert sich ja ganz konkret um die Ordnung in der Migrationsfrage wir treiben migrationsabkommen mit den Herkunftsländern voran damit aus ausreisepflichtigen jetzt auch tatsächlicher ausreisen werden denn ausreisen führt man nicht mit krachledernden Reden herbei sondern damit dass man sein politisches Handwerk beherrscht und mit den entsprechenden Ländern kooperiert unsere Innenministerin hat gerade durchgesetzt dass es erstmals eine Mehrheit in Europa für ein solidarischen verteilmechanismus zwischen den Ländern gibt es sind reale Erfolge wenn es darum geht die Belastung gemeinsam schultern zu können und es ist ein großer Fortschritt gegenüber dem was die Union jahrelang in der Regierung selber nicht zustande bekommen hat also wir arbeiten längster daran sagte Generalsekretär der SPD Kevin Kühnert vielen Dank für das Gespräch ich danke Ihnen</t>
+  </si>
+  <si>
+    <t>VGlUHXc-DRE</t>
+  </si>
+  <si>
+    <t>e9WL4GI5hpI</t>
+  </si>
+  <si>
+    <t>im aktuellen RTL NTV Trendbarometer verlieren die Unionsparteien gegenüber der Vorwoche 2% Punkte und sinken auf 25%. im Gegenzug gewinnt die AFD 2% Punkte hinzu und steigt auf 21 Prozent dies ist der höchste je von Forza auf Bundesebene gemessene Wert für die Partei darüber hinaus lagen Union und AFD mit 4% nie so nah beieinander die SPD verliert einen Prozentpunkt und kommt auf 17% während die Grünen sich um einen Punkt auf 15% verbessern können die Werte für die FDP 6%, die Linke 5% und die Splitterparteien mit zusammen 11 % bleiben unverändert zur Vorwoche bei der Kanzler Präferenz verliert Friedrich Merz 2% Punkte gegenüber der Vorwoche Olaf Scholz muss einen Verlust von einem Prozentpunkte nehmen während sich jeweils um einen Punkt verbessern könnten in der kandidatenkonstellation Scholz mehr als Habeck würden sich somit aktuell 22% für Scholz 18 % für März und 17 % für habe ich entscheiden in der Konstellation Scholz März würden sich 24% für Scholz 21% für mehr als 18 % für Werbung entscheiden</t>
+  </si>
+  <si>
+    <t>dieser Podcast wird unterstützt von sofos ich bin Tobias Holub das ist Thema des Tages der Nachrichten podcast vom Standard [Musik] es ist absolute Statement wie absolute Flüchtlingslager Terror Milizen russische Wagner Söldner und jetzt auch noch ein Militärputsch die Lage im westafrikanischen Niger ist extrem angespannt aktuell beraten mehrere Nachbarländer sogar darüber ob sie dort militärisch eingreifen sollen um die demokratische Bewegungen Afrika zu retten wie sie sagen doch unabhängig davon ob in Liga bald einen Krieg ausbricht oder die Militärregierung an der Macht bleibt die Situation dort wird enorme Folgen für die Region haben und auch hier bei uns in Europa über die Angst von neuer massenhafter mig Mission über Terrorgefahr und wachsenden russischen Einfluss in Afrika darüber sprechen wir heute [Musik] Johannes Dieterich du berichtest für den Standard über den afrikanischen Kontinent und da gibt es in den letzten Wochen sehr viele Medienberichte über ein Land von dem viele vielleicht noch wenig gehört haben nämlich den Niger kannst du uns zur Einleitung kurz sagen warum wir darüber so viel berichtet was ist dort vor kurzem passiert ja also ganz kürzlich das war aber vor zwei Wochen nur ich habe so ein Kuh ein Militärputsch es war ziemlich überraschend und irgendwie auch schade weil der Westen hat es sich nach dem schon im Burkina Faso und das ist ein Nachbarland und Mali das auch Nachbarland statt Streich stattfand haben da auch die generelle oder ein paar generelle geputzt und dem besten wurde das ziemlich nervös aufgenommen weil man da sich auf den nieder zurückgezogen hatte nachdem man aus Mali und Tina fast so praktisch rausgeworfen wurde und jetzt ist auch der noch gefallen das war also praktisch die letzte Bastion des besten unruhig deswegen war das wichtig und es ist jetzt vor allem für den Westen aber natürlich auch für Afrika auch für die umliegenden Ländern ist das ein großes Problem das können wir uns gleich alles noch im Detail anschauen aber zum jetzigen Stand die Militärs haben das Land jetzt fest unter Kontrolle also die Bevölkerung akzeptiert das auch also entscheidend immer fester am Anfang dachte man doch dass man da noch mit Verhandlungen oder mit Drogen irgendwas machen könnte aber die sind anscheinend wirklich einigermaßen fest im Sattel es gab viele Delegationen die da jetzt hingeflogen sind eine von den USA eine von der Afrikanischen Union eine von eco was das ist der regionale Staatenverband und die wurden alle abgeschmettert die wurden gar nicht bis zum putschistenführer vorgelassen und merkwürdig war auch so ganz am Anfang des Fuß gab es eine Gegendemonstration gegen den Kuh die wurde dann von den Soldaten ziemlich schnell beendet und danach gab es dann immer größere pro Kundgebungen und das hat das Ausland schon überrascht weil man rechten Seite eigentlich nicht damit dass die Militär ist das eine Unterstützung hätten man weiß natürlich auch die ob das wirklich echte Unterstützung ist oder ob die man kann ja auch so dass man im englischen ja Leute irgendwie bezahlen oder reinschirme mit Bussen und den irgendwie was zu essen geben das sind Afrika dann doch einfacher das kann schon sein dass die Leute also nicht wirklich hinter mir sind aber dass die dazu praktisch verleitet oder manipuliert worden sind du hast schon ein sogenanntes Eco was Bündnis angesprochen von dem habe ich jetzt in dem Kontext auch schon was gehört was ist das für ein Bündnis und inwiefern haben die sich jetzt denn diese Situation im mega quasi eingemischt also es gibt ja die Afrikanische Union da ist praktisch ganz Afrika das sind 54 Staaten organisiert und dann gibt es für jeden Teil von Afrika also Westafrikaner Nordafrika Südafrika Ostafrika gibt es noch ein eigenes Bündnis und Eco was ist das Bild Afrika das sind 15 Länder verbunden vier davon sind jetzt suspendiert weil überall eine Militärdiktatur herrscht also das Militär die Macht übernommen hat und das ist nicht zugelassen nach dem Statut des staatenbündnisses also die schließen aus dass dann Militärdiktaturen Mitglieder sein dürfen und wo geputzt wird das liegt das Land automatisch automatisch suspendiert und eigentlich sind dann auch wirklich Maßnahmen vorgesehen die Eco was ergreifen muss um dieses Land praktisch zu bestrafen da gehören Sanktion dazu aber das kann bis zu einer militärischen Prävention gehen und steht so eine militärische Intervention im Niger jetzt auch im Raum genau also das war interessant weil die ersten zwei Länder wo China Phase und Mali wo geputzt wurde das war alles in den letzten drei Jahren dazu kam auch noch die näher aber die näher ist noch ein bisschen andere Fall also Mario da ist es sehr ähnlicher und hat Eco was denn schon Sanktionen erlassen und so weiter aber nicht mit militärischem eigen greifen bedroht inzwischen ist aber in Nigeria neue Präsident gewählt worden und der wurde auch gleich zum Eco was Präsidenten gekürt weil wir sowieso bei weitem das größte Land da ist und der hat eine interessante Vergangenheit weil als jüngerer Mann hat ja gegen die Militärdiktatur in seinem eigenen Staat demonstriert oder war politisch aktiv dagegen in Nigeria gab es ja auch in den 70er 80er Jahren eine Militär Diktatur nach der anderen und er wurde dann von einem Militär Diktator auch mal eingesperrt und der ist also wirklich leidenschaftlich gegen Militärregierung und der wollte das nicht zulassen oder der will das auch heute eigentlich nicht zulassen dass jetzt der dritte wegbricht von der Demokratie sozusagen und er ist halt doch eigentlich ein überzeugt demokratisch wahrscheinlich und sagt ist die einzige Staatsform wie unsere Länder irgendwie blühen können und Militärdiktaturen die sind einfach nicht gut für die Bevölkerung nicht gut für die Wirtschaft und rechnest du damit dass diese Eco was starten jetzt tatsächlich in niederdon militärisch intervenieren könnten also das ist wirklich zu einer Art Krieg kommt in der Region also es wird immer unwahrscheinlich aber die Widerstände gegen eine militärische Intervention sind doch ziemlich groß erstens mal natürlich die Staaten Mali und Tina sowieso hinter der Militärregierung stehen aber dann auch agieren und derzeit ist auch Nachbarländer zumindest her die haben sich auch dagegen ausgesprochen weil die einfach Angst haben dass das alles zu einer großen Tisch Stabilisierung führen wird und inzwischen hat sich auch das Senat von Nigeria dagegen ausgesprochen und da wird es wirklich ein Problem für den Präsidenten weil er braucht eigentlich die Zustimmung des Senats und wenn er die nicht hat dann kann er da auch nicht wirklich einmarschieren er müsste das begründen damit dass da wirklich akute Gefahr für sein stark ausgeht und das ist ja nicht so ich würde gerne noch ein bisschen über die Hintergründe dieses Landes und dieser Region sprechen damit wir das besser verstehen kannst du vielleicht das Land Niger für uns ein bisschen beschreiben also ist Teil der Sahelzone die geht ja ganz von Senegal also am Atlantik bis rüber in den Sudan Indischen Ozean das sind ungefähr so sechs sieben Länder nicht sehr oder Niger ist mittendrin ist ein großes Landes doppelt so groß wie Frankreich und im Norden ist es wirklich Sahara und in der Mitte ist sozusagen die Sahelzone da ist agar.es ist eine relativ bekannte Stadt die ist auch bekannt da kommen wir nachher wahrscheinlich zu sprechen drauf wegen den Flüchtlingen da ziehen ganz viele Flüchtlinge im Motor durch und weiter unten ist dann der Fluss in die Schere oder Liga und an dem liegt auch die Hauptstadt Miami und da ist es natürlich dann ein bisschen fruchtbarer aber im großen und ganzen ist es ein trockener Staat da ist höchstens oder vereint oder viehzuchtbetrieben Ackerbau der nur wenn es bewässert wird und wir haben bis jetzt die Beziehungen von Niger zu westlichen Ländern zu Europa zu den USA ausgeschaut ja also das letzte pulverwerk für den besten sozusagen da war ein anderer Präsident ist vor zwei Jahren an der Macht der war wirklich irgendwie so ein bisschen beispielhaft der kriegte dann auch so ein Preis für eine gute Regierungsführung und auch dafür dass er ohne zu versuchen Jäger im Amt zu bleiben nach der zweiten Amtszeit abgetreten ist also der Nachfolger dieses doch beispielhaften Präsidenten des war Mohammed der ist seit zwei Jahren in der Macht und der ist eigentlich fast noch freundliche gegenüber dem Westen gewesen der hat also möglich gemacht dass alle westlichen Soldaten als es sowohl Franzosen als auch Deutsche die konnten von Mali in den Share verlegen und von dort aus können die weitermachten mit ihrem Kampf gegen den Terror sozusagen also die Einsätze gegen islamistische Terroristen also die Franzosen konnten also da ihre Gruppen verlegen und die Amerikaner die US Streitkräfte die haben im Niger 2 große riesige thronflughäfen und von dort aus fliegen die mit ihren Kronen sehr oft in die Gegenden wo halt die Islamisten vermutet werden und werfen dann auch Bomben ab oder versuchen den schon auch da einzugreifen jetzt muss ich kurz nachfragen du hast gesagt dass auch französisches Militär dort ist und du hast ja schon ab und zu Niger zu dem Land gesagt sich das richtig dass dort Frankreich früher mal das Sagen hatte ja also Afrika war ja fast alles außer Äthiopien und Liberia waren ja alles Kolonien und wie du richtig sagst du mich sehr war französische Kolonie und es wurde glaube ich 1960 unabhängig und ist interessant ist natürlich mit allen französischen Kolonien das Frankreich noch sehr lange mit seinen ehemaligen kolonial-nation ziemlich eng verwandelt war ich unbedingt immer zum Wohl der Bevölkerung aber zum Wohl von Eliten und das hat die Bevölkerung sehr oft gegen Frankreich aufgebracht also es gab wirtschaftliche Beziehungen noch vieles gibt zum Beispiel die Währung in Westafrika ist immer noch an den Fonds ursprünglich also jetzt an den Euro gebunden und das sind die Abhängigkeiten doch schon noch sehr groß die Verbindung positiv also viele studieren in Frankreich aber auch die Abhängigkeiten wirtschaftlich und so weiter es gibt zum Beispiel in die share auch eine große uranine und da geht es meistens die französische Atomkraftwerke und es hat immer der Elite des Landes geholfen und die haben davon profitiert und die fanden das gut aber die breite Bevölkerung hatte davon wenig und die wurden eigentlich immer verstimmter über den großen Einfluss Frankreichs und das wird sich doch jetzt verheerend aus von einem Land nach dem anderen also da werden sofort immer ein differische resortiments gewählt und interessanterweise werden die jetzt durch russische Loblieder ersetzt also jetzt ist plötzlich Russland das Land des Kolonialismus überwindet und in afrikanischen Ländern wirklich hilft eine vollkommene Fehleinschätzung aber so ist es nun mal von einer französischen Kolonie zu russischem Einfluss wie das passieren konnte schauen wir uns gleich noch genauer an wir sind gleich zurück [Musik] jedes Unternehmen jede it-security-abteilung und jeder IT-Umgebung ist anders deshalb bietet sofos mit Cyber Security Service individuelle Möglichkeiten ohne großen Aufwand an erfahrenes red-tunting-team kompatibel zu Ihren Anforderungen einzusetzen mehr als 17.000 Kunden vertrauen bereits auf sofus MDR dessen Service auch in Kombination mit security tools anderer Hersteller möglich ist jetzt informieren unter www.sofus.de/mdr Johannes jetzt hast du erst erzählt dass es da in Niger oder Niger gerade sehr viel politischen Aufruhr gibt das ist das sehr viel Auflehnung gegen die frühere französische Kolonialzeit gegeben hat und das ist jetzt aber russischen Einfluss gibt warum russischen Einfluss ich glaube angefangen hat es mit Mali in Mali war nach der Kolonialisierung das war glaube ich dir wirklich marxistische oder kommunistische Regierung und die hatten enge Verbindung zu Sowjetunion dann viele studiert die Militärs wurden da ausgebildet und so weiter die Waffen die Malik gekriegt haben kann von von Russland also diese Verbindung waren der sehr stark und die wurden jetzt reaktiviert das war ganz einfach wenn Sie die Leute kannten noch ihre Leute aus der Sowjet Zeit und ich glaube dass ich das jetzt dann auch auf Burkina Fassung und auf den Niger einfach ausgebreitet hat und in Mali kam dann sogar diese russische Gruppe die Wagners zum Einsatz also die Wagner sollten von denen wir in der Ukraine so viel gehört haben muss auch schon oft geheißen hat die sind auch in Afrika anscheinend tatsächlich aktiv du hast vorher auch angesprochen dass die ganze Region ein Zentrum des islamistischen Terrors ist kannst du das noch ein bisschen beschreiben welche Gruppen gibt es dort irgendwie groß ist dieses Problem wirklich ja das ist wahrscheinlich die größte Region in der Welt wo der extreme Islamismus oder islamische Extremismus wirklich noch ein großes Problem ist ein riesen Problem also es ist interessant ist ja schon mal das ist ja eigentlich nicht in afrikanisches Problem das ist ein importiertes Problem das Problem entstand ja in Afghanistan als die Amerikaner die mutscher Ideen die gegen die Russen oder gegen die Sowjetunion gekämpft haben unterstützt haben die haben sich dann auch gegen die Amerikaner irgendwann gewandt und es wurde dann praktisch fast nicht globale oder mindestens im arabischen und afrikanischen Raum Bewegung das ist natürlich vor allem alkaida und dann inzwischen als praktisch konkurrenzorganisation der islamische Staat beide haben in Afrika wieder viele kleine unterdrücken und im Nigeria das sind sicher auf jeder Seite zur fünf oder so Gruppen aktiv und die sind also immer entweder mit dem islamischen Staat verbündet oder mit al-Qaida und ab und zu gibt es da zwischen denen auch Krach und eventuell sogar Kämpfe aber als in dieser Region sind wirklich eine große Zahl an Extremisten tätig und interessant ist auch dass der Ursprung dass die plötzlich so stark wurden das hat sehr viel mit der Bombardierung Libyens durch die NATO zu tun also das war in den letzten Tagen als der arabische Frühling auch Libyen erreicht hat und die Bevölkerung dagegen protestiert hatte ist ja dann der beste auf der Seite der Bevölkerung sozusagen oder der Rebellen oder ja der Aufständischen gegen Kathi eingestiegen und hat bombardiert und das Land ist dadurch hat es eine Regierung verloren und wurde sehr chaotisch und ihn lieben gab es unglaublich viele Waffen das war ja ein relativ reiches Land und dafür hat auch viel rebellenbewegungen unterstützt und deswegen haben da viele Waffen sind da verkehrt und als das dann zusammenbrach Libyen diese Waffen kam dann in die Nachbarländer und mit ihnen ganz verschiedene Rebellen und Islamisten und so weiter und es wurde in gemischt das jetzt die Sache hält so eine wirklich sehr sehr schädigt und sehr distabilisiert und das war wie gesagt also einerseits der Islamismus mehr anti-bestliche islamistische Bewegung und andererseits mit den Waffen und mit der ganzen Militarisierung die von Libyen ausgehen und das hat sich zu einem exklusiven gemischt verbunden also es hat er in der Vergangenheit schon einige Krisenherde gegeben und was denkst du denn wären dann jetzt die Folgen im Niger tatsächlich ein größerer Konflikt ausbricht zum Beispiel mit diesen ecowas-staaten wenn es dazu einem Krieg kommen würde was würde das für Europa bedeuten also ich finde das unglaublich schwer zu beantworten weil es könnte natürlich sein wenn die ecovers starten sehr raffiniert Vorgehen also zum Beispiel ist das Militär im Niger nicht wirklich ein Block da gibt es verschiedene Strömung die könnten die gegenseitig ausspielen wenn die dann irgendwie mit der Invasion aus der Luft arbeiten würden könnte sein dass das Verschieben total schnell zusammenbricht und dann wieder die Zivilregierung eingesetzt werden könnte aber es kann auch sein das kann man bei so militärischen einsetzen deswegen sind wir ja auch immer so gefährlich kann man das nie so richtig Voraussagen und es könnte sein dass sich das dann in einem Flächenbrand entwickelt dass die Islamisten gestärkt werden und dass der Konflikt zwischen dem egoist-staaten und den Militär Diktaturen länger und größer wird und blutig wird und das kann natürlich wirklich fürchterliche Dimensionen an dem wie eben in Afghanistan oder in Libyen oder im Irak in diesen ganzen Ländern wo auch vorher schon Invasionen oder militärische Aktion stattgefunden haben das doch vorher schon Flüchtlingslager erwähnt das heißt es könnte wahrscheinlich zu mehr Migration kommen aus der Region oder absolut aber das könnte in beiden Fällen so sein also wenn sich die Militärregierung tatsächlich etabliert und stabilisiert dann ist davon auszugehen dass die Islamisten eher verstärkt aktiv werden so war es auf jeden Fall in Mali Mali versucht es Militär mit dieser russischen Truppe Wagner in die Islamisten zu kämpfen und die gehen unglaublich hat vor also politisch Verletzung sämtlicher Menschenrechte und das nutzen die Islamisten wieder aus und die Bevölkerung auf ihre Seite zu bringen weil die Bevölkerung sieht was sie damit uns machen was sie haben nämlich das macht was diese russischen machen das ist ja einfach vollkommen unakzeptabel und die schließen sich dann eher den Islamisten an die werden stärker und dann wird dieser Konflikt eher angestachelt das selbe ist in die Schere dann zu befürchten und dann würde es bedeuten dass natürlich auch so migrationsbewegung wieder verstärkt werden also das ist wirklich eine sehr komplizierte und vielschichtige Situation dort siehst du irgendeine Perspektive dass sich das wieder beruhigte nächster Zeit aber das beste war natürlich wenn man die Militärregierung jetzt wirklich entweder durch Verhandlungen oder durch ein wirklich smarten und guten Einsatz entmachten könnten ich glaube dass die Wahrscheinlichkeit nicht sehr groß ist dass das passiert also dann wird sich eher die Militärregierung etablieren und dann bleibt ein Problem und ich weiß auch nicht wie die Egoist starten denn sicherstellen wollen das war jetzt das vierte Land in ihrem Bereich zum Militär Diktatur wurde das nicht in 567 zu kommen irgendwann müssen die ja schon sicherstellen dass das nicht einfach weitergeht und du hast doch gesagt das war eine der letzten westlichen Verbündeten eine der letzten Bastionen des Westens wenn man das so sagen kann in der Region denkst du kann der Westen irgendetwas beitragen um die Situation zu verbessern oder wie sollte man da vorgehen auch angesichts der schwierigen Vergangenheit die europäische Staaten in der Region hatten genau also eigentlich wäre das Beste wenn sich der besten total zurückhalten würde weil wie du sagst alles was so als westliche Einflussnahme interpretiert werden kann wird von der Bevölkerung der natürlich sehr sehr stark abgelehnt und die französische Regierung hat schon falsche Töne erwischt als sie sagte sie würden ihre Interessen verteidigen in die Schere das ist natürlich unglaublich sowas zu sagen wenn sie können ja alle Denkweise schwingt dann doch mit und in Westafrika sagt jeder auch diejenigen die mit Frankreich ein bisschen sympathisieren oder ein westliches Sympathien haben das Beste wenn Frankreich wirklich den Mund hält und sich dann nicht einmischt und und dasselbe gilt natürlich auch für die Vereinigten Staaten also da tut sich aktuell noch sehr viel und am Donnerstag gibt es auch den nächsten großen Gipfel der Ecowas die sich mit dem Thema weiter beschäftigen der Gipfel wird leider erst nach Redaktionsschluss dieses Podcasts zu Ende gehen also die aktuellsten Informationen zur Situationen nie geöffnet man immer auf der standard.at aber danke dir Johannes Dieterich dass du uns heute vor allem die Hintergründe besser erklärt hast vielen dank vielen Dank alles Gute wir machen jetzt dann gleich noch weiter mit unserer meldungsübersicht und sprechen unter anderem über die ebenfalls schwierige Lage im südamerikanischen Land Ecuador und über die Zukunft der veganen Kochlehrerin in Österreich wenn Sie liebe Zuhörerinnen und Zuhörer die journalistische Arbeit die wir hier beim Standard machen unterstützen möchten dann geht das zum Beispiel indem sie uns abonnieren man kann die Zeitung abonnieren man kann für die Website der standard.at ein Abo abschließen oder wenn Sie unseren Podcast über Apple Podcast hören dann kann man dort auch ein paar Euro kein Premium Abo bezahlen und in Zukunft ohne Werbung hören und vor allem sehr unterstützen also vielen Dank dafür wir sind gleich wieder da jedes Unternehmen jede it-security-abteilung und jeder IT-Umgebung ist anders deshalb bietet sofos mit Cyber Security Service individuelle Möglichkeiten ohne großen Aufwand eine erfahrenes rect hunting-team kompatibel zu Ihren Anforderungen einzusetzen mehr als 17.000 Kunden vertrauen bereits auf sofus MDR dessen Service auch in Kombination mit security tools anderer Hersteller möglich ist jetzt informieren unter www.sofus.de/mdr und hier ist was sie heute sonst noch wissen müssen erstens im südamerikanischen Land Ecuador oder ein Kandidat für die Präsidentschaftswahl erschossen ein Tatverdächtiger wurde schwer verletzt festgenommen die Behörden konnten seine Identität oder Motive bisher aber noch nicht festmachen der Ermordete Kandidat hieß Fernando wieder vicenzio und war früher als Journalist tätig dabei hat er sich vor allem gegen Korruption und Missstände in Ecuador ausgesprochen vor rund einem Monat wurde schon ein lokaler Politiker in Ecuador ermordet danach hat er wieder vicenzio gesagt sich zu verstecken während kriminelle Bürger und Bürgerinnen ermorden wäre ein Akt der Feigheit nachdem nun aber auch wieder vicenzio ermordet wurde hat der bisherige Präsident den Ausnahmezustand im Land ausgerufen er schreibt in den sozialen Medien das organisierte Verbrechen seit zu weit gegangen es werde mit der ganzen Härte des Gesetzes bestraft werden die Präsidentschaftswahl in Ecuador soll trotzdem wie geplant am 20 August stattfinden sie wurde notwendig nachdem der bisherige Präsident wegen Korruptionsvorwürfen das Parlament auflösen wollte zweitens in Österreich könnte es bald eine eigene Lehre für vegane und vegetarische Köchinnen geben entsprechende Vorschläge und eine Diskussion um das Thema sind schon Anfang des Jahres aufgekommen jetzt liegt ein fertiger Entwurf in der Wirtschaftskammer der schon in den nächsten Monaten nun auf Herz und Nieren geprüft werden der Entwurf kamen überraschen schnell denn große Teile der kochbranche standen dem Thema kritisch gegenüber sie fürchten eine fleischlose Lehre würde das Kochhandwerk in Österreich verbessern und weniger prestigeträchtig machen befürworter:innen auf der anderen Seite sagen dass immer mehr Restaurants und auch Kundschaft auf vegetarisches und veganes Essen setzen mit einer professionellen Ausbildung könnte Österreich dabei in Zukunft eine Vorreiterrolle einnehmen die zuständigen Stellen sollen sich nur noch dieses Jahr mit dem Thema befassen die ersten veganen und vegetarischen Köchinnen könnten dann im Herbst 2024 ausgebildet werden und drittens im gestrigen Podcast haben wir schon gehört wie viele Schritte pro Tag wir gehen sollten um gesund zu bleiben Spoiler weniger als 10.000 reichen auch schon aber heute gibt's noch einen zweiten praktischen Tipp wie man den Blutdruck senken kann nämlich mit Planken Planking das kennen wir ja schon aus dem berühmten Video und dem der ORF ankerman Armin Wolf flach auf seinem Studio Tisch gelegen ist einfacher geht's aber auch den Boden abgestürzt auf die Unterarme und die Zehenspitzen ganz offiziell heißt das dann isometrisches Kraft Training und das ist dort Fachleuten für den Blutdruck sogar noch besser als klassisches Ausdauertraining also z.B eine Runde laufen gehen ein regelmäßiges isometrisches Krafttraining könnte demnach ähnlich effektiv sein wie ein Medikament gegen Bluthochdruck aber da muss man natürlich immer mit der Ärzte darüber sprechen was Mediziner aber in jedem Fall sagen gegen Bluthochdruck ist jeder Sport besser als kein Sport wenn Sie die nächste Planking Session noch ein bisschen herausfordernder machen wollen dann können Sie ja über dem Smartphone Planken und währenddessen ein paar Artikel auf der standard.at nachlesen dann wissen Sie auch gleich alles Wichtige zum aktuellen Weltgeschehen und falls auch das noch nicht genug Sport für Sie ist dann gehen sie doch eine Runde wandern währenddessen können Sie dann auch gleich die neue Folge unseres Schwester Podcasts besser leben anhören denn darin geht's um die Frage warum und wann dein glücklich macht und wie man auch ohne Auto auf den nächsten Berg kommt besser leben finden Sie überall wo es Podcast gibt falls Sie Feedback oder Anregungen für uns haben dann schicken Sie gerne eine Mail an Podcast add-standard.at und wenn Ihnen diese Folge von Thema des Tages gefallen hat dann abonnieren Sie uns am besten auf Ihrer Liebsten Podcast Plattform dann verpassen Sie auch keine weitere Folge mehr mit der Gelegenheit freuen wir uns auch sehr über nette Kommentare oder gute Bewertungen dadurch finden uns noch mehr Menschen in Zukunft vielen Dank dafür ich bin Tobias Rudow und an dieser Folge geht außerdem Schuld Wilhelm mitgearbeitet vielen Dank fürs zuhören und bis zum nächsten Mal [Musik] jedes Unternehmen jede it-security-abteilung und jeder IT-Umgebung ist anders deshalb bietet sofos mit Cyber Security Service individuelle Möglichkeiten ohne großen Aufwand an erfahrenes fragt hunting-team kompatibel zu Ihren Anforderungen einzusetzen mehr als 17.000 Kunden vertrauen bereits auf sofus MDR dessen Service auch in Kombination mit security tools anderer Hersteller möglich ist jetzt informieren unter www.sofus.de/mdr</t>
+  </si>
+  <si>
+    <t>4.5</t>
+  </si>
+  <si>
+    <t>-EKjEbn7FNo</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>-1</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>Markus rohhofer in der Gemeinde nahen in Oberösterreich ist vor kurzem eine Joggerin durch einen Hundebiss ums Leben gekommen die Besitzerin dieses Hundes ist schwer verletzt sie und ihre Lebensgefährtin halten noch weitere Hunde Markus du warst in dieser Gemeinde vor Ort was hast du dort mitbekommen ich komme gerade aus naden in Oberösterreich eine kleine ja unschbare Marktgemeinde die ser vom Radtourismus lebt ob dort jetzt im Gemeinder ein langes Gespräch ich mit dem Bürgermeister Martin geisbauer der bisschen die Situation vor Ort geschildert hat einerseits erst natürlich jetzt große Angst der Ort ist klein jeder kennt jeden und es hat gestern den ganzen Nachmittag bis in die Abendstunden Gespräche mit der Lebensgefährtin gegeben vor Ort es waren quasi gutacht in dem Haus die einerseit gesagt haben was z.B die örtlichen Gegebenheiten wie der Zaum zu klein ist das heiß da sowieso eine Erhöhung bedurft und die Besitzerin hat sich zunächst sehr standhaft geweigert die Hunde ein Pflegeplatz zu vermittel herzugeben es hat dann noch eine Vertrauensperson wurde hinzugezogen und man hat sich letztlich in den Abendstunden geeinigt die vier verbleibenden Hunde und die sieben Welpen man sagt an einem sicheren guten Pflegeplatz irgendwo in Österreich zu bringen es ist auch nicht geplant dass dort jemals wieder Hunde hinkommen der Bürgermeister hat theoretisch des B ein Zuchtverbot auszusprechen also die Damen waren gemeldet offiziell als Zuchtverein für diese Rasse im Gespräch hat er gesagt diese Option wird jetzt geprüft eben Zuchtverbot ausz sprchen de facto sind dort keine Hunde mehr und werden auch nicht mehr hinkommen und das wird jetzt im Ort versucht gesagt auch mit Hilfe von einem superweiser Psychologen bisschen diese kreben wieder zu kitten einerseits Trauerarbeit zu leisten weil wie gesagt in diesem kleinen Ort jeder jeden kennt und das hat die Gemeinde natürlich schon bis ins Mark geschüttert mhm weil dort wahrscheinlich auch einfach die Menschen jetzt Angst haben dass sowas wieder passieren könnte oder die Angst war riesengoß es hat wie die Kollege schon gesagt hat eiglich vorher keine Vorfälle gegeben W man dort mit den Einwohnern spricht was ja die Situation ne wie oft ist war da anreiner als verziergänger beim Zaun vorbeige dass der Hund hat bellt aber zumind sind keine prininzligen Situationen bekannt das was auch noch sehr aktuell ist ist dieser Punkt den die Experten von Anfang angezweifelt haben dass der Hund völlig unmotiviert plötzlich die jogerin angefallen hat habe ich gestern mit Experten gesprochen die sagen das gibt's eigentlich nicht da gibt's immer eine gewisse Eskalationsstufe da passieren Dinge vorher und mir wurden heute in der Früh auch Fotos zugespielt von diesem suchtverein von seinem abrchteplatz wo offensichtlich ganz klar erkennbar ist dass dieses Tier ein schutzhundeprogramm durchlaufen hat das heißt Schutzprogramm ist z.B in Wien strickt verboten und ist vorem Einsatzkräften vorbehalten wo es wirklich um Angriff auf den Mann geht um Überwältigung über absoluter Schutz des Hundehalters und diese Fotos deuten sehr klar drauf hin dass dieser Hund durchaus auf Schaf getrint worden ist und das ein möglicher undund auch ist umum die Situation so eskaliert ist mhm also da muss die Polizei jetzt noch genau untersuchen ob da wirklich der Hund bewusst auch aggressiver trainiert worden ist versteh ich das richtig es gibt viele Möglichkeiten diese auslöser können bis hin zu einer mögliche Erkrankung des Hundes sein das heiß das hat schon Fälle gegeben in der Vergangenheit wo man d bei der Obduktion des totenes gemerkt hat dass der irgendein Tumor hat und das das auslöst kann genauso sein dass dieses Bewegungsmuster nämlich der chockerin wie oft auch bei Radfahren ist den Hund irritiert hat wenn ich mit einer Hundetrainerin Rede sagt sie ist ungewöhnlich dass solche Tiere die so etwas tun im Vorfeld nie aufgefallen sind das heißt nie irgendwie gezwickt haben nie irgendwie bei anderen Hunden eartig reagiert haben nie irgendwie auffällig waren W me Menschen anem Ort waren das he das ist sehr unwahrscheinlich dass es da keine Signale vorgegeben [Musik] [Musik] hat wie können wir die erderhitzung stoppen wie verändert Intelligenz unser Leben und wann wird nachhaltiges Reisen endlich einfacher um diese und viele weitere Themen geht es im Podcast Edition Zukunft und Edition Zukunft [Musik] Klimafragen ich bin alia Prager und ich bin Jul Beirer wir sprechen über Lösungen für das Leben und die Welt von morgen jeden Freitag gibt's eine neue Folge überall wo es Podcasts [Musik] gibt ه</t>
+  </si>
+  <si>
+    <t>W1-b1aqca6I</t>
+  </si>
+  <si>
+    <t>[Musik] ich bin Tobias holup das ist Thema des Tages der nachrichtenpcast vom [Musik] Standard der moderne Staat ist da er ist jedenfalls zum Greifen nah stellen Sie sich vor die ÖVP Affäre rund um Inseraten Korruption wäre schon aufgedeckt worden als Sebastian Kurz noch nicht mal Bundeskanzler war nicht nur Österreichs Politik sehe heute wohl ganz anders aus möglich wäre das gewesen wenn es in Österreich nicht ein striktes Amtsgeheimnis gebe doch dieses Amtsgeheimnis könnte jetzt fallen und zwar durch ein neues Informationsfreiheitsgesetz auf das sich ÖVP und Grüne geeinigt haben das ist für die Republik Österreich ein monumentaler Kulturwechsel in Wahrheit eine transparenzrevolution wir schauen uns heute an welche Geheimnisse dadurch bald herauskommen K könnten und wann Österreich seine infofreiheit [Musik] bekommt Sebastian Fellner du hast für den Standard heute eine sehr wichtige Pressekonferenz besucht von den Ministerinnen Werner Kogler und Karoline etstadler indem es um ein sehr einflussreiches Gesetz mit einem sehr sperrigen Namen geht ja tatsächlich das Amtsgeheimnis wird abgeschafft das Grundrecht auf Informationsfreiheit kommt information freiheitsgesetz Sebastian warum sollte mich das interessieren weil du in diesem Staat regiert wirst das Konzept unseres Staates und der meisten anderen demokratischen Staaten ist dass die Bürgerinnen und Bürger ein Stück ihrer Freiheit und ein Stück ihres Geldes abgeben um quasi eine staatliche Organisation zu genießen und dadurch Sicherheit zu bekommen und der Kern der Informationsfreiheit ist dass wenn der Staat eine Information hat dass auch Du diese bekommen sollst wenn du sie haben willst also dass ich quasi herausfinden kann was sich da hinter den Kulissen abspielt und das ist jetzt so wie ich das verstanden habe oft nicht so weil es ein sogenanntes Amtsgeheimnis gibt oder genau in Österreich herrscht das Amtsgeheimnis es steht im Verfassungsrang das ist ein Gesetz aus der Monarchie und es funktioniert auch genauso nach rund 100 Jahren wollen wir das Amtsgeheimnis abschaffen der Kaiser wollte nicht dass seine Untertanen in die Schublade schauen können was er da für Dokumente drin hat aber ein modner Staat sollte halt anders funktionieren das Amtsgeheimnis hatte damals den Sinn die mächtigen zu schützen auch jetzt herrscht es noch in dem Sinn vor allem dass es eine kulturelle Sache innerhalb der Behörden ist dieses na ja was interessiert Sie das überhaupt und warum fragt er mich das und warum sollten wir ihm das geben das ist die Form des Amtsgeheimnisses die jetzt unabhängig von Gesetzestext sehr stark in Österreich noch wirkt das heißt es gibt's in anderen Ländern nicht in dem gleichen Ausmaß Österreich ist das letzte Land in der Europäischen Union das das Amtsgeheimnis noch im Verfassungsrang stehen hat andere Länder sind uns da weit V raus ich denke da an Slowenien Großbritannien oder auch Schweden da ist es ganz selbstverständlich dass Bürgerinnen und Bürger Zugang zu staatlichen Informationen haben da wird Transparenz tatsächlich in weiten Teilen der Verwaltung gelebt während es in Österreich dann noch sehr große Geheimniskrämerei gibt mhm und das soll sich jetzt aber bald ändern mit einem Informationsfreiheitsgesetz richtig das ist der Plan der Regierung das ist zum einen die proaktive Informationserteilung nämlich Informationen die von allgemeinen Interesse sind müssen proaktiv zugänglich gemacht werden und zum zweiten die passive Informationspflicht das heißt auf Anfrage von Bürgerinnen und Bürgern dieses Gesetz ist natürlich auch nur ein Gesetzestext der dann am Ende mit Leben gefüllt werden muss das ist auch der große Test für die österreichische Verwaltung da ob ein neues Gesetz und ein Grundrecht auf Information das geplant ist dann tatsächlich so gelebt wird dass die Leute was davon haben mhm wir schauen uns am besten einfach ein paar konkrete Beispiele an damit wir das besser verstehen können und ein ganz konkretes Beispiel ist mir diese Woche aufgefallen da haben wir den Podcast aufgenommen über diese heimlichen u-ausschusspläne die die ÖVP gegen ganz viele andere Parteien gehabt hat und da haben ganz viele Kollegen von uns und Kolleginnen mir im Gespräch gesagt diese Missstände die es da bei anderen Parteien gegeben haben könnte ob es vielleicht z.B umfragenkorruption gegeben hat bei der SPÖ war das Beispiel die hätte es vielleicht nicht gegeben mit einem Informationsfreiheitsgesetz wie ist das gemeint warum hätt es die da nicht gegeben es ist so dass Transparenz präventiv gegen Korruption wirkt wann immer jemand quasi in Versuchung geführt wird oder in Versuchung ist irgendwie krumme Dinge zu drehen in der öffentlichen Verwaltung wir er sich sehr gut überlegen ob er das macht und wie großes Risiko ist dass erwischt wird je mehr Transparenz herrscht desto größer ist das Risiko dass erwischt wird es geht bei diesen Umfragen und Inseraten Deals um Geschäfte der öffentlichen Hand um Dokumente und Aufträger die bei Ministerien und anderen Behörden vorhanden sind und mit einem Informationsfreiheitsgesetz das gut funktioniert kann man solche Dinge Anfragen und wenn das quasi eine gelebte Praxis ist und wenn das tatsächlich passiert dass Leute Dinge wollen und sich mal erkundigen welche Studien hat z.B das Bundeskanzleramt in Auftrag gegeben und wer hat das bezahlt dann senkt das das Risiko dass Dinge mit öffentlichen Mitteln getan werden die nicht passieren sollten mhm und genau solche Dinge sind ja auch besprochen worden in diesem einen großen Untersuchungsausschuss den es wirklich gegeben hat dem ÖVP korruptionsuntersuchungsausschuss kann man dann quasi sagen dass es diese große Umfragen und inseratenffäre bei der ÖVP die das Land bewegt hat in den letzten Jahren vielleicht auch nicht gegeben hätte wenn es so ein Informationsfreiheitsgesetz schon viel früher gegeben hätte das ist eine was wäre wenn Frage die naturgemäß sehr schwierig ist zur Erinnerung es ging bei dieser Inseraten umfrageaffäre darum dass das Finanzministerium studienen Auftrag gegeben hat wo der Verdacht besteht dass diese nicht dem Finanzministerium der Steuerzahlerin dem Steuerzahler nutzen sondern dem damaligen Außenminister Sebastian Kurz diese Studien waren lange vorhanden sind aber die längste Zeit nicht öffentlich geworden und erst nach einem längeren Kampf mit dem Finanzministerium und wenn es quasi logisch wäre dass die irgendwann rauskommen oder relativ bald rauskommen und sich der Verdacht bestätigt dass da was nicht mit rechten Dingen zugegangen ist hätten sich die Beteiligten sicher zweimal überlegt ob sie sowas machen und auch eine komplette waswäre win Überlegung aber das heißt wenn diese Infos über diese Umfragen früher rausgekommen wären hätte das vielleicht auch die öffentliche Meinung beeinflusst und dann wäre Sebastian Kurz vielleicht gar nicht Bundeskanzler geworden unter Umständen unter Umständen ich meine hätten wir in den 90ern schon einen Informationsfreiheitsgesetz gehabt wären vielleicht ganz andere Dinge passiert und wir hätten eine ganz ganz andere Regierung oder ganz andere Probleme jetzt das ist wirklich schwer zu sagen aber was unbeschritten ist ist die Präventivwirkung von Dingen wie informationsfreiheitsgesetzen und anderen Transparenzregeln Leute drehen weniger krumme Dinge wenn Sie Angst haben müssen erwischt zu [Musik] werden wir sind gleich zurück was ich nicht nachvolziehen kann ist warum an jedem Unrecht immer ich schuld sein soll ein Korruptionsskandal jagt den anderen österreich hat in den letzten 30 Jahren viel über Klimaschutz gesprochen aber zu wenig getan die Politik schläft die Klimakrise die Behörden haben alles richtig gemacht Fehler vergisst man statt daraus zu lernen so sind wir nicht so ist Österreich einfach nicht aber wie ist Österreich dann das wollen wir bei inside Austria herausfinden wir blicken auf die großen österreichischen Skandale von Ibiza bis ischkel wir wollen wissen wer dafür in der Politik die Verantwortung trägt und wir schauen genau hin wo Österreich über seine Grenzen hinaus mitmischt vom wrecard Skandal bis zum ukrainekrieg das ist inside Austria von Standard und Spiegel jeden Samstag eine neue Folge überall wo es Podcasts [Musik] gibt Sebastian was gibt sonst noch für Skandale in Österreich die man mit so einem Informationsfreiheitsgesetz hätte verhindern können na ja ein klassischer Fall ist die Affäre um die Erwin Pröll Privatstiftung der damal ige Landeshauptmann von Niederösterreich hat sich ja über Jahre relativ viel Geld in seine eigene Privatstiftung die einem bestimmten Zweck hatte zur Förderung des endlichen Lebens soweit ich mich erinnere hat das fördern lassen vom Land Niederösterreich per Beschluss der Landesregierung der damals allerdings noch geheim war das ist dann nur durch einen Whistleblower der das in Wahrheit illegal rausgespielt hat bekannt geworden und in weiterer Folge hat Niederösterreich sich dann ein bisschen getedränkt gefühlt seine Landes Regierungsbeschlüsse nicht mehr geheim zu halten und zu veröffentlichen wäre das von Anfang an so gewesen dass diese Beschlüsse öffentlich sind und bekannt gegeben wird wer wie viel Förderung kriegt in Niederösterreich kann ich mir auch vorstellen dass das z.B nicht passiert wä oder jedenfalls nicht so lange passiert wä Sebastian wenn ich mehr darüber weiß was im Staat in Bundesländern in Gemeinden hinter den Kulissen sich abspielt dann klingt das noch etwas sehr positiven für mich was spricht gegen so ein Gesetz warum gibt es das nicht schon tatsächlich haben schon viele Regierungen versucht oder zumindest versucht den Anschein zu erwecken zu versuchen so ein Gesetz umzusetzen es hat dann aber immer Widerstände gegeben es liegt ein bisschen in der Natur der Sache dass die Politik die die Macht hat diese Macht ungern einschränkt und es ist eine Einschränkung von macht wenn du deinen Bürgerinnen und Bürger gegenüber transparent sein musst die größten Widerstände gegen diese Einigung jetzt gab es innerhalb der ÖVP aber auch von SPÖ Seite wenn wir an die Bundesländer denken Bundesländer und Gemeinden und Städte haben wirklich sehr lange und heftig gegen dieses Gesetz opponiert die offizielle Erklärung ist dass sie Sorge haben vor einem überborderenden Verwaltungsaufwand mit dem Beispiel eine kleine Gemeinde bekommt eine Anfrage von einem Bürger und muss dann überlegen okay darf ich ihm diesen Akt jetzt geben oder muss ich ihm den Akt geben weil es die Informationsfreiheit gibt oder darf ich nicht geben weil z.B ein datenschutzgrund dagegen spricht da haben die Gemeinden gesagt das würde kleine Gemeinden schnell überfordern und überlasten tatsächlich ist es aber natürlich so dass diese Kultur der Intransparenz die ich vorher angesprochen habe in ganz ganz vielen öffentlichen Stellen so stark vorhanden ist dass dieses Informationsfreiheitsgesetz eigentlich ein Worst Case Szenario für sie ist weil sie plötzlich ihr ganzes Denken umstellen müssen jeder Bürger jede Bürgerin kann bei jeder gem egal welcher Größe auch Informationen abfragen allerdings müssen nur Gemeinden über 5000 Einwohner tatsächlich proaktiv diese Informationen auch zur Verfügung stellen offensichtlich sind da deswegen auch ein paar extra Maßnahmen eingebaut worden um kleine Gemeinden zu schonen aber Sebastian die die da jetzt tatsächlich die Macht haben so ein Gesetz einzuführen das ist eben die schwarzgrüne Bundesregierung und die hat wenn ich mich recht erinnere schon vor längerer Zeit so ein Informationsfreiheit Gesetz versprochen warum hat das jetzt so lange gedauert und warum ist es gerade jetzt gekommen verfassungsministerin cararoline Stadler die für dieses Gesetz verantwortlich zeichnet hat heute bei der Pressekonferenz gesagt gut Ding will Weile haben es hat sehr Langeweile gehabt nicht Langeweile sondern es hat sehr lange gebraucht tatsächlich haben sich ÖVP und Grüne schon im Regierungsprogramm dass sie im Jahr 2019 ausverhandelt haben sehr detailreiche Pläne für dieses Informationsfreiheitsgesetz paktiert gehabt dann waren sie sich 2020 schon im Sommer untereinander eigentlich einig dann haben aber Länder und Gemeinden gesagt oha so geht das nicht und dann musste dann noch mal ein Jahr nachverhandelt werden und dann haben sie schon eigentlich einen fertigen Entwurf präsentiert und in Begutachtung geschickt und nach dieser Begutachtung wurde dann noch mal weiter verhandelt um Gemeinden und Länder und im Kern natürlich die ÖVP selbst davon zu überzeugen das hat bis jetzt gedauert mir wurde gesagt Dinge passieren einfach wann sie passieren von Leuten die mitverhandelt haben es gibt keinen bestimmten Grund warum das jetzt passiert ist es ist aber natürlich so dass die Bundesregierung gerade massiv unter Druck steht weil in der öffentlichen Wahrnehmung zumindest der Eindruck entsteht dass sehr wenig weitergeht und immer wieder die Frage aufgeworfen wird zahlt es sich überhaupt noch aus bis zum regulären Ende der Legislaturperiode weiter zu regieren wenn sie dann eh nichts auf die Reihe bekommen ich glaube schon dass da ein großer Druck da war jetzt noch ein großes Paket jedenfalls auf den Boden zu bringen und zu präsentieren wenn ich das richtig verstehe wäre das jetzt auch so ein bisschen ein Erfolgsmoment für den kleineren Koalitionspartner für die Grünen die da se hinter waren aber Sebastian ist das jetzt schon fix dass das so kommt wie jetzt der Entwurf aussieht wann tritt das dann in Kraft also fix ist noch gar nichts denn dieses Gesetz beinhaltet zahlreiche verfassungsmaterien und für eine Änderung der Verfassung braucht es im Nationalrat eine zwe Drittel Mehrheit das heißt ÖVP und Grüne brauchen entweder die Stimmen der Freiheitlichen Abgeordneten oder die der sozialdemokratischen abgeordnet die Freiheitlichen haben eigentlich schon signalisiert dass sie das nicht wirklich interessiert die SPÖ sagt sie möchten das schon auch wenn rote Städte und rote Länder da deutlich skeptischer sind und jetzt muss die Bundesregierung wo sie sich intern einig geworden ist also noch im Parlament weiter verhandeln damit Sie die notwendigen Stimmen zusammenkommt sollte diese Einigung mit wahrscheinlich der SPÖ gelingen und das Gesetz wird beschlossen dann dauert es immer noch eineinhalb Jahre bis es tatsächlich wirkt denn weil das so eine große Umstellung ist haben die Koalitionsparteien quasi sowas wie eine Wartefrist vereinbart im Gesetz dass ab den Zeitpunkt der Kundmachung oder des Beschlusses es noch eineinhalb Jahre dauert 18 Monate bis das Gesetz wirksam ist das heißt realistischerweise wenn es mit den Verhandlungen schnell geht und das Gesetz mit Anfang 2024 kund gemacht wird wird Mitte 2025 die gesetzlichen Bestimmungen wirksam sein das heißt ein bisschen spannend bleibt es noch ob sich da auch im Parlament noch eine unterstützende dritte Partei findet aber Sebastian man merkt schon du kennst dich bei dem Thema sehr gut aus was würdest du denn sagen wie historisch wie wichtig ist so ein infogesetz für Österreich dass das tatsächlich in Kraft tritt wenn es in Kraft tritt ich bin immer noch vor sichtig weil es schon sehr oft versprochen wurde und dann oft kurz vor der Legislaturperiode oder kurz vor Ende der Legislaturperiode dann doch nicht gekommen ist aber wenn es tatsächlich kommt ist das schon ein Riesenschritt das ist für die Republik Österreich und gerade für die Republik Österreich ein monumentaler Kulturwechsel wenn man so wie ein historischer Paradigmen Wechsel das ist nicht von sich aus der große Paradigmenwechsel da muss ich der Regierung wiedersprechen ich glaube nicht dass dieses Gesetz allein auf einen Schlag alles verändern wird denn diese Kultur wird sich nicht so schnell wandeln ich glaube da wird es einige mühsame Gerichtsprozesse brauchen höchstgerichtliche Entscheidungen die da klare Linien vorgeben aber das ist mal so eine Richtungsentscheidung in der Republik in Richtung Transparenz zu gehen und das erleichtert diesen Kampf für Transparenz ein bisschen aber der Kampf an sich wird den Leuten die ih führen nicht erspart bleiben und du hast vorher schon gesagt die Regierung ist gerade unter große Vorhaben umzusetzen wenn tatsächlich jetzt das Amtsgeheimnis noch fällt was wäre dann der nächste große Schritt in die Regierung noch machen könnte also was schon sehr lange auf der Agenda der Regierung steht und noch immer nicht beschlossen ist ist das Klimaschutzgesetz so wie andere Gesetzesvorhaben in diesem Bereich die zweite Sache und das ist fast schon skuril sind die nicht besetzten posten die türkisgrün nicht schafft nachzubesetzen mit mit Personen weil sich einfach nicht auf diese Personen eigen können das betrifft die Spitze des Bundes Verwaltungsgerichts die Bundeswettbewerbsbehörde mittlerweile auch die Generalprokuratur die Datenschutzbehörde da stehen eine ganze Reihe von wichtigen Jobs in Österreich an die nur deshalb nicht nachbesetzt werden weil sich ÖVP und Grüne nicht einig werden das ist glaube ich auch was wo es gerade den größten Druck gibt also es gibt noch einiges zu tun aber auf jeden Fall ist jetzt mal ein Informationsfreiheitsgesetz auf der Ziel geraden was auch schon sehr historisch wäre wenn es das wirklich noch schafft danke dir Sebastian fner dass du uns da heute einen so gut verständlichen Einblick gegeben hast danke dir wir machen jetzt dann gleich noch weiter mit unserer meldungsübersicht wir sprechen unter anderem über eine weitere junge Iranerin die von der dortigen Sitten poliizei schwer verletzt wurde und darüber ob der Energieanbieter Verbund bald erhöhte Strompreise zurückzahlen muss wenn Ihnen diese Folge von Thema des Tages gefallen hat dann abonnieren Sie uns am besten gleich auf Ihrer Liebsten Podcast Plattform egal ob Apple Podcast Spotify oder was auch sonst dann verpassen Sie auch keine weitere Folge mehr bei der Gelegenheit freuen wir uns auch sehr über gute Bewertungen oder nette Kommentare das hilft unsere Sichtbarkeit sehr vielen Dank dafür wir sind gleich wieder [Musik] da Standard podcasts gibt's ja wirklich schon zu jedem Thema also fast jeben Thema des Tages lohnt sich das inside austrien besser leben Edition Zukunft und und und aber nicht jeder hat die Zeit das alles zu hören und manchmal möchte man sich einfach nur ein paar Minuten beschallen lassen ich bin sch Wilhelm und ich bin magit ehenhöfer ab sofort bringen wir auch Highlights unserer Podcasts für zwischendurch wenn mal weniger Zeit ist diese kurzen Ausschnitte nennen wir Shorts so wie eine kurze Hose oder eine kurze Geschichte okay und Shorts vom Standard finden Sie jetzt überall wo es Podcast gibt und hier ist was sie heute sonst noch wissen müssen erstens im Iran wurde wieder eine junge Frau in Zusammenhang mit der Sittenpolizei verletzt die 16-jährige Amita garawand liegt seit einem Vorfall mit Sittenwächtern in einer U-Bahn im Koma in den sozialen Medien kursiert ein Video in dem eine junge Frau ohne Kopftuch von Einsatzkräften in die U-Bahn gestoßen wird die meisten Infos über den Vorfall werden durch AktivistInnen verbreitet offiziell dementieren die Behörden alles Amita garaband ist außerdem kurdischeer Abstammung genauso wie Massa amenie der ein Tod in Haft im vergangenen Jahr für enorme Proteste für Frauen und Menschenrechte im Iran gesorgt hat zweitens der Energieanbieter Verbund hätte im vergangenen Jahr nicht seine Strompreise erhöhen dürfen das hat ein Gericht entschieden und zwar schon in zweiter Instanz der Hintergrund ist eine Klausel in einem alten verbundvertrag darin steht dass der Strompreis erhöht werden darf wenn ein gewisser Börsenindex ansteigt weil Energie im Jahr 2022 so teuer wurde hat der Verbund davon Gebrauch gemacht dagegen hat allerdings der Verein für Konsumentenschutz kurz VKI geklagt denn Verbund wirb damit seinen Strom in Österreich per Wasserkraft zu erzeugen und steigende Gaspreise am internationalen Markt hätten darauf keinen Einfluss die Gerichte haben dieser Klage jetzt also schon zweimal Recht gegeben und wenn das Urteil rechtskräftig wird dann muss Verbund die Differenz zum erhöhten Preis an rund 400 000 kund innen zurückzahlen wie der VKI meint und drittens bei den Nobelpreisen kommen gerade ja unzähige Experimente ins Scheinwerferlicht darunter auch österreichische aber ein besonders spannendes paper spielt sich abseits der Schwedischen Akademie ab ein österreichischer Forscher hat nämlich das Schnurren von Katzen erforscht warum katzenschnurren darüber herrscht in der Wissenschaft ein gewisser Konsens sie machen das wenn Sie sich wohl und sicher fühlen wie das Schnurren allerdings funktioniert da ist man sich gar nicht so sicher vor allem auch deswegen weil die Frequenz von schnurgeräuschen auffallend tief ist das ist eigentlich nur bei großen Tieren wie Elefanten üblich aber nicht bei so kleinen wie Hauskatzen die neue Studie hat jetzt herausgefunden dass das schnurrgeräusch durch spezielle Fettpolster erzeugt wird die sich zwischen den Stimmbändern von Katzen verstecken und das Schnurren funktioniert anscheinend ganz automatisch also ohne dass die Katze bewusst irgendwelche Muskeln anspannen müsste einmal vom Gehirn gestartet läuft das Schnurren einfach von selbst weiter wie die Katze das Schnurren dann wieder stoppen kann das konnte ich aus dem paper zwar nicht herauslesen aber ich freue mich schon sehr darauf in Zukunft noch viel mehr Forschung über dieses wichtige Thema zu sehen und zu hören alles weitere zum aktuellen Weltgeschehen können Sie auf der standard.at nachlesen und wenn Sie jetzt noch nicht genug von Standard Podcasts haben dann empfehle ich Ihnen die neue Folge unseres Schwester Podcasts besser leben da geht es darum wie man gesund kochen kann und erklärt wird das von einer Ernährungsexpertin besser leben finden Sie überall wo es Podcasts gibt und dann noch ein ganz kurzer Tipp unser neuer podcastkanal Standard Shorts ist auch online dort geben wir ganz kurze und kompakte Antworten auf spannende Fragen die uns beschäftigen falls Sie Feedback oder Anregungen für das Standard Podcast Team haben dann schicken Sie die gerne an podcast@standard.at wenn Sie die journalistische Arbeit die wir hier beim Standard machen unterstützen möchten dann geht das z.B ind dem sie ein Abo abschließen aktuell gibt es dafür besonders gute Konditionen weil der Standard sein 35-jähriges Jubiläum feiert mehr Infos auf abo.dstandard.at ich bin Tobias holup und an dieser Folge hat außerdem Sch mitgearbeitet und in der gestrigen Folge habe ich vergessen unserem Produzenten Christoph Neuwirt für die aufwendige Bearbeitung der Audiospuren zu danken also das an dieser Stelle auch noch vielen Dank fürs zuhören und bis zum nächsten [Musik] Mal das Standardforum ist ein Ort zum Mitreden auch ganz anonym wenn sie das möchten freier Diskurs bedeutet auch die Balance zwischen meinungsfrei Freiheit und respektvollen Umgang zu halten das macht dann das Moderationsteam mit Hilfe von transparenten Community Richtlinien sie können Ihre Meinung zu tagesaktuellen Themen abgeben oder sich in den Community Foren über unterschiedlichstes austauschen was auch immer Sie gerade beschäftigt egal ob sie aktiv posten oder Beiträge anderer bewerten ihre Stimme findet anglang bei über 100.000 aktiven Userinnen und Usern einfach bei dst.at/forum anmelden und losreden</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>viUdbnRUdeo</t>
+  </si>
+  <si>
+    <t>die CDU belügt uns schamlos auf Bundesebene fordert sie eine Begrenzung der Migration auf Kommunalebene öffnet sie der Massenmigration Tür und Tor und hat heute in Prenzlau in Brandenburg für einen Tabubruch gesorgt dort will die CDU Landrätin Carina Dirk eine demokratische Abstimmung verbieten den Bürgerentscheid verbieten darüber hat heute der Kreistag entschieden wir wissen wie das Ganze ausgegangen ist denn wir waren live vor Ort wir werden zu unserem Chefredakteur Jürgen Elsässer Schalten der sich vor Ort befindet und wir wissen auch wie das Ganze weitergeht bleiben Sie dran das ist der Brennpunkt des Tages [Musik] heute in Prenzlau Entscheidungen im Kreistag es geht um dieses Gebäude hier die brüssower Allee 91 wo bis zu 300 Migranten einquartiert werden sollen nach ihrem Willen Carina Dirk die CDU Landrätin die also weitere Migranten aufnehmen will die AFD hat ein Bürgerbegehren dagegen angestrengt was sehr erfolgreich war was zu einem Bürgerentscheid führen sollte aber Carina Dirk will diesen Bürgerentscheid einfach für unzulässig erklären und will das heute auch im Kreistag durchsetzen heute war die Kreistagssitzung heute ist die Entscheidung gefallen unser Chefredakteur Jürgen Elsässer vor Ort und wir schalten dorthin Jürgen wie ist die Entscheidung in Prenzlau im Kreistag ausgefallen ja Paul gerade kam das Ergebnis der Abstimmung 27 sind für die nicht Zulassung des Bürgerentscheid elf waren dafür also Wesentlichen die AFD zwei Enthaltungen dass entspricht der Zusammensetzung des Kreistages wo die Blockparteien die eindeutige Mehrheit haben und es gab nur wenige von ihnen die sich besonnen haben und für die Demokratie rotiert haben ja eine katastrophal Entscheidung für die Demokratie hier sieht man mal wie es vor Ort aussieht ähm Jürgen wie waren denn die Reaktionen der Bürger vor Ort nach dieser Entscheidung ja Paul natürlich die Stimmung ist niedergeschlagen hier 16.000 Bürger haben unterschrieben dieses Bürgerbegehren noch niemals in so kurzer Zeit im Land Brandenburg war ein Volksbegehren so erfolgreich und jetzt hat der Kreistag ohne Führung der CDU Landrätin diese Unterschriften in die Tonne getreten der Bürgerentscheid wird nicht stattfinden so sieht's aus mit der Demokratie in diesem Land wir haben heute gesehen wer die Demokratie verteidigt und wer sie beerdigen möchte vielen Dank Jürgen ja das war Jürgen Elsässer live aus Prenzlau Katastrophe Steffi der Bürgerentscheid der mit 16.000 Unterschriften in nur drei Wochen erreicht worden ist kommt nicht zustande und zwar wundert das ja wenig weil bei der Landrätin ist einfach das falsche Ergebnis rausgekommen und die sogenannten Demokraten hier das wissen wir ja die machen demokratische Wahlen oder Entscheidungen dann einfach rückgängig oder verbieten Sie oder lassen Sie nicht zu weil demokratisch sind ja nur Wahlen oder Entscheidungen die auch dem System genehm sind also wir haben gelernt nur wenn die Menschen die richtigen Entscheidungen treffen zum Beispiel pro offene Grenzen pro asylheime dann ist das eine demokratische Entscheidung und naja also ich bin auch enttäuscht von diesem Kreistag ja weil wir wissen nicht was da für Leute drin sitzen die wollen vielleicht auch noch Karriere machen wollen ihr ihre Wohnung abbezahlen und sie haben jetzt so abgestimmt aus den Reihen der Altparteien wie es eben auch abstimmen sollen wie es eben auch genehm ist und für die CDU mal wieder bezeichnend wie du es auch eingangs gesagt hast ja haben wir auch erst wieder konservativ geredet ja also es ist gut dass es diesen Bürgerentscheid gibt und natürlich ist es nicht mehr zu verkraften was uns hier zugemutet ist und dann wenn es drauf ankommt biegen Sie dann doch immer wieder grün rot oder links ab ja das ist so typisch für die CDU ich bin sehr enttäuscht von dieser Partei ja vor allem dieses wahlrückgängig machen das können wir ja schon von der Thomas Kemmerich weil in Thüringen 2020 war das glaube ich wo Merkel aus Afrika heraus diese Wahl hat rückgängig machen lassen muss man sich mal vorstellen und hier auch diese Karina Dirk wie eine Diktatorin verhindert sie den Bürgerentscheid für mich ist es kein Wunder dass ein Umfragen die AFD bei über 30% liegt in Brandenburg und AFD Vertreter waren auch vor Ort heute natürlich auch die AFD Chefin von Brandenburg Birgit beziehen die haben wir auch kurz interviewen können ja es ist ja eine grundlegende Bedeutung wenn hier mehrere tausend Menschen 16.000 Menschen Unterschriften gesammelt haben um im Prinzip hier in der Uckermark darzustellen dass sie mit der Unterbringung hier im Prenzlau nicht einverstanden sind und die Landrätin oder der ganze Kreis oder die Mehrheit des Kreistages gegebenenfalls später diese Entscheidung der Bürger ablehnen wird da darf man sich mal die Frage stellen inwieweit herrscht die Demokratie hier in Brandenburg überhaupt noch ja das ist eine berechtigte Frage weil gerade auf der kommunal Ebene da gibt's ja nur dieses Mittel des Bürgerentscheids um direkt demokratisch Einfluss nehmen zu können auf Landesebene gibt's noch die Volksentscheide auf Bundesebene gibt's ja sowas gar nicht da kann man nur indirekt werden das ist nicht wie in der Schweiz leider auch das will die AFD ja ändern auf jeden Fall ist dieser Bürgerentscheid eigentlich ein sehr mächtiges Instrument weil der auch rechtlich bindend ist dann zumindest für eine gewisse Zeit und es hat ja bereits sehr erfolgreich funktioniert in Mecklenburg-Vorpommern z.B in Greifswald wo 67 während der Bürger gegen Asylunterkünfte gestimmt haben in Ihrer Stadt oder in Grevesmühlen wo das ganze noch krasser war 91 Prozent fast 100% der Bürger haben dagegen die neuen Unterkünfte gestimmt also da sieht man wie es auch funktionieren kann wenn es Demokraten geben würde die das auch zulassen würden ja aber hier ist ja auch noch nicht das letzte Wort gesprochen weil was da passiert ist heute das geht überhaupt nicht ja das geht nicht und denn was die Menschen wirklich ganz unmittelbar betrifft das ist eben ein Flüchtlingsheim mit sogenannten traumatisierten und dann hier gleich 300 also das kann schon passieren dass dann auch die Kriminalitätsrate hochgeht das auch da Mädchen Frauen gefährdet sind das wird ja immer alles unterdrückt in den Medien ins Kindergartens also das ist auch gefährlich und ganz aktuelles Beispiel in Monheim sind aktuell Eltern den Angst weil der Bürgermeister der heißt Daniel Zimmermann auf einem Schulgelände 80 Asylanten unterbringen will und da fragt der eine Mutter nach einem Sicherheitskonzept die macht sich einfach Sorgen um ihre Tochter und der Typ hat sie ganz arrogant abgebügelt das ist kein Sicherheitskonzept gibt nicht das das ist kein Sicherheitskonzept gibt und dass die Asylanten ungefährlich sein ich glaube die Monheimer Bürger die da in der Sprechstunde waren in dieser offiziellen Runde die waren glaube ich so geschockt dass da keiner mehr nachgefragt hat ja dann mache ich sie dafür verantwortlich wenn was passiert also es ist ja immer wie Russisch Roulette war da ja eine Schale Bonbons 80 Bonbons drin Eis ist vergiftet willst du dann als essen ja es ist einfach es sind bestimmt die meisten lieb und nett tun kein was aber es sind ja traumatisierte dabei und die tun dann eben auch manchmal böse Dinge die vergewaltigen die morgen die laufen mit einer Machete rum aber es passiert ihnen nichts und wir bieten ja auch hier die Anreize nicht nur der opulenten sozialversorgung sondern auch keine beziehungsweise Lasche strafferfolgung ja und das ist auch das was viele Menschen ängstigt und das wollen die einfach nicht mehr aber wie gesagt die CDU diese ganzen systempolitiker die wollen ja das Asylanten herkommen die wollen es ja nicht anders die sind ja wie besessen auf Asylanten Frau Felser voran also wie Pyromanen die überall Brände machen ja die sind wie versessen drauf und meiner Meinung nach sind das jetzt mal abgesehen von diesen demokratischen Fragen alles verrückte das sind verrückte ja vor allem die Bundesregierung das ist ja ein einziges Gruselkabinett Alter aber haben wir doch ein paar Stimmen von den Bürgern eingefangen aus dem Landtag in Brandenburg mit der ein bisschen Mut macht weil die AFD will jetzt auch gegen diese Entscheidung Vorgehen juristisch es soll eine heilklage geben beim Verwaltungsgericht Potsdam und Lars Günther kündigt hier eine große kampagnenwelle in ganz Brandenburg an schauen wir uns auch an wir werden jetzt Kampagnen ins Leben rufen wir werden in im ganzen Land Brandenburg werden wir Kundgebungen anmelden in Zukunft ich bitte daher auch alle an den sozialen Medien sich dort die Informationen kund zu tun wir werden auch weitere Bürgerinitiativen im sämtlichen Land unterstützen durch unsere Kreisverbände und Kreistagsfraktionen und wir werden dem nicht weiter zuschauen das ist doch klar das ist richtig so weil die Entscheidung ist wirklich ein Skandal äh die Landrätin begründet das ja so ja die Unterbringung der Migranten seine Pflichtaufgabe per Weisung des Landes aber es geht bei dem Bürgerentscheid das ist ganz wichtig zu wissen gar nicht darum ob die Migranten untergebracht werden sondern wie sie untergebracht werden und da spielt eben dieses alte Bürogebäude eine sehr wichtige Rolle weil das ist der völlig ungeeignete Ort wie gesagt im Stadtgebieten Kindergarten in der Nähe da sollen bis zu 300 Migranten rein und dann waren da noch Unternehmen angesiedelt z.B eine Autovermietung die wurden einfach alle rausgekickt aus dem Gebäude um die 300 Migranten aufnehmen nutzen zu können und das geht so nicht und darum ging es bei den Bürgerentscheid nicht darum ob jetzt dieser Pflichtaufgabe nachgekommen werden soll oder nicht worüber sich natürlich auch streiten ließe aber darum ging es nicht und deswegen ist die Begründung daran Landrätin völlig falsch und auch diese Entscheidung heute unrechtmäßig ja wobei ja doch jetzt mal abgesehen von diesen ganzen juristischen findeigkeiten jeder Depp inzwischen weiß das ist überhaupt nicht darum geht den Menschen zu helfen wenn es darum ginge ihnen zu helfen würde man ihn vor Ort helfen und in den Ländern wo sie herkommen ist es ja auch nicht so schlimm denn die machen da regelmäßig Heimaturlaub in den Ländern aus denen sie angeblich vor Verfolgung geflüchtet sind also das ist alles so lächerlich und so verrückt darum geht es nicht und dass sie immer wieder mit der gleichen Leier kommen wir sind verpflichtet nein sind wir nicht wir müssen es machen wie Dänemark das habe ich mir mal angeschaut also Dänemark war genauso doof und großzügig wie Deutschland sind auch gerne die Asylanten hin und jetzt hat Dänemark seine Politik komplett geändert gibt den Leuten nur noch das Nötigste und es will da keiner mehr hin ja das ist schon mal ein Grund dann sollten wir dringend endlich mal diese Anreize senken ja um Hilfsbedürftige wenn es darum geht Menschen zu helfen überhaupt mal zu erkennen wäre es ja zwingend notwendig auf Sachleistungen umzustellen das ist zwar erstmal ein bisschen schwierig so organisieren könnte vielleicht auch erstmal ein bisschen was kosten aber unterm Strich spart man viel Geld und vielleicht und auch hier viel Getränk und Geschacher ja darauf müssten wir abstellen und was auch wichtig ist immer wieder Schutz der Außengrenzen also ich weiß nicht warum sich da inzwischen keiner mehr so richtig drum kümmert wir sollten uns einfach selber mal drum kümmern weil letzte Woche hat er Europäische Gerichtshof die Zurückweisung von Migranten an der binnengrenze verboten also das ist schenken Binnengrenzen juristisch gesehen war ja ein gutes Konzept wir konnten mal nach Polen fahren günstig Tabak kaufen für die Wirtschaft war es auch gut ja das funktioniert aber nur wenn man die Außengrenzen schützt also nochmal zu Schengen Schengen ist ja wie ein Haus also das ist wie eine Wohngemeinschaft im Haus Europa also wir sind eine Wohngemeinschaft und teilen uns das Haus Europa da hat jeder sein Zimmer Finnland Deutschland Frankreich und wir haben eine Haustür ja die Türen innen im Haus wir sind auch mal zugänglich ne da kann man anklopfen bei Frankreich oder bei Polen und die Haustür muss aber abgeschlossen sein sonst funktioniert das nicht und wir wissen ja auch dass die Ostgrenze brennt ist ja nicht nur Lampedusa sondern auch die Ostgrenze also wir haben wirklich eine Situation die ist für uns existenziell bedrohlich und wenn man hier dieser kreistagsentscheidung was Positives abgewinnen will dann doch dass wir immer mehr kämpfen müssen interessant ist auf jeden Fall dass auch die Mehrheit der Stadtverordneten von Prenzlau gegen die Aufnahme der Migranten ist zumindest in diesem Gebäude auch die Prenzlauer CDU aber natürlich der Kreistag schlägt dann den Stadtrat das ist das Problem an der Sache aber wir haben hier noch einen Einspieler von dem CDU-Fraktionschef von Prenzlau der also gegen dieses migrantenheim ist der sich auch im Kreistag dagegen heute ausgesprochen hat können wir auch noch mal reinhören das auch ganz spannend aus Partei strategischer sichtbar ist [Musik] Aufgaben möchten das nicht nur verwandt Prinzessin sondern die gesamte Wasser [Musik] ja das ist dieses komische Doppelspiel was die CDU mal spielt also auf stadttebene sagen sie okay es geht nicht aber im Kreistag beschließen dann die Parteifreunde das glatte Gegenteil und das ist so ein verwirr Spiel was der Burger also das ist doch muss dann doch ins Auge stechen trotzdem hat die CDU leider noch immer gute Umfrageergebnisse muss man sagen also ich glaube manche haben schon wieder vergessen dass Merkel damals die Grenzen aufgerissen hat oder hoffen irgendwie dass es unter Friedrich Merz besser werden könnte aber an solchen kleinen Beispielen auf lokaler Ebene sieht man ja dass die CDU sich 0 gebessert hat sondern immer noch dieses doppelgesichtige und letztlich politisch migrationspolitisch massiv schädliche Partei gewesen ist von der CDU ist keine Wände zu erwarten das hat sie mehrmals bewiesen auch heute wieder aber wir von kompakt wir unterstützen diese Asyl Bürger entscheide mit aller Kraft nicht nur ein Prenzlau auch anderswo wir haben im Vorfeld schon tausende von Flyern gedruckt wir waren gestern mit einem Infostand in Prenzlau heute ist Jürgen Elsässer vor Ort mit Kameramann und zwei Redakteuren wir machen weiter unterstützen Sie uns bitte dabei helfen sie uns spenden sie etwas jeder Euro zählt gehen sie auch auf die Straße beteiligen sie sich und es geht um unser Land holen wir uns unsere Demokratie zurück und holen wir uns unser Land zurück unser Land heißt Deutschland nicht jedermann kommentieren Sie gerne wieder mit auf Youtube oder auf unserer Online Seite und vor allem verbreiten sie dieses Video denn dieser demokratie-skandal soll vertuscht werden die Mainstream-Medien berichten kaum drüber und deswegen ist es so wichtig dass die Bürger in diesem Land davon erfahren also unbedingt diese Sendung verbreiten gerne auch den Kanal abonnieren darüber würden wir uns sehr freuen und dann sehen wir uns morgen wieder mit dem nächsten Brennpunkt des Tages bis dahin [Musik] deutschland schafft sich ab auch außerhalb der Großstädte erkennt man unser Land kaum noch wieder während unsere Leute kaum noch Wohnraum finden Krankenhäuser und Altersheime schließen werden flächendeckend neue asylheime gebaut das Boot ist voll ich bin daher für eine sofortige Abschiebung aller Kriminellen und abschiedepflichtigen Ausländer Herstellung eines effektiven Grenzschutzes und Aussetzung des Asylrechts damit sie und ihre Familien wieder in Sicherheit leben können mein Name ist René tiergeist ich bin Rechtsanwalt und Anwalt des Volkes wenn sie am 8 Oktober die AFD und holen sie sich Bayern zurück [Musik] [Musik]</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>_ezOaxW3DY8</t>
+  </si>
+  <si>
+    <t>hat das alles mit dir gemacht diese Jahrzehnte in der eiskalten Brandung in den Wellen des Hasses [Musik] hier in Tanja einem Dörfchen im Tessin versuchen wir heute Hannah Arendt besser zu verstehen sie zählen zu den bedeutenden politischen Denkerinnen des 20 Jahrhunderts berühmt wurde sie auch durch die sogenannte Eichmann Kontroverse in ihren späten Lebensjahren suchte sie wiederholt das verschlafene Dörfchen Tanja auf Hildegard Keller hat Hannah Arend dabei begleitet ihnen Gedanken vielen Roman was wir scheinen hat sie dabei jahrelang recherchiert lieber Hildegard was hat Hanne Arendt hierher geführt der Wunsch nach Ruhe nach Abgeschiedenheit in diesem kleinen Dörfchen findet sie niemand aber natürlich war sie keine ganz übliche Touristin ja und was war sie dann sie arbeitet in erinnert sich an das Buch ihres ganzen Werks dass sie am meisten Schwierigkeiten bereitet hat es ist das Buch über den Prozess gegen Adolf Eichmann der 1961 war weil der hat sie ganz schweres erlebt über Jahre hinweg sie war ausgesetzt in der Weltöffentlichkeit ganz großem Hass eine für sie sicher sehr sehr schwierige Situation 1961 wird der deutsche ss-kriegsverbrecher Adolf Eichmann bei einem öffentlichen Prozess in Jerusalem zum Tode verurteilt Ahrend ist als Gerichtsreporterin dabei und kommt zu einer unerwarteten Erkenntnis ja viele waren schockiert über die Beobachtungen die Hannah harend über Adolf Eichmann aufstellte sie scheint auch selbst über diese Beobachtungen schockiert zu sein lieber ihre eigene Erkenntnisse was waren das eigentlich für Beobachtungen das schockierende daran hängt auch zusammen mit dem was in der Öffentlichkeit aufgebaut worden war nämlich das Bild eines Monsters hier werdet ihr sehen zum ersten Mal vor der Welt Kamera leider konnte Adolf Eichmann nicht mit so einem Profil mit so einer Statur auf warten mit kaum einer eigenen Sprache kaum einem eigenen Denken keiner wirklichen Absicht keine wirklich erkennbaren Ideologisierung und sie gehörte zu den wenigen die das ausgesprochen hat dargelegt hat in einem wunderbaren Psychogramm von Adolf Eichmann und war natürlich heiklerweise die einzige Jüdin die das gemacht hat der Kriegsverbrecher wird eine Flucht bedroht verteufelt zu Recht nach dem Prozess scheint ein Teil der Wut auf eine Art überzuschwappen denn bei ihrer Suche nach Adolf Eichmann findet sie kein extremistisches Monster sondern einen Menschen einen Menschen von den pören der Dummheit war wie sie sagt aber trotzdem einen Menschen sie nennen das die Banalität des Bösen er ist eine Frage der Empathie ja ja genau wo ist das menschliche wo ist der Mensch auch bei Adolf Eichmann wo ist der Mensch im Monster ich habe hier zu lange geforscht und plötzlich gemerkt dass das nicht nur ihr Kernthema in diesem Buch ist sondern dass ihr selber auch sehr viel daran gelegen ist dann Menschen nicht einfach mit Huldigung oder verdammungen oder verteufelungen zu sehen sondern als Menschen und daraus habe ich dann meinen Schlüssel gemacht für den Roman weil ich gefragt habe Hannah was hat das alles mit dir gemacht die sie Jahrzehnte in der eiskalten Brandung in den Wellen des Hasses und im Rahmen dieser Recherche für den Roman habe ich auch gemerkt dass es das etwas in ihr verstummt ist was eigentlich gar niemand gekannt hat deshalb suchte auch niemand danach nämlich die Fähigkeit Gedichte zu schreiben in der Matcha Schlucht bei Ponte Brolla verbringt eine sich Alt fühlende Hannah Arendt den letzten Sommer ihres Lebens in gewisser Weise wirkt es so als würde ihr die Zeit nicht weitergelaufen sein es ist alles so da es ist alle so steinig ist das das was eine Art angezogen hat die nicht Vergänglichkeit das ist ein sehr schöner Gedanke Mila das ist ein toller Gedanke aber ich glaube echt sie hat viel viel pragmatischer gedacht echt das war abgeschrieben sie sagte auch hier findet mich niemand sie wollte nicht mehr gefunden werden die Welt die Öffentlichkeit sie war durch diese Eichmann Kontroverse Welt berühmt geworden und berichtigt auch sie sagte schon 1955 also 20 Jahre vor diesem letzten Sommer schreibt sie kein Erfolg der Welt könnte mich versöhnen mit dem Schrecken im in der Öffentlichkeit stehen zu müssen da war sie noch gar nicht wirklich in der Öffentlichkeit das schrieb sie damals und es ist 20 Jahre umso wahrer als sie mittlerweile den Schrecken dieser Öffentlichkeit wirklich erlebt hat und ich glaube sie liebte das Gefühl auch hier findet mich niemand mehr und ich kann mich auch einmal meine Themen zu wenden sie ist zurückgekehrt zu ihren alten allerersten Themen medizinischen Themen the life of the mind was macht den Menschen aus das Innere des Menschen auch die Seele große Verbindungen sind kosmische sein Wille sein Wille die Urstein Urteilskraft und so weiter und das war indirekt jedenfalls sagt sie so indirekt auch eine Folge der Auseinandersetzung mit dem Nationalsozialismus mit Menschen wie Eichmann und dazu hierher zurück sie bringt das Buch nicht ganz fertig sie arbeitet jetzt daran 1975 ist Arendt zum letzten Mal in Kenia noch im selben Jahr stirbt sie ihre Gedanken ihre Geschichten ihre Gedichte bleiben eins davon geht so ich liebe die Erde so wie auf der Reise den fremden Ort und anders nicht so spinnt das Leben mich an seinem Faden leise ins nie gekannte Muster vor Ort bis plötzlich wieder Abschied auf der Reise die große Stille in den Rahmen bricht erfahren möchtet hier geht es zu einem Gespräch mit Eva von Edeka und wenn ihr einen weiteren denkort kennenlernen möchtet hier könnt ihr sehen was Ahrens Liebhaber Martin heiliger in Davos veranstaltet</t>
+  </si>
+  <si>
+    <t>OObv1VCOCCs</t>
+  </si>
+  <si>
+    <t>die Finanzierung der Nazis die Liebe zum Profit beherrscht die ganze Welt Aristophanes wenn es um die Aufarbeitung der eigenen Vergangenheit geht steht Deutschland mit enormem Abstand weltweit an erster Stelle in den letzten zehn Jahren konnte man sehr schön beobachten dass kein Tag vergingen an dem nicht in irgendeiner Form die Medien über den Zeitraum von 1933 bis 1945 berichten Tendenz steigend der Eindruck entsteht mittlerweile dass sich die deutsche Geschichte nur auf die eben benannten zwölf Jahre beschränkt interessant ist dabei zu beobachten dass über das noch so kleinste Detail berichtet wird aber nicht darüber wer Hitlers Aufstieg und Deutschlands Aufrüstung damals finanziert hat die Namen die in den Medien kursieren beschränken sich in der Regel auf deutsche Unternehmen wie ThyssenKrupp Flick und so weiter wie war das nationalsozialistische Wirtschaftswunder von 1933 bis 1939 finanziell überhaupt machbar mit anderen Worten die Oberfläche wird auf Hochglanz poliert nur über den Kern wird nicht gesprochen dabei ist doch ganz klar dass kein verschuldetes Land auf der Welt finanziell in der Lage ist einen Krieg zu führen das Land das letztendlich die Absicht hegt einen Krieg vom Zaun zu brechen muss sich immer erst an die internationalen Bankiers wenden um Geld für sein Vorhaben zu erhalten das galt damals wie heute aufgrund des versaja Vertrags und den damit verbundenen Auflagen war Deutschland hoch verschuldet und musste enorme Reparationszahlungen an das Ausland leisten das führte letztendlich zum Zusammenbruch der deutschen Währung und als Folge zur chronischen Inflation im Jahre 1923 aber die internationalen Bankiers waren zur Stelle indem sie über den dorse planen und den Young planen ab 1924 gewaltige Beträge an Deutschland überwiesen ohne diese wäre es unmöglich gewesen in so kurzer Zeit eine Kriegsmaschine ri solchen Ausmaßes aufzubauen Professor Carol quickly Historiker an der Georgetown Universität in Washington DC berichtete es ist zu beachten dass dieses System der Doors und Young Pläne von den internationalen Bankiers eingerichtet wurde und dass das Ausleihen des Geldes an Deutschland für diese Bankiers Höchstgewinn bringen waren im Jahre 1929 bemächtigten sich drei Großkonzerne der Wall Street einiger der wichtigsten Schlüsselstellungen der deutschen Wirtschaft die General Motors Corporation kaufte die Opel Werke in Rüsselsheim die internationale telefon-netz aus und General electrics die schon 1922 einen Vertrag mit der AEG abgeschlossen hatten intensivierten ihre Aktivitäten des Griffin schreibt in seinem Buch der höchste diplomatische Vertreter Amerikas in Hitler Deutschland war nach 1933 Botschafter dort am 15 August 1936 mehr als dreieinhalb Jahre nach Hitlers macht Ergreifung berichtete dort an den amerikanischen Präsidenten wo sie Welt zur Zeit haben wir hier mehr als 100 amerikanische Unternehmen Tochtergesellschaften oder Kooperationsabkommen diese Firmen waren direkt beim Aufbau der deutschen Kriegsmaschine Rebe höflich in der Tat hatten die Deutschen Tochterfirmen fort und Opel mit Wissen und Belegung der amerikanischen Mutterkonzerne Hitlers Kriegsführung unterstützt und kräftig davon profitiert kurz vor Kriegsbeginn errichtete beispielsweise Opel eine 100-prozentige Tochtergesellschaft von General Motors in Brandenburg an der Havel ein Werk in welchem der beste Lastkraftwagen der Welt gebaut wurde ohne den Opel Blitz hätten der Ost und der Afrika Feldzug nicht geführt werden können die Erlöse wurden bis kurz vor Kriegsende via Schweiz Portugal und die Türkei in Devisen und Edelmetalle an die Muttergesellschaft in den USA abgeführt in dieser Zeit blieb das Werk von den Luftangriffen der Alliierten verschont als amerikanisches Soldaten 1944 nach der Landung in der Normandie in Richtung rheinvorrücken mussten sie erstaunt feststellen dass die deutsche Wehrmacht teilweise die gleichen Lastkraftwagen und Militärfahrzeuge fuhr wie sie selbst dieses Kooperationsmodell dauerte aber nur so lange bis in die Alter klar wurde dass sich der Produktionsstandort in der künftigen sowjetischen Besatzungszone befinden würde mit einem gezielten Luftschlag würde das Werk daraufhin zerstört die sehr sorgfältig dokumentierten Beweise darüber dass amerikanische Banken und industriekreise an dem Aufstieg von Hitlers Dritten Reich höchst maßgeblich beteiligt waren sind inzwischen öffentlich zugänglich ein Name ist untrennbar mit den Geschäften der Nazizeit verbunden die Rede ist von der IG Farben einem Konzern der die Chemie und Pharmaindustrie in der ganzen Welt kontrollierte die Beteiligungen bestanden in 93 Ländern Ende 1929 war es dann soweit die IG Farben und die Standard Oil Company Rockefeller Konzern fusionierten in dem Standard Oil im Gegenzug IG Farben 546 000 seiner Stammaktien gab die IG Farben wurde zum größten Industriekonzern Europas und größten Chemieunternehmen der Welt an der Besetzung des Vorstands konnte man sehr schön die internationalen Verflechtungen erkennen da waren unter anderem Max und Paul Warburg die große Banken in Deutschland und den USA besaßen ein weiteres Mitglied des Verwaltungsrats war sie Mitchell der zum Verwaltungsrat der Federer Reservebank und der National City Bank gehörte sowie HHL Metz von der Bank von Manhattan Hermann Schmitz Präsident der ige Farben gehörte zugleich zum Vorstand der Deutschen Bank sowie auch zur Bank für internationalen Zahlungsausgleich Bits diese wurde 1930 von Hilmar Schacht gegründet und kann auch als Bank der Zentralbanken bezeichnet werden in der Bits waren vor allem die führenden Geldinstitute der Wall Street vertreten unter ihnen Rockefellers Investmentbank Chase Manhattan Bank GP Morgans Investmentbank GP Morgan und Co Clarence lapowskis Investmentbank Dillen weed und Co die alle eines Verband das starke Interesse an Geschäften mit Deutschland auch die Luftwaffe hätte ohne bestimmte Chemieprodukte zum Beispiel t3-ethyl Blei die nur von Standard Oil General Motors und die produziert und dann an die IG Farben verkauft wurden nicht fliegen können ähnlich sah es auch mit dem Öl aus wie die FAZ schon am 11.02.199 in dem Artikel Öl für den Führer schrieb das Hitlers Truppen ohne amerikanische Öllieferungen vor und noch während des Krieges Frankreich womöglich gar nicht hätten besetzen können wie aus der mineralölstatistik des Oberkommandos der Wehrmacht vorgeht lieferten die Vereinigten Staaten im Jahre 1937 mehr als eine Millionen Tonnen Öl ein Viertel der gesamten deutschen Ölimporte wie groß die Bedeutung dieser Lieferungen war geht aus einem Schreiben des Oberbefehlshabers der Kriegsmarine Großadmiral geräder vom 27.06.1940 hervor ohne diese Ölimporte hätte jetzt weder die Marine noch die Wirtschaft das nötige Mineralöl wer jedoch glaubte die amerikanischen Lieferungen hätten mit Kriegsbeginn aufgehört der sah sich getäuscht in den lange unter Verschluss gehaltenen importübersichten der Reichsstelle für Mineralöl finden sich nicht nur Einzellieferungen sondern vielmehr eine konkrete Aufstellung das Deutschland vom September 1939 bis zum Sommer 1940 verschiedenste dringend benötigte Ölprodukte aus den USA importierte darunter Motoren Benzin Diesel Heizöl schmier und Motorenöle ausgerechnet im Mai 1940 als deutsche Panzer Frankreich über vielen wurde das dringend benötigte Motoröl und Schmiermittel aus den Vereinigten Staaten eingeführt wie aus den Akten der reißstelle für Mineralöl hervorgeht wurde so zu 100% der deutsche Bedarf gedeckt die Ölgeschäfte der amerikanischen Industrie waren im Jahre 1940 Bestandteil einer Kabinettssitzung in Washington in Anwesenheit von Präsident Roosevelt und Außenminister Hall dort äußerte sich der damalige unter Staatssekretär Summer Wells das Öl aus Mexiko Kolumbien und Venezuela gleichfalls über Spanien nach Deutschland geliefert werde und das wir unseren Anteil an diesem Geschäft nicht verlieren sollten im September 1941 betrug der amerikanische Anteil an den Motoröl Einfuhren 94%. und damit lief der Krieg im wahrsten Sinne des Wortes wie geschmiert für die Beteiligten amerikanischen Firmen Einnahme der in diesem Zusammenhang neben Rockefeller harryman und den IG Farben Direktoren den Bankiers Paul und Max Warburg immer wieder auftritt ist Senator presken Busch der Vater des ehemaligen Präsidenten George Bush und Großvater von George Bush tätigte Geschäfte mit der deutschen Luftwaffe ferner für die er weiter Geld Transaktionen über die Union Banking Corporation durch damit verstieß er gegen das Gesetz dass einen Handel mit dem Feind verbietet er wurde aber nie dafür belangt die deutschen Großindustriellen Fritz Thyssen sowie Friedrich Flick wickelten ihre Bankgeschäfte über Busch John den Bank ab mit der Unterstützung von presskan Bush und Felix Warburg Bank aus Kuhn Loeb und Co organisierte der spätere Außenminister john Foster Dallas während der 30er Jahre die schuldenrestrukturierungen für deutsche Firmen damit ermöglichte er die Umstellung auf die Rüstungsproduktion wofür Busch und Warburg enorme Summen kassierten wie bereits erwähnt war der wichtigste dreh- und Angelpunkt für die Geschäfte die mit Deutschland abgewickelt worden sind die IG Farben interessant ist das nach dem Krieg die hauptproduktionsstätten der deutschen Rüstungsindustrie unter der Führung der IG Farben noch zu über 80% intakt waren es ist jedoch sehr wahrscheinlich dass die Alliierten die Standorte dieser Fabriken genau kannten sollte das tatsächlich der Fall gewesen sein hätte der Krieg schon Jahre vorher durch die Alliierten mit der Zerstörung der Anlagen beendet werden können das wiederum würde bedeuten dass die Profiteure des Krieges an einem schnellen Ende kein Interesse hatten Charles Heimen ehemalige Reporter der New York Times weist in seinem Buch Trading the enemy auf den Umstand hin dass die US-Regierung versucht hatte die Rolle von Busch und vielen anderen führenden amerikanischen Finanz und Industriemagnaten bei der Unterstützung Hitlers zu verschleiern die Regierung habe befürchtet eine Verfolgung dieser Person würde einen öffentlichen Skandal verursachen und die öffentliche Moral untergraben und Streiks und vielleicht sogar Meutereien in den Streitkräften provozieren außerdem glaubte die Regierung so Heimen weiter ihre Anklage und Verurteilung würde es den unternehmensvorständen unmöglich machen die Kriegsanstrengungen Amerikas zu unterstützen die Profite aus dem Zweiten Weltkrieg waren nicht das einzige was aus der Sicht der Siegermächte eine profitable der Sache war da gab es noch etwas anderes was lange im Dunkeln verborgen blieb und dessen mystischer Glanz seit jeher die Menschen in seinen Bann zieht und Begehrlichkeiten weckt gold ich hoffe dass ihr neue Sachen auch dazu lernen konntet bei diesen Hörbuch Kapitel teilt es dringend mit Freunden und Bekannten dass unsere Gemeinschaft immer größer wird und schaut euch noch mal die Beschreibung an weil weiterführende Links findet ihr genau dort bis zum nächsten Hörbuch Kapitel</t>
+  </si>
+  <si>
+    <t>8.5</t>
+  </si>
+  <si>
+    <t>jaY81wxdKko</t>
+  </si>
+  <si>
+    <t>hallo ihr Lieben Heiko ist hier ich habe heute eine Menge gepostet über die große GEZ Lüge die von euch die seit Jahren mein Format verfolgen die den großen Prozess mitbekommen haben im Jahre 2020 Potsdam wo Zucker 1.000 Leute vor der Tür Standspiegel wie immer mit Lügen darüber berichtet hat die wissen dass wir eigentlich alle nur noch müde drüber lachen können das jetzt aufgedeckt wird oh die großen schoßen Fernsehen die haben ja so viel Geld kassiert die verdienen ja pro Minute weil sie 6000 wie auch immer ist schon alles im Buch drinne was Klaus Kleber verdient hat die gezüge im Endeffekt müsst euch vorstellen das ist immer der Sandmann ist wieder unterwegs der Sandmann der schmeißt wieder gerade den Leuten Sand in die Eule bleiben aber am narrativ darf natürlich nicht werden also narrativ heißt wir brauchen trotzdem öffentlich-rechtliches Fernsehen das war alles nicht so ganz korrekt ist darüber wird zwar die debattiert aber Fakt ist eins wir reden über ein verbrecherischen System wir reden über ein selbstbereicherungsladen mit angeschlossenen Fernsehstudio wir reden über eine pensionsbombe das wurde alles von uns detailliert beschrieben schon vor Jahren wie hoch die Pensionsverpflichtung sind der Intendanten was sind das eigentlich für Leute den Rundfunk reden sitzen in dem Buch sind alle Namen alle Politiker von A bis Z überall wer welche Partei wo drin sitzt und das Buch ist jetzt mittlerweile sechs Jahre alt sechs Jahre alt und ich finde interessant wie wir angegriffen worden ich bin damals als Rechtsextremist Nazi als alles mögliche beschimpft worden hat mich zwar nie interessiert aber so war es ihr müsst doch einfach mal erkennen dass dieses System doch kein Interesse hat irgendwie zu sagen nur gut ja jetzt oh man vielleicht macht es gehen wir mal man versucht so ähnlich wie eine DDR in der Endphase mit allen Mitteln alle zu verändern da wird honiger abgesehen ja dann kam Egon Krenz ran und die Leute waren erstmal zufrieden und dann kann man's Notruf an und er kann unter dem sehr und der hat dann die DDR verkauft quasi so so sinngemäß und hier ist es in Ordnung das heißt die Hölle wird zwar gewechselt aber der Inhalt ist immer derselbe es ist immer derselbe weil im Endeffekt geht es um nichts anderes um die Beeinflussung und das narrativ die Menschen zu verdummen die Menschen in einer Diktatur hier rein ich würde sagen hinein zu führen aber die führen sie ja nicht hinein wir sind ja schon mittendrin in dieser tiefen Diktatur und der muss weiterhin so bleiben also das ist ein Witz diese Diskussion immer darüber da habe ich damals übrigens ein bisschen anders gesehen als jetzt da ging schon mal der große Kampf um die Gebühren was sind 10 Milliarden Witz ich weiß nicht was haben wir jetzt ausgegeben das haben wir außerdem Kampf gegen Rechts 100 Milliarden Logic mittlerweile auch schon wieder ein bisschen mehr aber 10 Milliarden das gar nichts zur Not wurde zu subventioniert wichtig ist das liest hier Müller weiter vom Fernseher sitzen bleibt und sich diese Lügenpropaganda reinzieht jeden Tag aber jetzt nicht nur es billig gesagt das Fernsehen wir reden ja auch über Kanäle die auch finanziert werden im Internet für die jungen Leute dir sagen was ganz anderes guckt euch an die Kanäle die das Name steht jetzt nicht sagen aber könnte jetzt einfach rausfinden wer finanziert wird davon und nur darum geht es um nichts anderes im Endeffekt es ist nur ein verwirr Spiel für die Leute aber trotzdem soll dieses verlorene geht das System aufrecht erhalten werden deswegen nochmals guckt euch das an ich habe in der Schweiz diverse reden darüber gehalten wir haben so viel über Jahre hinweg zu dem Thema gemacht das nichts Neues dazu gekommen könnte es denken fettern Wirtschaft oh da wurde Gelder hintergangen ist alles schon bekannt es ist nur einfach mal so dass die Leichen im Keller mittlerweile immer ekliger riechen das heißt vorher konntest du irgendwie noch zudecken über die ganzen Jahre konnten Leute wie wir angegriffen werden aber jetzt ist es anders jetzt kommt doch schon ein bisschen mehr raus und das ist das Positive daran dass Tatsache sich doch der einer oder andere sich jetzt noch mal die Frage stellt irgendwas haut dir eigentlich gar nicht hin aber für wichtiger ist weniger Fernsehen sieht mehr durch weil das eigentlich die Hauptbotschaft zusammen lasst doch einfach mal diese Lügen Propaganda aus und da rede ich von allen nicht nur über die öffentlichen in diesem Sinne alles Liebe euer Heiko wünsche euch einen schönen Tag</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>R4KZrBgwrSw</t>
+  </si>
+  <si>
+    <t>[Musik] der Wettlauf in Pazifik zwischen den USA und China gewinnt dann Tempo Mitte Juli unterzeichneten die Volksrepublik China und die salomonen-inseln ein umfassendes bilaterales Abkommen darin enthalten sind neben wirtschaftlichen auch sicherheitspolitische Aspekte so besagt das Abkommen konkret die Zusammenarbeit in Fragen der Strafverfolgung und der Sicherheit wird verstärkt ich chinesische Seite wird den Salomonen bei Bedarf weiterhin Unterstützung und Hilfe bei der Stärkung der polizeilichen strafverfolgungskapazitäten der Salomonen bieten chines Präsident Chi Gin Ping kam eigens zur Unterzeichnung des Abkommens nach hohen Jahre in die Hauptstadt des pazifischen Inselstaates gegenüber dem salomonischen Premierminister Manna Absicht seines Landes die gesamte Pazifik Region zu unterstützen China versteht dass die pazifischen Inselstaaten durch den Klimawandel vor großen Herausforderung stehen und ist bereit den Austausch und die Zusammenarbeit zu verstärken schon 2022 löst ein Chinesisch salomonisches Sicherheitsabkommen einen medialen aufschreiben Westen aus besonders die USA und Australien sehen im chinesischen Bestreben ihre eigenen Einflusssphären im Pazifik bedroht angesichts der nun neu aufklammernden Kritik rechtfertigt sich sogar wahre die Salomonen haben keine Feinde nur Freunde unsere Herausforderung ist es uns weiterzuentwickeln wir reichen allen die Hand in Freundschaft wir streben eine ehrliche Zusammenarbeit und Partnerschaft mit allen Ländern an gleichzeitig waren sogar Ware aber auch in Richtung USA und Australien für eine Einmischung in die souveräne Außenpolitik seines Landes für China sind die Abkommen mit den salomonen-inseln ein Meilenstein in seiner pazifik-politik schließlich verfolgen die USA den Plan einer Eindämmung Chinas durch die inselkettenstrategie soll China durch Militärstützpunkte und den USA wohlgesonnenen Inselstaaten isoliert werden die salomonen-inseln liegen jenseits der von den USA konstruierten ersten Inselkette entsprechend groß ist das Entsetzen Washingtons über Chinas Einfluss auf den Salomonen um direkt zu kontern schlossen die USA Mitte Mai dieses Jahres ein Abkommen mit dem Pazifik statt Papa Neuguinea aber noch weitere Pazifikinsel starten im Fokus der USA Tonga war nur 2 und Kiribati vergangene Woche besuchte US-Außenminister Anthony blinken den Inselstaat Tonga dort formuliert er we are fellow President für die USA ein sicherer Hafen schonende Vergangenheit orientierte sich der Insel statt eng an der US Außenpolitik das zeigt sich auch an der Bevölkerung während auf dem Territorium Tangas knapp 100.000 Menschen siedeln Leben 70.000 Bürger Tangas in den USA entsprechend positiv zeichnet Tangas Premierminister guacavamelli so das Bild der USA international Thomas Afghanistan in subwood of the britishes Erfurts in einer Stunde aber nicht nur die USA und China kämpfen um einflussferien im Pazifik auch Frankreich bekundet sich im Kampf um den Pazifik beteiligen zu wollen Frankreich besitzt umfangreiche Überseegebiete im Pazifik ehemalige Kolonien wie Französisch Polynesien und die Insel Neukaledonien genau dorthin reiste der französische Präsident Emmanuel macron vergangene Woche zum Auftakt seiner Reise twitterte er Frankreich ist eine indopazifische Macht Neukaledonien ist aber keineswegs ein sicherer Rückhalt für Frankreichs Pazifik Ambitionen es gibt eine starke Unabhängigkeitsbewegung die einen Loslösung von frankreich fordert ein Unabhängigkeitsreferendum scheiterte zwar im dezember 2021 die Befürworter witterten jedoch einen massiven Wahlbetrug und die Spannungen dauern bis heute an Frankreich bezichtigt in des China die Unabhängigkeitsbewegung zu unterstützen die Reise macrons nach Neukaledonien und danach weiter nach Papua-Neuguinea und war nur Tour von zeitgleich zu einer großen Militärübung in der Region statt die von den USA und Australien geleitet wurde dem Marine-Manöver mit dem Namen Talisman sable es stellt sich die Frage reit Frankreich sich in die Anti chinesische Front im Pazifik ein oder spielt Paris auf eigene Rechnung Anfang Juli hatte macronate brüskiert durch sein Veto gegen die Eröffnung eines NATO Büros in der japanischen Hauptstadt Tokio am Rande des Nato-Gipfels in Vilnius begründete der französische Präsident was auch immer die Leute sagen die Geographie ist hartnäckig der indupazifische Raum ist nicht der nordatlantische Raum ich bin zwar der Meinung dass die Nato-Partner in anderen Regionen haben sollte aber man darf nicht vergessen dass NATO für North Atlantic 3D organization steht diese Haltung macrons wird von China geteilt der Sprecher des chinesischen Außenministeriums macht deutlich was sein Land von einer Präsenz der NATO in Asien hält Sache die mir eigentlich was meint ihr wer wird sich am Ende durchsetzen im Kampf um den Pazifik China oder die USA wer ist der bessere Bündnispartner für die Inselstaaten im Pazifik und welche Rolle spielt Frankreich in diesem Spiel schreibt uns eure mein ungen in die Kommentare [Musik]</t>
+  </si>
+  <si>
+    <t>HND_g5h4u8A</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>Haftbefehl spricht über Immobilien ich bekomme von euch auf Instagram immer sehr coole Release zugeschickt da werde ich jetzt mal auf ein paar Projekten werden coolen real hat kann einfach mir das Ganze zu schicken hier ist eine insta dann werde ich eventuell drauf reagieren schauen wir uns mal kurz das Video an weil hier geht's darum wie kann man mit Immobilien Geld verdienen und das will ich für euch mal aufklären okay checken was ab oder 4 Millionen so 3 Minuten könnte man sich eventuell Immobilien in Deutschland kaufen die im Jahr 100 bis 150.000 € abschmeißen das wird heißen Monaten 10 Jahre sauber auf die Hand und Zehner saftig dann hast du ausgesucht dein Leben lang oder zehn also auf die Hand kriegst sag mal zwei Finanzamt irgendwas solchen dass sie wieder ansehen das sind zwei also im Jahr ja du kriegst du sie macht bist du durch dann brauchst du die nix mehr Gedanken weißt du schon grob wie viele Millionen du brauchst oder sowas jeden Monat deine Mühle hast du 6 Millionen Monat dicker okay also gehen wir das mal durch Leute ich spricht er von zwei bis vier m okay jetzt nehmen wir mit einem konkreten Fall durchgehen dass sie mal wisst diese Immobiliengeschäft ungefähr abläuft so da meinte 100 bis 150k Mieteinnahmen er sagt ca 20% Steuer bleiben also 8k übrig jetzt will ich mal mit euch ein konkretes Beispiel durchgehen und zwar ein Kunde von mir 200k für Immobilie bezahlt wie man das bezahlt wie man das sogar ohne Eigenkapital machen kann wie man also im Endeffekt mehr oder weniger sogar aus dem Nichts Vermögen aufbauen kann auch passive Einnahmen aufbauen kann dazu gleich mehr aber er bekommt für diese 200.000 Euro ca 700 € Mieteinnahmen so wenn wir jetzt also mal hier von dem Wert 3 Millionen ausgehen das würde also heißen wenn wir jetzt hier pro 100000 also pro 100k kriegen wir dann also hier in dem Beispiel 350 und jetzt hängt natürlich komplett davon ab hast du jetzt die Immobilie in München in Stuttgart am Bodensee ist in Leipzig welcher Zuschauer das ist ein extrem viele Faktoren du kannst pro 100000 € kannst du 200 € Miete kriegen kannst aber auch 1000 € Miete kriegen jetzt gehen wir mal wirklich so ein durchschnittliches echtes Beispiel so da haben wir jetzt hier 350 Euro pro Monat wenn wir jetzt also drei Millionen eingesetzt haben ja den Mittelwert von dem wir jetzt hier gesprochen hat dann müssen wir jetzt diese 100k mal 30 machen das heißt jetzt gehen wir mal hier in unseren Rechner rein und machen jetzt diese 350 x 30 das sind knapp über 10 kg So 30 mal 350 sind glaube ich zehn fünf ja so sind 10.500 Euro und das muss ich jetzt mal 12 rechnen dass ich ein Jahr habe das heißt das jetzt mal 12 dann bin ich jetzt hier bei 126 000 €, also wenn ich jetzt in den Mittelwert nehmen dann bin ich jetzt wirklich genau bei den Mittelwert hier den er gesagt hat 126k es kommt natürlich darauf an besitzt du die Immobilien selber dann geht's am einkommensteuerersatz dann zahlst du bis zu 50% sogar Steuer drauf dann kann sein da bleiben dann pro Monat und diesen zehn fünf vielleicht nur noch ca 5 übrig ja und dann kommt natürlich eben noch drauf an hast du das ganze vielleicht in der GmbH oder anderes also die Rechnung die er jetzt hier gerade aufgezeigt hat die stimmt sogar so und jetzt schauen wir uns mal wie kannst du denn so ein Beispiel haben von 200k ohne dass du Eigenkapital zahlst also der Haftbefehl die ich jetzt mal starte von außen ist selbstständiger bzw Unternehmer ist keine Angestellter das heißt also er hat jetzt diese Möglichkeit von Anfang an nicht wenn du Angestellter bist und jetzt z.B ab 2,1° netto für Dienst und unbefristeten Arbeitsvertrag hast dann bekommst du von der Bank im Regelfall + - z.B 200000 € für eine Immobilie und so wie wir das auch machen ohne Eigenkapital jetzt hast du aber ca 6,5%, was du im Jahr Zins + Tilgung zahlst so jetzt zahlst du hier ungefähr 4,5 bis 6 Prozent Zins je nach Einkommen Bonität Kosten Bank etc und hast zwischen ein bis zwei Prozent Tilgung okay das heißt also du zahlst jetzt 12 bis 13k pro Jahr ab also sagen wir mal ungefähr 1000 Euro pro Monat über zum Beispiel 25 bis maximal 30 Jahre jetzt haben wir aber vorhin gesehen du bekommst ja einen anführerzeichen nur 700 Euro Miete ja musst du also noch mal 300 Euro selber beisteuern braucht zwar kein Eigenkapital muss aber noch mal beisteuern und ich gehe jetzt hier wirklich alles relativ grob durch okay so von diesen 300 Euro weil du jetzt Zinskosten gegen deine Einnahmen stellen kannst kriegst du von der Steuer noch mal Geld zurück du zahlst also effektiv ca 150 Euro Salz also effektiv das heißt jetzt zahlst du zum Beispiel 25 Jahre effektiv 150 Euro sind also 45k hast du also insgesamt bezahlt 200 245k und ich persönlich sagen legst du noch mal ähnlich viel auf die Seite für später in 20 30 Jahren Renovierungsarbeiten badküche etc bist du vielleicht bei 92 achso insgesamt bezahlt hast hat fast alles die Miete bezahlt du hast nur 90k bezahlt und das Objekt wird jetzt wahrscheinlich durch allein schon durch die Inflation durch die Wertsteigerung wahrscheinlich 400k wert sein hast du also 300k aus dem Nichts erschaffen und hast dann zu diesem Zeitpunkt wenn wir jetzt nach dieser Rechnung gehen noch Mieteinnahmen von wie viel sagen wir sind jetzt von 350 mein mindestens auf 500 gestiegen wahrscheinlich mehr ja gibt es überhaupt ein 25 Jahren den Euro noch haben wir da wieder eine D-Mark oder wieder irgendwas anderes und dann wärst Du bei 400 also 4 mal 500 bei 2000 Euro mit einer an du hast ja also fast also nichts nur mit einer Zuzahlung von 150 € hast du dir 300k extra Vermögen aufgebaut und passive Einnahmen von 2K geht es halt selbstständiger auch geht auch da musst du aber meistens wirklich schon mal drei richtig saubere gute Jahresabschlüsse mit mindestens 60 bis 100000 Euro Einkommen für dich was wieder rausgezogen hast aus der Selbständigkeit vorweisen können und wichtig ist eben auch deswegen zum Beispiel Gerald Hörnern sagt er du sollst da wo du wohnst mieten und das was du kaufst sollst zu vermieten warum z.B wenn du jetzt dir was bei der Bank holst wo du selber drin wohnen willst dann hast du wieder ein ganz anderes Thema den Griff zu bekommen plus du kannst natürlich die Zinsen nicht als Kosten wieder mit der Steuer verrechnen das also nochmal in riesen Thema das also so ein bisschen Einführung in das Thema Immobilien ich persönlich kann so gut wie jedem empfehlen dass man sich zu einem gewissen Zeitpunkt besser früher als später eine Immobilie holt dann stell dir mal vor du beginnst jetzt dein ganzes Leben lang zwei zwei fünf drei fünf netto und hast dann im Endeffekt nach 25 Jahren wenn du z.B 45 oder 50 bist eben nicht diese Partner tausend Eigenkapital aufgebaut du hast dir nicht diese Steuerersparnisse geholt du hast dir keine Beziehung mit der Bank aufgebaut ist natürlich meistens deutlich schlechter das heißt also wenn ich sowas interessiert der erste Link oder einfach hier bei Whatsapp Immobilien schreiben dann können wir dich jetzt mal komplett beraten und allgemein ich persönlich sage immer eine Immobilie war bei mir das allererste große Investment sogar wenn wir jetzt bei mir auf dem Youtube-Kanal geht dann seht mir das Thema Immobilien ganz vorne und ich würde jedem empfehlen befasst die mit Immobilien und dann aber auch als nächstes befasst dich wirklich mit Aktien jeden Monat ein bisschen was ein ETFs rein befasst sich mit Krypto mit hirosk da ein bisschen was rein und sicherlich auch ab Gold und Silber da noch ein bisschen was rein das heißt also natürlich Fazit unterm Strich wenn du Angestellter bist ich würde mir das abchecken und würde aber trotzdem das ist jetzt für mich der zweite große Vorteil wenn man angestellt ist man ja meistens 35 40 Stunden Woche da kannst du locker noch 10 20 Stunden nebenbei was machen nebenbei was machen und kannst dann da auch noch mal locker 1 2 5 10 20.000 Euro noch mal zusätzlich für dienen zum Beispiel mit marketingvertrieb und da selbstständigen Tätigkeit nebendran hast trotzdem deine Bonität trotzdem den Fix Einkommen und nach der Arbeit und dann Wochenende Pause dann die eben dazu noch zusätzlich was auf ja es ist also absolut meine Empfehlung und dann würde ich mir mit dem erhöhten Einkommen natürlich klar auch ein besseren Lifestyle leisten aber ich würde auch hergehen und neben dem Thema Immobilien auch abchecken Aktien kryptus Gold und Silber zur Absicherung ja das sind also die Themen dann hast du alle vier alle vier Säulen abgedeckt und dann 30 Jahren 40 50 Jahren hast du ein paar hunderttausende Immobilien und ein all diesen drei eselklassen auch nochmal richtig Geld und dann bis zum Endeffekt abgesichert und ihr wisst ja selber wie es mit der Rente läuft hast du lieber ein paar tausend Euro Miete ein richtiges Polster an Vermögen noch eine richtig gute Bonität und insgesamt ein paar hunderttausend Euro in Aktien Gold Silber und Krypto kann ich also absolut empfehlen viel besser als einfach nur irgendwie auf die Rente zu warten und wenn ihr irgendwelche anderen coolen Videos habt schickt mir einfach zu das war's von meiner Seite und wer das Thema Geld verdienen sich noch anschauen will ich habe eine komplett gratis Kurs einen magischen Lied generierer Kurs mit dem Thema im Monat ich ich will es ja gar nicht ansprechen weil viele glauben das gar nicht aber wirklich nebenbei noch mal in Cashflow von mehreren 1000 € aufbauen kann ein bisschen gratis Download einfach hier schreiben Marketing bei Whatsapp oder dann wahrscheinlich die der zweite Link unten sein schaut euch an ich gucke mir jetzt noch ein paar andere von euren Videos an dem mir zugeschickt habt auf Instagram ist dann</t>
+  </si>
+  <si>
+    <t>lKEIDe7DKgY</t>
+  </si>
+  <si>
+    <t>in der umkämpften Region Berg Karabach hat es am Montag eine Explosion in einem Treibstofflager gegeben dem örtlichen Gesundheitsministerium zufolge sollen dabei mindestens 20 Menschen ums Leben gekommen sein 290 weitere Menschen seien ins Krankenhaus eingeliefert worden dutzende verletzte schweben in Lebensgefahr die Ursache der schweren Explosion war bis Dienstagnachmittag noch unklar eine Politikerin erklärte an dem Lager hätten zum Zeitpunkt des Unglücks viele Menschen für Benzin angestanden weil sie mit Autos nach Armenien fliehen wollten Aserbaidschan und Armenien kämpfen seit Jahren um das Gebiet Bergkarabach gehört völkerrechtlich zu Aserbaidschan in dem Gebiet leben aber überwiegend Armenia vor einer Woche hatte das autoritär geführte Aserbaidschan eine Militäroperation zu Eroberung bergkarabachs gestartet bereits ein Tag später mussten die Pro armenischen Kämpfer eine Waffenstillstandsvereinbarung akzeptieren dass menschenrechtsbüro der Region appellierte an die Weltgemeinschaft das ist dringend notwendig sei schwer verletzte Menschen zu Behandlung auszufliegen die medizinischen Kapazitäten Berg Karabach sind nicht ausreichend um die Leben der Menschen zu retten hieß es in der Mitteilung auf der früher als Twitter bekannten Plattform x die humanitäre Lage in Bergkarabach ist ohnehin katastrophal seit Monaten blockieren Aserbaidschaner die einzig armenische Zufahrtsstraße weshalb Lebensmittel Medikamente und Benzin in der Region knapp sind die zehntausenden armenischen Zivilisten in der Region fürchten nun vertrieben oder von den neuen aserbaidschanischen Machthabern unterdrückt zu werden nach Angaben der armenischen Regierung trafen bis Dienstag rund 13.000 Flüchtlinge aus der Kaukasus Region in Armenien ein im Land selbst gibt es schwere Proteste gegen die Regierung die sich nach Angaben der Demonstranten zu wenig für die Karabach Armenia eingesetzt hat</t>
   </si>
 </sst>
 </file>
@@ -190,12 +406,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -476,406 +694,1109 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H18"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:H50"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="3" width="12.73046875" customWidth="1"/>
+    <col min="1" max="1" width="12.77734375" customWidth="1"/>
+    <col min="2" max="3" width="12.77734375" style="3" customWidth="1"/>
+    <col min="4" max="7" width="8.88671875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="3" t="s">
         <v>9</v>
       </c>
       <c r="H1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="1">
-        <v>0</v>
-      </c>
-      <c r="C2" s="1">
-        <v>1</v>
-      </c>
-      <c r="D2">
+      <c r="B2" s="4">
+        <v>0</v>
+      </c>
+      <c r="C2" s="4">
+        <v>1</v>
+      </c>
+      <c r="D2" s="3">
         <v>4</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="3">
         <v>0</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="1">
-        <v>0</v>
-      </c>
-      <c r="C3" s="1">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>5</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-      <c r="F3">
+      <c r="B3" s="4">
+        <v>0</v>
+      </c>
+      <c r="C3" s="4">
+        <v>1</v>
+      </c>
+      <c r="D3" s="3">
+        <v>5</v>
+      </c>
+      <c r="E3" s="3">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3">
         <v>4</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="3">
         <v>3</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="1">
-        <v>0</v>
-      </c>
-      <c r="C4" s="1">
-        <v>0</v>
-      </c>
-      <c r="D4">
+      <c r="B4" s="4">
+        <v>0</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3">
         <v>-1</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="3">
         <v>-1</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="1">
-        <v>0</v>
-      </c>
-      <c r="C5" s="1">
-        <v>0</v>
-      </c>
-      <c r="D5">
+      <c r="B5" s="4">
+        <v>0</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3">
         <v>-1</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="3">
         <v>-1</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="1">
-        <v>0</v>
-      </c>
-      <c r="C6" s="1">
-        <v>0</v>
-      </c>
-      <c r="D6">
+      <c r="B6" s="4">
+        <v>0</v>
+      </c>
+      <c r="C6" s="4">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3">
         <v>-1</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="3">
         <v>-1</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="1">
-        <v>0</v>
-      </c>
-      <c r="C7" s="1">
-        <v>1</v>
-      </c>
-      <c r="D7">
-        <v>5</v>
-      </c>
-      <c r="E7">
+      <c r="B7" s="4">
+        <v>0</v>
+      </c>
+      <c r="C7" s="4">
+        <v>1</v>
+      </c>
+      <c r="D7" s="3">
+        <v>5</v>
+      </c>
+      <c r="E7" s="3">
         <v>0</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="1">
-        <v>0</v>
-      </c>
-      <c r="C8" s="1">
-        <v>1</v>
-      </c>
-      <c r="D8">
-        <v>5</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8">
+      <c r="B8" s="4">
+        <v>0</v>
+      </c>
+      <c r="C8" s="4">
+        <v>1</v>
+      </c>
+      <c r="D8" s="3">
+        <v>5</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3">
         <v>3</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="3">
         <v>0</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B9" s="1">
-        <v>0</v>
-      </c>
-      <c r="C9" s="1">
-        <v>1</v>
-      </c>
-      <c r="D9">
-        <v>5</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9">
-        <v>5</v>
-      </c>
-      <c r="G9">
+      <c r="B9" s="4">
+        <v>0</v>
+      </c>
+      <c r="C9" s="4">
+        <v>1</v>
+      </c>
+      <c r="D9" s="3">
+        <v>5</v>
+      </c>
+      <c r="E9" s="3">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3">
+        <v>5</v>
+      </c>
+      <c r="G9" s="3">
         <v>2</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B10" s="1">
-        <v>0</v>
-      </c>
-      <c r="C10" s="1">
-        <v>1</v>
-      </c>
-      <c r="D10">
-        <v>5</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="F10">
-        <v>5</v>
-      </c>
-      <c r="G10">
+      <c r="B10" s="4">
+        <v>0</v>
+      </c>
+      <c r="C10" s="4">
+        <v>1</v>
+      </c>
+      <c r="D10" s="3">
+        <v>5</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3">
+        <v>5</v>
+      </c>
+      <c r="G10" s="3">
         <v>2</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B11" s="1">
-        <v>0</v>
-      </c>
-      <c r="C11" s="1">
-        <v>0</v>
-      </c>
-      <c r="D11">
+      <c r="B11" s="4">
+        <v>0</v>
+      </c>
+      <c r="C11" s="4">
+        <v>0</v>
+      </c>
+      <c r="D11" s="3">
         <v>4</v>
       </c>
-      <c r="E11">
+      <c r="E11" s="3">
         <v>0</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B12" s="1">
-        <v>0</v>
-      </c>
-      <c r="C12" s="1">
-        <v>1</v>
-      </c>
-      <c r="D12">
-        <v>5</v>
-      </c>
-      <c r="E12">
+      <c r="B12" s="4">
+        <v>0</v>
+      </c>
+      <c r="C12" s="4">
+        <v>1</v>
+      </c>
+      <c r="D12" s="3">
+        <v>5</v>
+      </c>
+      <c r="E12" s="3">
         <v>0</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B13" s="1">
-        <v>1</v>
-      </c>
-      <c r="C13" s="1">
-        <v>1</v>
-      </c>
-      <c r="D13">
-        <v>5</v>
-      </c>
-      <c r="E13">
+      <c r="B13" s="4">
+        <v>1</v>
+      </c>
+      <c r="C13" s="4">
+        <v>1</v>
+      </c>
+      <c r="D13" s="3">
+        <v>5</v>
+      </c>
+      <c r="E13" s="3">
         <v>3</v>
       </c>
-      <c r="F13">
+      <c r="F13" s="3">
         <v>6</v>
       </c>
-      <c r="G13">
+      <c r="G13" s="3">
         <v>4</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B14" s="1">
-        <v>0</v>
-      </c>
-      <c r="C14" s="1">
-        <v>1</v>
-      </c>
-      <c r="D14">
-        <v>5</v>
-      </c>
-      <c r="E14" s="1">
-        <v>0</v>
-      </c>
-      <c r="F14" s="1">
-        <v>5</v>
-      </c>
-      <c r="G14" s="1">
+      <c r="B14" s="4">
+        <v>0</v>
+      </c>
+      <c r="C14" s="4">
+        <v>1</v>
+      </c>
+      <c r="D14" s="3">
+        <v>5</v>
+      </c>
+      <c r="E14" s="4">
+        <v>0</v>
+      </c>
+      <c r="F14" s="4">
+        <v>5</v>
+      </c>
+      <c r="G14" s="4">
         <v>0</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B15" s="1">
-        <v>0</v>
-      </c>
-      <c r="C15" s="1">
-        <v>1</v>
-      </c>
-      <c r="D15">
-        <v>5</v>
-      </c>
-      <c r="E15" s="1">
-        <v>0</v>
-      </c>
-      <c r="F15" s="1">
-        <v>5</v>
-      </c>
-      <c r="G15" s="1">
+      <c r="B15" s="4">
+        <v>0</v>
+      </c>
+      <c r="C15" s="4">
+        <v>1</v>
+      </c>
+      <c r="D15" s="3">
+        <v>5</v>
+      </c>
+      <c r="E15" s="4">
+        <v>0</v>
+      </c>
+      <c r="F15" s="4">
+        <v>5</v>
+      </c>
+      <c r="G15" s="4">
         <v>1</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="16" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="1">
-        <v>0</v>
-      </c>
-      <c r="C16" s="1">
-        <v>1</v>
-      </c>
-      <c r="D16">
-        <v>5</v>
-      </c>
-      <c r="E16" s="1">
+      <c r="B16" s="4">
+        <v>0</v>
+      </c>
+      <c r="C16" s="4">
+        <v>1</v>
+      </c>
+      <c r="D16" s="3">
+        <v>5</v>
+      </c>
+      <c r="E16" s="4">
         <v>0</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="17" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="1">
-        <v>0</v>
-      </c>
-      <c r="C17" s="1">
-        <v>0</v>
-      </c>
-      <c r="D17">
+      <c r="B17" s="4">
+        <v>0</v>
+      </c>
+      <c r="C17" s="4">
+        <v>0</v>
+      </c>
+      <c r="D17" s="3">
         <v>-1</v>
       </c>
-      <c r="E17" s="1">
+      <c r="E17" s="4">
         <v>-1</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>40</v>
       </c>
+      <c r="B18" s="4">
+        <v>0</v>
+      </c>
+      <c r="C18" s="4">
+        <v>1</v>
+      </c>
+      <c r="D18" s="3">
+        <v>5</v>
+      </c>
+      <c r="E18" s="4">
+        <v>0</v>
+      </c>
+      <c r="F18" s="4">
+        <v>5</v>
+      </c>
+      <c r="G18" s="4">
+        <v>0</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B19" s="4">
+        <v>0</v>
+      </c>
+      <c r="C19" s="4">
+        <v>1</v>
+      </c>
+      <c r="D19" s="3">
+        <v>3</v>
+      </c>
+      <c r="E19" s="4">
+        <v>9</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B20" s="4">
+        <v>0</v>
+      </c>
+      <c r="C20" s="4">
+        <v>1</v>
+      </c>
+      <c r="D20" s="3">
+        <v>5</v>
+      </c>
+      <c r="E20" s="4">
+        <v>0</v>
+      </c>
+      <c r="F20" s="4">
+        <v>5</v>
+      </c>
+      <c r="G20" s="4">
+        <v>1</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B21" s="4">
+        <v>0</v>
+      </c>
+      <c r="C21" s="4">
+        <v>0</v>
+      </c>
+      <c r="D21" s="3">
+        <v>-1</v>
+      </c>
+      <c r="E21" s="4">
+        <v>-1</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B22" s="4">
+        <v>0</v>
+      </c>
+      <c r="C22" s="4">
+        <v>0</v>
+      </c>
+      <c r="D22" s="3">
+        <v>-1</v>
+      </c>
+      <c r="E22" s="4">
+        <v>-1</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B23" s="4">
+        <v>0</v>
+      </c>
+      <c r="C23" s="4">
+        <v>1</v>
+      </c>
+      <c r="D23" s="3">
+        <v>7</v>
+      </c>
+      <c r="E23" s="4">
+        <v>0</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A24" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B24" s="4">
+        <v>0</v>
+      </c>
+      <c r="C24" s="4">
+        <v>0</v>
+      </c>
+      <c r="D24" s="3">
+        <v>-1</v>
+      </c>
+      <c r="E24" s="4">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A25" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B25" s="4">
+        <v>0</v>
+      </c>
+      <c r="C25" s="4">
+        <v>0</v>
+      </c>
+      <c r="D25" s="3">
+        <v>-1</v>
+      </c>
+      <c r="E25" s="4">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A26" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B26" s="4">
+        <v>0</v>
+      </c>
+      <c r="C26" s="4">
+        <v>1</v>
+      </c>
+      <c r="D26" s="3">
+        <v>5</v>
+      </c>
+      <c r="E26" s="4">
+        <v>0</v>
+      </c>
+      <c r="F26" s="3">
+        <v>4</v>
+      </c>
+      <c r="G26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A27" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B27" s="4">
+        <v>0</v>
+      </c>
+      <c r="C27" s="4">
+        <v>1</v>
+      </c>
+      <c r="D27" s="3">
+        <v>8</v>
+      </c>
+      <c r="E27" s="4">
+        <v>8</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A28" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B28" s="4">
+        <v>1</v>
+      </c>
+      <c r="C28" s="4">
+        <v>1</v>
+      </c>
+      <c r="D28" s="3">
+        <v>7</v>
+      </c>
+      <c r="E28" s="4">
+        <v>8</v>
+      </c>
+      <c r="F28" s="4">
+        <v>7</v>
+      </c>
+      <c r="G28" s="4">
+        <v>8</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A29" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B29" s="4">
+        <v>0</v>
+      </c>
+      <c r="C29" s="4">
+        <v>1</v>
+      </c>
+      <c r="D29" s="3">
+        <v>8</v>
+      </c>
+      <c r="E29" s="4">
+        <v>9</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A30" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B30" s="4">
+        <v>0</v>
+      </c>
+      <c r="C30" s="4">
+        <v>1</v>
+      </c>
+      <c r="D30" s="3">
+        <v>6</v>
+      </c>
+      <c r="E30" s="4">
+        <v>2</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A31" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B31" s="4">
+        <v>0</v>
+      </c>
+      <c r="C31" s="4">
+        <v>1</v>
+      </c>
+      <c r="D31" s="3">
+        <v>9</v>
+      </c>
+      <c r="E31" s="4">
+        <v>9</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A32" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B32" s="4">
+        <v>0</v>
+      </c>
+      <c r="C32" s="4">
+        <v>1</v>
+      </c>
+      <c r="D32" s="3">
+        <v>5</v>
+      </c>
+      <c r="E32" s="4">
+        <v>0</v>
+      </c>
+      <c r="F32" s="4">
+        <v>5</v>
+      </c>
+      <c r="G32" s="4">
+        <v>0</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A33" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B33" s="4">
+        <v>0</v>
+      </c>
+      <c r="C33" s="4">
+        <v>1</v>
+      </c>
+      <c r="D33" s="3">
+        <v>5</v>
+      </c>
+      <c r="E33" s="4">
+        <v>0</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A34" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B34" s="4">
+        <v>0</v>
+      </c>
+      <c r="C34" s="4">
+        <v>1</v>
+      </c>
+      <c r="D34" s="3">
+        <v>5</v>
+      </c>
+      <c r="E34" s="4">
+        <v>0</v>
+      </c>
+      <c r="F34" s="4">
+        <v>6</v>
+      </c>
+      <c r="G34" s="4">
+        <v>0</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A35" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B35" s="4">
+        <v>0</v>
+      </c>
+      <c r="C35" s="4">
+        <v>1</v>
+      </c>
+      <c r="D35" s="3">
+        <v>5</v>
+      </c>
+      <c r="E35" s="4">
+        <v>0</v>
+      </c>
+      <c r="F35" s="3">
+        <v>5</v>
+      </c>
+      <c r="G35" s="4">
+        <v>0</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A36" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B36" s="4">
+        <v>0</v>
+      </c>
+      <c r="C36" s="4">
+        <v>1</v>
+      </c>
+      <c r="D36" s="3">
+        <v>4</v>
+      </c>
+      <c r="E36" s="4">
+        <v>0</v>
+      </c>
+      <c r="F36" s="4">
+        <v>4</v>
+      </c>
+      <c r="G36" s="4">
+        <v>0</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A37" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B37" s="4">
+        <v>0</v>
+      </c>
+      <c r="C37" s="4">
+        <v>0</v>
+      </c>
+      <c r="D37" s="3">
+        <v>-1</v>
+      </c>
+      <c r="E37" s="4">
+        <v>-1</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A38" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B38" s="4">
+        <v>0</v>
+      </c>
+      <c r="C38" s="4">
+        <v>1</v>
+      </c>
+      <c r="D38" s="3">
+        <v>4</v>
+      </c>
+      <c r="E38" s="4">
+        <v>3</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A39" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B39" s="4">
+        <v>0</v>
+      </c>
+      <c r="C39" s="4">
+        <v>1</v>
+      </c>
+      <c r="D39" s="3">
+        <v>5</v>
+      </c>
+      <c r="E39" s="4">
+        <v>0</v>
+      </c>
+      <c r="F39" s="4">
+        <v>4</v>
+      </c>
+      <c r="G39" s="4">
+        <v>0</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A40" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B40" s="4">
+        <v>0</v>
+      </c>
+      <c r="C40" s="4">
+        <v>1</v>
+      </c>
+      <c r="D40" s="3">
+        <v>5</v>
+      </c>
+      <c r="E40" s="4">
+        <v>0</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A41" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B41" s="4">
+        <v>0</v>
+      </c>
+      <c r="C41" s="4">
+        <v>1</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="E41" s="4">
+        <v>0</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A42" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A43" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A44" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A45" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A46" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A47" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A48" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A49" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A50" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>112</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>